--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD706B9-61D4-416B-AA8E-6BE1845D9636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418539D3-F409-41F5-B301-D138C163D561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="380">
   <si>
     <t>Signal</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -708,10 +708,6 @@
     <t>w_wb_memtoreg_mux_data</t>
   </si>
   <si>
-    <t>ALU Output or D-MEM RDATA ([Warning] Hazard)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>w_ex_alusrc_mux_data</t>
   </si>
   <si>
@@ -837,20 +833,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_alu_forwarding_unit
-u_mem_wb_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>u_alu_forward_a_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_alu_forward_b_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_forwarding_unit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -976,92 +963,540 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_jump_mux
+    <t>w_mem_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump Flag (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump Flag (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_regdst_jal_mux_reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_regdst_jal_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rt or rd or $ra Register (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_mem_pc_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_pc_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR (WB)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_alu_negative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Negative Out</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_flush</t>
+  </si>
+  <si>
+    <t>u_pc_stall_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_if_pc_stall_mux_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I-MEM RADDR (Next) (Not Applied Load Stall)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_if_pc_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_if_i_mem_addr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PC ADDR (IF)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_if_id_bridge
+u_id_ex_bridge
+u_pc_stall_mux
+u_i_mem_addr_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_id_ex_bridge
+w_id_jump_addr
+u_i_mem_addr_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_i_mem_addr_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_addr_4_addr
+u_i_mem_addr_mux
+u_if_id_bridge
+u_pc_stall_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>o_d_mem_strb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRB_BIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_memrstrb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRB_BIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_control_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemRead Strobe (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_memwstrb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_id_ex_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MemWrite Strobe (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge</t>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge</t>
+  </si>
+  <si>
+    <t>w_ex_arbiter_req</t>
+  </si>
+  <si>
+    <t>w_ex_beq_taken</t>
+  </si>
+  <si>
+    <t>w_ex_bge_taken</t>
+  </si>
+  <si>
+    <t>w_ex_blt_taken</t>
+  </si>
+  <si>
+    <t>w_ex_bne_taken</t>
+  </si>
+  <si>
+    <t>w_ex_link_ret_addr_kill</t>
+  </si>
+  <si>
+    <t>w_ex_load_unsigned</t>
+  </si>
+  <si>
+    <t>w_ex_memrstrb</t>
+  </si>
+  <si>
+    <t>w_ex_memwstrb</t>
+  </si>
+  <si>
+    <t>w_id_load_unsigned</t>
+  </si>
+  <si>
+    <t>w_mem_arbiter_req</t>
+  </si>
+  <si>
+    <t>w_mem_branch_taken</t>
+  </si>
+  <si>
+    <t>w_mem_load_unsigned</t>
+  </si>
+  <si>
+    <t>w_mem_memrstrb</t>
+  </si>
+  <si>
+    <t>w_mem_memwstrb</t>
+  </si>
+  <si>
+    <t>w_wb_branch_taken</t>
+  </si>
+  <si>
+    <t>w_wb_ctr_link_ret_addr</t>
+  </si>
+  <si>
+    <t>w_wb_d_mem_data</t>
+  </si>
+  <si>
+    <t>w_wb_load_unsigned</t>
+  </si>
+  <si>
+    <t>w_wb_memrstrb</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>w_ex_branch
+w_ex_alu_zero</t>
+  </si>
+  <si>
+    <t>w_ex_ctr_branch_taken</t>
+  </si>
+  <si>
+    <t>w_ex_branch
+w_ex_alu_negative</t>
+  </si>
+  <si>
+    <t>STRB_BIT</t>
+  </si>
+  <si>
+    <t>u_control_unit</t>
+  </si>
+  <si>
+    <t>REG_BIT</t>
+  </si>
+  <si>
+    <t>u_regdst_mux</t>
+  </si>
+  <si>
+    <t>u_id_ex_bridge
+u_load_stall_unit</t>
+  </si>
+  <si>
+    <t>o_arbiter_req</t>
+  </si>
+  <si>
+    <t>o_d_mem_strb</t>
+  </si>
+  <si>
+    <t>w_wb_jump
+w_wb_branch_taken</t>
+  </si>
+  <si>
+    <t>u_regdst_jal_mux
+u_memtoreg_mux</t>
+  </si>
+  <si>
+    <t>DATA_BIT</t>
+  </si>
+  <si>
+    <t>u_load_ctrl</t>
+  </si>
+  <si>
+    <t>u_memtoreg_mux</t>
+  </si>
+  <si>
+    <t>Arbiter Request (EX)</t>
+  </si>
+  <si>
+    <t>Branch Equal Taken Flag</t>
+  </si>
+  <si>
+    <t>Branch Greater Equal Taken Flag</t>
+  </si>
+  <si>
+    <t>Branch Less Than Taken Flag</t>
+  </si>
+  <si>
+    <t>Branch Not Equal Taken Flag</t>
+  </si>
+  <si>
+    <t>BLT/BGEZAL Not Taken Flag Signal</t>
+  </si>
+  <si>
+    <t>Load Unsigned Flag (EX)</t>
+  </si>
+  <si>
+    <t>MemRead Strobe (EX)</t>
+  </si>
+  <si>
+    <t>MemWrite Strobe (EX)</t>
+  </si>
+  <si>
+    <t>Arbiter Request (ID)</t>
+  </si>
+  <si>
+    <t>Load Unsigned Flag (ID)</t>
+  </si>
+  <si>
+    <t>rt or rd Register (ID)</t>
+  </si>
+  <si>
+    <t>Arbiter Request (MEM)</t>
+  </si>
+  <si>
+    <t>Total Branch Taken Flag (MEM)</t>
+  </si>
+  <si>
+    <t>Load Unsigned Flag (MEM)</t>
+  </si>
+  <si>
+    <t>MemRead Strobe (MEM)</t>
+  </si>
+  <si>
+    <t>MemWrite Strobe (MEM)</t>
+  </si>
+  <si>
+    <t>Total Branch Taken Flag (WB)</t>
+  </si>
+  <si>
+    <t>Link $ra MemtoReg Flag Signal</t>
+  </si>
+  <si>
+    <t>D-MEM RDATA (WB)</t>
+  </si>
+  <si>
+    <t>Load Unsigned Flag (WB)</t>
+  </si>
+  <si>
+    <t>MemRead Strobe (WB)</t>
+  </si>
+  <si>
+    <t>u_alu_ctrl</t>
+  </si>
+  <si>
+    <t>w_ex_alu_fw_mux_data_a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_blt_taken
+w_ex_bge_taken
+w_ex_link_ret_addr_kill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_beq_taken
+w_ex_bne_taken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_beq_taken
+w_ex_bne_taken
+w_ex_blt_taken
+w_ex_bge_taken
+w_ex_link_ret_addr_kill</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_branch_taken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_beq_taken
+w_ex_bne_taken
+w_ex_blt_taken
+w_ex_bge_taken</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_flush
+u_branch_mux
+u_ex_mem_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total Branch Taken Flag (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Branch ADDR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU ForwardA MUX Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU ForwardB MUX Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_ex_ctr_branch_taken
+w_ex_ctr_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_alu_forwarding_unit
+u_wdata_forwarding_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward Output (2 Cycle) (EX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_branch_addr_adder
+u_branch_mux
+u_ex_mem_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forward_b_mux
+u_wdata_forward_2cycle_mux
+u_ex_mem_bridge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU ForwardA Output (1 Cycle)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU ForwardA Output (2 Cycle)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU ForwardB Output (1 Cycle)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU ForwardB Output (2 Cycle)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward Output (1 Cycle)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_i_mem_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I-MEM DATA (ID)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_registers
+u_control_unit
+u_regdst_mux
+u_id_ex_bridge
+u_load_stall_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_ctr_regdst</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WDATA Forward Output (2 Cycle) (MEM)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_memtoreg_mux
+u_wdata_forward_mux
+u_wdata_forward_2cycle_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_jump</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_registers
+u_wdata_forwarding_unit
+u_alu_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_regwrite</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_ctr_memtoreg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_arbiter_req</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_id_regdst_mux_reg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU Internal Interface</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU External Interface</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_load_stall_ctr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_jump_1c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_fw_ctr_jump_2c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_jump_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump Forward Output (1 Cycle)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump Forward Output (2 Cycle)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_jump_register_forward_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_jump_register_forward_mux
 u_alu_forward_a_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>w_mem_jump</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jump Flag (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jump Flag (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_regdst_jal_mux_reg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_regdst_jal_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rt or rd or $ra Register (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_mem_pc_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_pc_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC ADDR (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC ADDR (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC ADDR (WB)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_alu_negative</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU Negative Out</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_ctr_flush</t>
-  </si>
-  <si>
-    <t>u_pc_stall_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_if_pc_stall_mux_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I-MEM RADDR (Next) (Not Applied Load Stall)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_if_pc_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_if_i_mem_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PC ADDR (IF)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
-      <t xml:space="preserve">u_mem_wb_bridge
+      <t xml:space="preserve">u_jump_register_forward_mux
+u_mem_wb_bridge
 </t>
     </r>
     <r>
@@ -1092,448 +1527,52 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_if_id_bridge
-u_id_ex_bridge
-u_pc_stall_mux
-u_i_mem_addr_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_id_ex_bridge
-w_id_jump_addr
-u_i_mem_addr_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_i_mem_addr_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_addr_4_addr
-u_i_mem_addr_mux
-u_if_id_bridge
-u_pc_stall_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_d_mem_strb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRB_BIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_memrstrb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRB_BIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_control_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_id_ex_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemRead Strobe (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_memwstrb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_id_ex_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MemWrite Strobe (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ctr_load_stall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_ex_mem_bridge</t>
-  </si>
-  <si>
-    <t>u_mem_wb_bridge</t>
-  </si>
-  <si>
-    <t>w_ex_arbiter_req</t>
-  </si>
-  <si>
-    <t>w_ex_beq_taken</t>
-  </si>
-  <si>
-    <t>w_ex_bge_taken</t>
-  </si>
-  <si>
-    <t>w_ex_blt_taken</t>
-  </si>
-  <si>
-    <t>w_ex_bne_taken</t>
-  </si>
-  <si>
-    <t>w_ex_link_ret_addr_kill</t>
-  </si>
-  <si>
-    <t>w_ex_load_unsigned</t>
-  </si>
-  <si>
-    <t>w_ex_memrstrb</t>
-  </si>
-  <si>
-    <t>w_ex_memwstrb</t>
-  </si>
-  <si>
-    <t>w_id_load_unsigned</t>
-  </si>
-  <si>
-    <t>w_mem_arbiter_req</t>
-  </si>
-  <si>
-    <t>w_mem_branch_taken</t>
-  </si>
-  <si>
-    <t>w_mem_load_unsigned</t>
-  </si>
-  <si>
-    <t>w_mem_memrstrb</t>
-  </si>
-  <si>
-    <t>w_mem_memwstrb</t>
-  </si>
-  <si>
-    <t>w_wb_branch_taken</t>
-  </si>
-  <si>
-    <t>w_wb_ctr_link_ret_addr</t>
-  </si>
-  <si>
-    <t>w_wb_d_mem_data</t>
-  </si>
-  <si>
-    <t>w_wb_load_unsigned</t>
-  </si>
-  <si>
-    <t>w_wb_memrstrb</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>w_ex_branch
-w_ex_alu_zero</t>
-  </si>
-  <si>
-    <t>w_ex_ctr_branch_taken</t>
-  </si>
-  <si>
-    <t>w_ex_branch
-w_ex_alu_negative</t>
-  </si>
-  <si>
-    <t>STRB_BIT</t>
-  </si>
-  <si>
-    <t>u_control_unit</t>
-  </si>
-  <si>
-    <t>REG_BIT</t>
-  </si>
-  <si>
-    <t>u_regdst_mux</t>
-  </si>
-  <si>
-    <t>u_id_ex_bridge
-u_load_stall_unit</t>
-  </si>
-  <si>
-    <t>o_arbiter_req</t>
-  </si>
-  <si>
-    <t>o_d_mem_strb</t>
-  </si>
-  <si>
-    <t>w_wb_jump
-w_wb_branch_taken</t>
-  </si>
-  <si>
-    <t>u_regdst_jal_mux
-u_memtoreg_mux</t>
-  </si>
-  <si>
-    <t>DATA_BIT</t>
-  </si>
-  <si>
-    <t>u_load_ctrl</t>
-  </si>
-  <si>
-    <t>u_memtoreg_mux</t>
-  </si>
-  <si>
-    <t>Arbiter Request (EX)</t>
-  </si>
-  <si>
-    <t>Branch Equal Taken Flag</t>
-  </si>
-  <si>
-    <t>Branch Greater Equal Taken Flag</t>
-  </si>
-  <si>
-    <t>Branch Less Than Taken Flag</t>
-  </si>
-  <si>
-    <t>Branch Not Equal Taken Flag</t>
-  </si>
-  <si>
-    <t>BLT/BGEZAL Not Taken Flag Signal</t>
-  </si>
-  <si>
-    <t>Load Unsigned Flag (EX)</t>
-  </si>
-  <si>
-    <t>MemRead Strobe (EX)</t>
-  </si>
-  <si>
-    <t>MemWrite Strobe (EX)</t>
-  </si>
-  <si>
-    <t>Arbiter Request (ID)</t>
-  </si>
-  <si>
-    <t>Load Unsigned Flag (ID)</t>
-  </si>
-  <si>
-    <t>rt or rd Register (ID)</t>
-  </si>
-  <si>
-    <t>Arbiter Request (MEM)</t>
-  </si>
-  <si>
-    <t>Total Branch Taken Flag (MEM)</t>
-  </si>
-  <si>
-    <t>Load Unsigned Flag (MEM)</t>
-  </si>
-  <si>
-    <t>MemRead Strobe (MEM)</t>
-  </si>
-  <si>
-    <t>MemWrite Strobe (MEM)</t>
-  </si>
-  <si>
-    <t>Total Branch Taken Flag (WB)</t>
-  </si>
-  <si>
-    <t>Link $ra MemtoReg Flag Signal</t>
-  </si>
-  <si>
-    <t>D-MEM RDATA (WB)</t>
-  </si>
-  <si>
-    <t>Load Unsigned Flag (WB)</t>
-  </si>
-  <si>
-    <t>MemRead Strobe (WB)</t>
-  </si>
-  <si>
-    <t>u_alu_ctrl</t>
-  </si>
-  <si>
-    <t>w_ex_alu_fw_mux_data_a</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_blt_taken
-w_ex_bge_taken
-w_ex_link_ret_addr_kill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_beq_taken
-w_ex_bne_taken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_beq_taken
-w_ex_bne_taken
-w_ex_blt_taken
-w_ex_bge_taken
-w_ex_link_ret_addr_kill</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_ctr_branch_taken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_beq_taken
-w_ex_bne_taken
-w_ex_blt_taken
-w_ex_bge_taken</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_ctr_flush
-u_branch_mux
-u_ex_mem_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Total Branch Taken Flag (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Branch ADDR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU ForwardA MUX Data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU ForwardB MUX Data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_ex_ctr_branch_taken
-w_ex_ctr_jump</t>
+    <t>u_registers
+u_jump_register_forward_mux
+u_alu_forward_a_mux
+u_alu_forward_b_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALU Output or D-MEM RDATA</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_jump_mux
 u_ex_mem_bridge
-w_ex_ctr_flush</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_ex_mem_bridge
-u_alu_forwarding_unit
-u_wdata_forwarding_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WDATA Forward Output (2 Cycle) (EX)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_branch_addr_adder
-u_branch_mux
-u_ex_mem_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_alu_forward_b_mux
-u_wdata_forward_2cycle_mux
-u_ex_mem_bridge</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU ForwardA Output (1 Cycle)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU ForwardA Output (2 Cycle)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU ForwardB Output (1 Cycle)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALU ForwardB Output (2 Cycle)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WDATA Forward Output (1 Cycle)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_i_mem_data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I-MEM DATA (ID)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_registers
-u_control_unit
-u_regdst_mux
-u_id_ex_bridge
-u_load_stall_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_ctr_regdst</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WDATA Forward Output (2 Cycle) (MEM)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_memtoreg_mux
-u_wdata_forward_mux
-u_wdata_forward_2cycle_mux</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_jump</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_ctr_link_ret_addr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_registers
-u_wdata_forwarding_unit
-u_alu_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_regwrite</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_wb_ctr_memtoreg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_registers
-u_alu_forward_a_mux
-u_alu_forward_b_mux</t>
+w_ex_ctr_flush
+u_jump_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forwarding_unit
+u_mem_wb_bridge
+u_jump_forwarding_unit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>u_regdst_jal_mux
 u_alu_forwarding_unit
-u_wdata_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_arbiter_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_regdst_mux_reg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU Internal Interface</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CPU External Interface</t>
+u_wdata_forwarding_unit
+u_jump_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_alu_forwarding_unit
+u_jump_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_jump_register_forward_mux_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jump Forward MUX Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w_wb_ctr_link_ret_addr
+u_regdst_jal_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2025,7 +2064,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2188,6 +2227,231 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2197,218 +2461,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2753,7 +2813,7 @@
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.25" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.625" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32.625" style="1" bestFit="1" customWidth="1"/>
@@ -2765,17 +2825,17 @@
   <sheetData>
     <row r="1" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="54" t="s">
-        <v>371</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="56"/>
+      <c r="B2" s="129" t="s">
+        <v>361</v>
+      </c>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="131"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="106" t="s">
         <v>40</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -2804,10 +2864,10 @@
       <c r="D4" s="30">
         <v>1</v>
       </c>
-      <c r="E4" s="115" t="s">
+      <c r="E4" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="116" t="s">
+      <c r="F4" s="109" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="9" t="s">
@@ -2824,10 +2884,10 @@
       <c r="D5" s="31">
         <v>1</v>
       </c>
-      <c r="E5" s="117" t="s">
+      <c r="E5" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="118" t="s">
+      <c r="F5" s="111" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="10" t="s">
@@ -2904,10 +2964,10 @@
       <c r="D9" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="119" t="s">
+      <c r="E9" s="112" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="120" t="s">
+      <c r="F9" s="113" t="s">
         <v>22</v>
       </c>
       <c r="G9" s="17" t="s">
@@ -2999,10 +3059,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E14" s="53" t="s">
         <v>22</v>
@@ -3024,10 +3084,10 @@
       <c r="D15" s="45">
         <v>1</v>
       </c>
-      <c r="E15" s="121" t="s">
+      <c r="E15" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="121" t="s">
+      <c r="F15" s="114" t="s">
         <v>24</v>
       </c>
       <c r="G15" s="15" t="s">
@@ -3047,7 +3107,7 @@
       <c r="E16" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="122" t="s">
+      <c r="F16" s="115" t="s">
         <v>22</v>
       </c>
       <c r="G16" s="16" t="s">
@@ -3056,17 +3116,17 @@
     </row>
     <row r="17" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="111" t="s">
-        <v>370</v>
-      </c>
-      <c r="C18" s="112"/>
-      <c r="D18" s="112"/>
-      <c r="E18" s="112"/>
-      <c r="F18" s="112"/>
-      <c r="G18" s="113"/>
+      <c r="B18" s="132" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="133"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="134"/>
     </row>
     <row r="19" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="114" t="s">
+      <c r="B19" s="107" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="6" t="s">
@@ -3085,2516 +3145,2546 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B20" s="105">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="102">
         <f>IF(C20="","",1)</f>
         <v>1</v>
       </c>
-      <c r="C20" s="106" t="s">
-        <v>271</v>
-      </c>
-      <c r="D20" s="107">
+      <c r="C20" s="103" t="s">
+        <v>169</v>
+      </c>
+      <c r="D20" s="104">
         <v>1</v>
       </c>
-      <c r="E20" s="106" t="s">
-        <v>231</v>
-      </c>
-      <c r="F20" s="108" t="s">
-        <v>257</v>
-      </c>
-      <c r="G20" s="109" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="92">
+      <c r="E20" s="103" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="128" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="105" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B21" s="89">
         <f t="shared" ref="B21:B50" si="0">IF(C21="","",B20+1)</f>
         <v>2</v>
       </c>
-      <c r="C21" s="60" t="s">
-        <v>170</v>
-      </c>
-      <c r="D21" s="61">
-        <v>1</v>
-      </c>
-      <c r="E21" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21" s="93" t="s">
-        <v>71</v>
+      <c r="C21" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" s="58">
+        <v>4</v>
+      </c>
+      <c r="E21" s="57" t="s">
+        <v>326</v>
+      </c>
+      <c r="F21" s="71" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21" s="90" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B22" s="92">
+      <c r="B22" s="89">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C22" s="60" t="s">
-        <v>166</v>
-      </c>
-      <c r="D22" s="61">
-        <v>4</v>
-      </c>
-      <c r="E22" s="60" t="s">
-        <v>332</v>
-      </c>
-      <c r="F22" s="74" t="s">
+      <c r="C22" s="57" t="s">
+        <v>327</v>
+      </c>
+      <c r="D22" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="F22" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="G22" s="93" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B23" s="92">
+      <c r="G22" s="90" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="89">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C23" s="60" t="s">
-        <v>333</v>
-      </c>
-      <c r="D23" s="58" t="s">
+      <c r="C23" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="D23" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="60" t="s">
-        <v>202</v>
-      </c>
-      <c r="F23" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="G23" s="93" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="92">
+      <c r="E23" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="F23" s="71" t="s">
+        <v>195</v>
+      </c>
+      <c r="G23" s="90" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B24" s="89">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C24" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="D24" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="60" t="s">
-        <v>203</v>
-      </c>
-      <c r="F24" s="74" t="s">
-        <v>196</v>
-      </c>
-      <c r="G24" s="93" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="92">
+      <c r="C24" s="57" t="s">
+        <v>243</v>
+      </c>
+      <c r="D24" s="58">
+        <v>1</v>
+      </c>
+      <c r="E24" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="F24" s="71" t="s">
+        <v>328</v>
+      </c>
+      <c r="G24" s="90" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="89">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C25" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="D25" s="61">
-        <v>1</v>
-      </c>
-      <c r="E25" s="60" t="s">
+      <c r="C25" s="57" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="74" t="s">
-        <v>334</v>
-      </c>
-      <c r="G25" s="93" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="92">
+      <c r="F25" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="90" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B26" s="89">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C26" s="60" t="s">
-        <v>136</v>
-      </c>
-      <c r="D26" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="60" t="s">
+      <c r="C26" s="57" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" s="58">
+        <v>1</v>
+      </c>
+      <c r="E26" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="F26" s="74" t="s">
-        <v>119</v>
-      </c>
-      <c r="G26" s="93" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B27" s="92">
+      <c r="F26" s="71" t="s">
+        <v>329</v>
+      </c>
+      <c r="G26" s="90" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="89">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C27" s="60" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" s="61">
-        <v>1</v>
-      </c>
-      <c r="E27" s="60" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" s="74" t="s">
-        <v>335</v>
-      </c>
-      <c r="G27" s="93" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="92">
+      <c r="C27" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" s="58">
+        <v>4</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="59" t="s">
+        <v>326</v>
+      </c>
+      <c r="G27" s="90" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B28" s="89">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C28" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="D28" s="61">
-        <v>4</v>
-      </c>
-      <c r="E28" s="60" t="s">
-        <v>118</v>
-      </c>
-      <c r="F28" s="62" t="s">
-        <v>332</v>
-      </c>
-      <c r="G28" s="93" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B29" s="92">
+      <c r="C28" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="D28" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" s="57" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="71" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="90" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B29" s="89">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C29" s="60" t="s">
-        <v>169</v>
-      </c>
-      <c r="D29" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="60" t="s">
-        <v>68</v>
-      </c>
-      <c r="F29" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="G29" s="93" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="92">
+      <c r="C29" s="57" t="s">
+        <v>268</v>
+      </c>
+      <c r="D29" s="73" t="s">
+        <v>288</v>
+      </c>
+      <c r="E29" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" s="71" t="s">
+        <v>266</v>
+      </c>
+      <c r="G29" s="97" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B30" s="89">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C30" s="60" t="s">
-        <v>274</v>
-      </c>
-      <c r="D30" s="76" t="s">
-        <v>294</v>
-      </c>
-      <c r="E30" s="77" t="s">
-        <v>116</v>
+      <c r="C30" s="72" t="s">
+        <v>269</v>
+      </c>
+      <c r="D30" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="E30" s="74" t="s">
+        <v>289</v>
       </c>
       <c r="F30" s="74" t="s">
-        <v>272</v>
-      </c>
-      <c r="G30" s="100" t="s">
-        <v>310</v>
+        <v>290</v>
+      </c>
+      <c r="G30" s="98" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B31" s="92">
+      <c r="B31" s="89">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C31" s="75" t="s">
-        <v>275</v>
-      </c>
-      <c r="D31" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E31" s="77" t="s">
-        <v>295</v>
-      </c>
-      <c r="F31" s="77" t="s">
-        <v>296</v>
-      </c>
-      <c r="G31" s="101" t="s">
-        <v>311</v>
+      <c r="C31" s="72" t="s">
+        <v>270</v>
+      </c>
+      <c r="D31" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="E31" s="74" t="s">
+        <v>291</v>
+      </c>
+      <c r="F31" s="74" t="s">
+        <v>290</v>
+      </c>
+      <c r="G31" s="98" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B32" s="92">
+      <c r="B32" s="89">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C32" s="75" t="s">
-        <v>276</v>
-      </c>
-      <c r="D32" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E32" s="77" t="s">
-        <v>297</v>
-      </c>
-      <c r="F32" s="77" t="s">
-        <v>296</v>
-      </c>
-      <c r="G32" s="101" t="s">
-        <v>312</v>
+      <c r="C32" s="72" t="s">
+        <v>271</v>
+      </c>
+      <c r="D32" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="E32" s="74" t="s">
+        <v>291</v>
+      </c>
+      <c r="F32" s="74" t="s">
+        <v>290</v>
+      </c>
+      <c r="G32" s="98" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B33" s="92">
+      <c r="B33" s="89">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C33" s="75" t="s">
-        <v>277</v>
-      </c>
-      <c r="D33" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E33" s="77" t="s">
-        <v>297</v>
-      </c>
-      <c r="F33" s="77" t="s">
-        <v>296</v>
-      </c>
-      <c r="G33" s="101" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B34" s="92">
+      <c r="C33" s="72" t="s">
+        <v>272</v>
+      </c>
+      <c r="D33" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="E33" s="74" t="s">
+        <v>289</v>
+      </c>
+      <c r="F33" s="74" t="s">
+        <v>290</v>
+      </c>
+      <c r="G33" s="98" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B34" s="89">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C34" s="75" t="s">
-        <v>278</v>
-      </c>
-      <c r="D34" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E34" s="77" t="s">
-        <v>295</v>
-      </c>
-      <c r="F34" s="77" t="s">
-        <v>296</v>
-      </c>
-      <c r="G34" s="101" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B35" s="92">
+      <c r="C34" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="D34" s="58">
+        <v>3</v>
+      </c>
+      <c r="E34" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="71" t="s">
+        <v>330</v>
+      </c>
+      <c r="G34" s="90" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="89">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C35" s="60" t="s">
-        <v>141</v>
-      </c>
-      <c r="D35" s="61">
-        <v>3</v>
-      </c>
-      <c r="E35" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="F35" s="74" t="s">
-        <v>336</v>
-      </c>
-      <c r="G35" s="93" t="s">
-        <v>142</v>
+      <c r="C35" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="90" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="92">
+      <c r="B36" s="89">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C36" s="60" t="s">
-        <v>159</v>
-      </c>
-      <c r="D36" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="60" t="s">
-        <v>39</v>
-      </c>
-      <c r="F36" s="62" t="s">
+      <c r="C36" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="D36" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="57" t="s">
         <v>52</v>
       </c>
-      <c r="G36" s="93" t="s">
-        <v>341</v>
+      <c r="F36" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" s="90" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="92">
+      <c r="B37" s="89">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C37" s="60" t="s">
-        <v>174</v>
-      </c>
-      <c r="D37" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" s="60" t="s">
-        <v>52</v>
-      </c>
-      <c r="F37" s="62" t="s">
-        <v>35</v>
-      </c>
-      <c r="G37" s="93" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="92">
+      <c r="C37" s="57" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" s="58">
+        <v>1</v>
+      </c>
+      <c r="E37" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="F37" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="G37" s="90" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B38" s="89">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C38" s="60" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" s="61">
+      <c r="C38" s="57" t="s">
+        <v>331</v>
+      </c>
+      <c r="D38" s="58">
         <v>1</v>
       </c>
-      <c r="E38" s="60" t="s">
-        <v>118</v>
-      </c>
-      <c r="F38" s="62" t="s">
-        <v>68</v>
-      </c>
-      <c r="G38" s="93" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B39" s="92">
+      <c r="E38" s="71" t="s">
+        <v>332</v>
+      </c>
+      <c r="F38" s="71" t="s">
+        <v>333</v>
+      </c>
+      <c r="G38" s="90" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B39" s="89">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C39" s="60" t="s">
-        <v>337</v>
-      </c>
-      <c r="D39" s="61">
+      <c r="C39" s="57" t="s">
+        <v>245</v>
+      </c>
+      <c r="D39" s="58">
         <v>1</v>
       </c>
       <c r="E39" s="74" t="s">
         <v>338</v>
       </c>
-      <c r="F39" s="74" t="s">
-        <v>339</v>
-      </c>
-      <c r="G39" s="93" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B40" s="92">
+      <c r="F39" s="71" t="s">
+        <v>230</v>
+      </c>
+      <c r="G39" s="90" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B40" s="89">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C40" s="60" t="s">
-        <v>249</v>
-      </c>
-      <c r="D40" s="61">
-        <v>1</v>
-      </c>
-      <c r="E40" s="77" t="s">
-        <v>344</v>
-      </c>
-      <c r="F40" s="74" t="s">
-        <v>233</v>
-      </c>
-      <c r="G40" s="93" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B41" s="92">
+      <c r="C40" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" s="58">
+        <v>2</v>
+      </c>
+      <c r="E40" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" s="71" t="s">
+        <v>373</v>
+      </c>
+      <c r="G40" s="90" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="89">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C41" s="60" t="s">
-        <v>143</v>
-      </c>
-      <c r="D41" s="61">
-        <v>2</v>
-      </c>
-      <c r="E41" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="F41" s="74" t="s">
-        <v>345</v>
-      </c>
-      <c r="G41" s="93" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="92">
+      <c r="C41" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="D41" s="58">
+        <v>6</v>
+      </c>
+      <c r="E41" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" s="59" t="s">
+        <v>326</v>
+      </c>
+      <c r="G41" s="90" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B42" s="89">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C42" s="60" t="s">
-        <v>123</v>
-      </c>
-      <c r="D42" s="61">
-        <v>6</v>
-      </c>
-      <c r="E42" s="60" t="s">
-        <v>116</v>
-      </c>
-      <c r="F42" s="62" t="s">
-        <v>332</v>
-      </c>
-      <c r="G42" s="93" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B43" s="92">
+      <c r="C42" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="D42" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" s="71" t="s">
+        <v>376</v>
+      </c>
+      <c r="G42" s="90" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B43" s="89">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C43" s="60" t="s">
-        <v>186</v>
-      </c>
-      <c r="D43" s="58" t="s">
+      <c r="C43" s="57" t="s">
+        <v>180</v>
+      </c>
+      <c r="D43" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="60" t="s">
+      <c r="E43" s="57" t="s">
         <v>118</v>
       </c>
-      <c r="F43" s="74" t="s">
-        <v>204</v>
-      </c>
-      <c r="G43" s="93" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B44" s="92">
+      <c r="F43" s="71" t="s">
+        <v>339</v>
+      </c>
+      <c r="G43" s="90" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B44" s="89">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C44" s="60" t="s">
-        <v>181</v>
-      </c>
-      <c r="D44" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="60" t="s">
-        <v>118</v>
-      </c>
-      <c r="F44" s="74" t="s">
-        <v>346</v>
-      </c>
-      <c r="G44" s="93" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B45" s="92">
+      <c r="C44" s="57" t="s">
+        <v>202</v>
+      </c>
+      <c r="D44" s="58">
+        <v>1</v>
+      </c>
+      <c r="E44" s="74" t="s">
+        <v>203</v>
+      </c>
+      <c r="F44" s="71" t="s">
+        <v>217</v>
+      </c>
+      <c r="G44" s="90" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B45" s="89">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C45" s="60" t="s">
-        <v>205</v>
-      </c>
-      <c r="D45" s="61">
-        <v>1</v>
-      </c>
-      <c r="E45" s="77" t="s">
-        <v>206</v>
-      </c>
-      <c r="F45" s="74" t="s">
-        <v>220</v>
-      </c>
-      <c r="G45" s="93" t="s">
-        <v>347</v>
+      <c r="C45" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="D45" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="F45" s="59" t="s">
+        <v>63</v>
+      </c>
+      <c r="G45" s="90" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B46" s="92">
+      <c r="B46" s="89">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C46" s="60" t="s">
-        <v>172</v>
-      </c>
-      <c r="D46" s="58" t="s">
+      <c r="C46" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="E46" s="60" t="s">
-        <v>73</v>
-      </c>
-      <c r="F46" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="G46" s="93" t="s">
-        <v>74</v>
+      <c r="E46" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="F46" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="G46" s="90" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B47" s="92">
+      <c r="B47" s="89">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C47" s="60" t="s">
-        <v>114</v>
-      </c>
-      <c r="D47" s="63" t="s">
-        <v>19</v>
-      </c>
-      <c r="E47" s="77" t="s">
-        <v>116</v>
-      </c>
-      <c r="F47" s="62" t="s">
+      <c r="C47" s="61" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="G47" s="93" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B48" s="92">
+      <c r="F47" s="78" t="s">
+        <v>191</v>
+      </c>
+      <c r="G47" s="91" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B48" s="89">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C48" s="64" t="s">
-        <v>152</v>
+      <c r="C48" s="72" t="s">
+        <v>273</v>
       </c>
       <c r="D48" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="F48" s="81" t="s">
-        <v>192</v>
-      </c>
-      <c r="G48" s="94" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B49" s="92">
+        <v>288</v>
+      </c>
+      <c r="E48" s="74" t="s">
+        <v>291</v>
+      </c>
+      <c r="F48" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="G48" s="98" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="89">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C49" s="75" t="s">
-        <v>279</v>
-      </c>
-      <c r="D49" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E49" s="77" t="s">
-        <v>297</v>
-      </c>
-      <c r="F49" s="77" t="s">
-        <v>272</v>
-      </c>
-      <c r="G49" s="101" t="s">
-        <v>315</v>
+      <c r="C49" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="D49" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E49" s="57" t="s">
+        <v>73</v>
+      </c>
+      <c r="F49" s="59" t="s">
+        <v>63</v>
+      </c>
+      <c r="G49" s="90" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B50" s="95">
+      <c r="B50" s="92">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C50" s="60" t="s">
-        <v>173</v>
+      <c r="C50" s="72" t="s">
+        <v>274</v>
       </c>
       <c r="D50" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" s="60" t="s">
-        <v>73</v>
-      </c>
-      <c r="F50" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="G50" s="93" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B51" s="92">
+        <v>288</v>
+      </c>
+      <c r="E50" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="F50" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="G50" s="98" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B51" s="89">
         <f t="shared" ref="B51:B82" si="1">IF(C51="","",B50+1)</f>
         <v>32</v>
       </c>
-      <c r="C51" s="75" t="s">
-        <v>280</v>
-      </c>
-      <c r="D51" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E51" s="77" t="s">
-        <v>116</v>
-      </c>
-      <c r="F51" s="77" t="s">
-        <v>272</v>
-      </c>
-      <c r="G51" s="101" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B52" s="92">
+      <c r="C51" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="58">
+        <v>1</v>
+      </c>
+      <c r="E51" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="F51" s="78" t="s">
+        <v>226</v>
+      </c>
+      <c r="G51" s="90" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B52" s="89">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="C52" s="60" t="s">
-        <v>127</v>
-      </c>
-      <c r="D52" s="61">
-        <v>1</v>
-      </c>
-      <c r="E52" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="F52" s="81" t="s">
-        <v>229</v>
-      </c>
-      <c r="G52" s="93" t="s">
-        <v>129</v>
+      <c r="C52" s="72" t="s">
+        <v>275</v>
+      </c>
+      <c r="D52" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="E52" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="F52" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="G52" s="98" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B53" s="92">
+      <c r="B53" s="89">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
-      <c r="C53" s="75" t="s">
-        <v>281</v>
-      </c>
-      <c r="D53" s="58" t="s">
-        <v>298</v>
-      </c>
-      <c r="E53" s="77" t="s">
-        <v>116</v>
-      </c>
-      <c r="F53" s="77" t="s">
-        <v>272</v>
-      </c>
-      <c r="G53" s="101" t="s">
-        <v>317</v>
+      <c r="C53" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="D53" s="58">
+        <v>1</v>
+      </c>
+      <c r="E53" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="G53" s="90" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B54" s="92">
+      <c r="B54" s="89">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="C54" s="60" t="s">
-        <v>145</v>
-      </c>
-      <c r="D54" s="61">
+      <c r="C54" s="57" t="s">
+        <v>128</v>
+      </c>
+      <c r="D54" s="58">
         <v>1</v>
       </c>
       <c r="E54" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="F54" s="74" t="s">
+      <c r="F54" s="62" t="s">
         <v>119</v>
       </c>
-      <c r="G54" s="93" t="s">
-        <v>147</v>
+      <c r="G54" s="90" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B55" s="92">
+      <c r="B55" s="89">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="C55" s="60" t="s">
-        <v>128</v>
-      </c>
-      <c r="D55" s="61">
-        <v>1</v>
-      </c>
-      <c r="E55" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="F55" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="G55" s="93" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B56" s="92">
+      <c r="C55" s="72" t="s">
+        <v>276</v>
+      </c>
+      <c r="D55" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="E55" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="F55" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="G55" s="98" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B56" s="89">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="C56" s="75" t="s">
-        <v>282</v>
-      </c>
-      <c r="D56" s="58" t="s">
-        <v>298</v>
-      </c>
-      <c r="E56" s="77" t="s">
+      <c r="C56" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="D56" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="F56" s="77" t="s">
-        <v>272</v>
-      </c>
-      <c r="G56" s="101" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B57" s="92">
+      <c r="F56" s="71" t="s">
+        <v>341</v>
+      </c>
+      <c r="G56" s="91" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B57" s="89">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="C57" s="60" t="s">
-        <v>228</v>
-      </c>
-      <c r="D57" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="E57" s="62" t="s">
+      <c r="C57" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="D57" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E57" s="57" t="s">
         <v>116</v>
       </c>
-      <c r="F57" s="74" t="s">
-        <v>348</v>
-      </c>
-      <c r="G57" s="94" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B58" s="92">
+      <c r="F57" s="71" t="s">
+        <v>369</v>
+      </c>
+      <c r="G57" s="90" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B58" s="89">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="C58" s="60" t="s">
-        <v>102</v>
-      </c>
-      <c r="D58" s="58" t="s">
+      <c r="C58" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="D58" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="60" t="s">
+      <c r="E58" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="F58" s="74" t="s">
-        <v>235</v>
+      <c r="F58" s="79" t="s">
+        <v>342</v>
       </c>
       <c r="G58" s="93" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B59" s="92">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B59" s="89">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
-      <c r="C59" s="66" t="s">
-        <v>103</v>
-      </c>
-      <c r="D59" s="67" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" s="66" t="s">
-        <v>116</v>
-      </c>
-      <c r="F59" s="82" t="s">
-        <v>349</v>
-      </c>
-      <c r="G59" s="96" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B60" s="92">
+      <c r="C59" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="D59" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="F59" s="71" t="s">
+        <v>226</v>
+      </c>
+      <c r="G59" s="90" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B60" s="89">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
-      <c r="C60" s="60" t="s">
-        <v>199</v>
-      </c>
-      <c r="D60" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="E60" s="60" t="s">
+      <c r="C60" s="57" t="s">
+        <v>174</v>
+      </c>
+      <c r="D60" s="58">
+        <v>1</v>
+      </c>
+      <c r="E60" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="F60" s="74" t="s">
-        <v>229</v>
-      </c>
-      <c r="G60" s="93" t="s">
-        <v>200</v>
+      <c r="F60" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="G60" s="90" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B61" s="92">
+      <c r="B61" s="89">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="C61" s="60" t="s">
-        <v>175</v>
-      </c>
-      <c r="D61" s="61">
-        <v>1</v>
-      </c>
-      <c r="E61" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="F61" s="74" t="s">
-        <v>119</v>
-      </c>
-      <c r="G61" s="93" t="s">
-        <v>176</v>
+      <c r="C61" s="57" t="s">
+        <v>157</v>
+      </c>
+      <c r="D61" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="E61" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="F61" s="57" t="s">
+        <v>158</v>
+      </c>
+      <c r="G61" s="90" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B62" s="92">
+      <c r="B62" s="89">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="C62" s="60" t="s">
+      <c r="C62" s="57" t="s">
+        <v>158</v>
+      </c>
+      <c r="D62" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="D62" s="58" t="s">
-        <v>48</v>
-      </c>
-      <c r="E62" s="60" t="s">
-        <v>46</v>
-      </c>
-      <c r="F62" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="G62" s="93" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B63" s="92">
+      <c r="F62" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="G62" s="90" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B63" s="89">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="C63" s="60" t="s">
-        <v>158</v>
-      </c>
-      <c r="D63" s="58" t="s">
+      <c r="C63" s="57" t="s">
+        <v>106</v>
+      </c>
+      <c r="D63" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E63" s="60" t="s">
-        <v>157</v>
-      </c>
-      <c r="F63" s="62" t="s">
-        <v>39</v>
-      </c>
-      <c r="G63" s="93" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B64" s="92">
+      <c r="E63" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="F63" s="71" t="s">
+        <v>47</v>
+      </c>
+      <c r="G63" s="90" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B64" s="89">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="C64" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="D64" s="58" t="s">
+      <c r="C64" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="D64" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E64" s="60" t="s">
-        <v>116</v>
-      </c>
-      <c r="F64" s="74" t="s">
-        <v>47</v>
-      </c>
-      <c r="G64" s="93" t="s">
-        <v>108</v>
+      <c r="E64" s="57" t="s">
+        <v>216</v>
+      </c>
+      <c r="F64" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="G64" s="90" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B65" s="92">
+      <c r="B65" s="89">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="C65" s="60" t="s">
-        <v>221</v>
-      </c>
-      <c r="D65" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E65" s="60" t="s">
-        <v>219</v>
-      </c>
-      <c r="F65" s="60" t="s">
-        <v>119</v>
-      </c>
-      <c r="G65" s="93" t="s">
-        <v>222</v>
+      <c r="C65" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="D65" s="58">
+        <v>1</v>
+      </c>
+      <c r="E65" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="F65" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="G65" s="90" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B66" s="92">
+      <c r="B66" s="89">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="C66" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="D66" s="61">
+      <c r="C66" s="57" t="s">
+        <v>207</v>
+      </c>
+      <c r="D66" s="58">
         <v>1</v>
       </c>
-      <c r="E66" s="62" t="s">
-        <v>216</v>
-      </c>
-      <c r="F66" s="62" t="s">
-        <v>217</v>
-      </c>
-      <c r="G66" s="93" t="s">
-        <v>350</v>
+      <c r="E66" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="F66" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="G66" s="90" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B67" s="92">
+      <c r="B67" s="89">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="C67" s="60" t="s">
-        <v>210</v>
-      </c>
-      <c r="D67" s="61">
+      <c r="C67" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="D67" s="58">
         <v>1</v>
       </c>
-      <c r="E67" s="62" t="s">
-        <v>216</v>
-      </c>
-      <c r="F67" s="62" t="s">
-        <v>217</v>
-      </c>
-      <c r="G67" s="93" t="s">
-        <v>351</v>
+      <c r="E67" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="F67" s="59" t="s">
+        <v>215</v>
+      </c>
+      <c r="G67" s="90" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B68" s="92">
+      <c r="B68" s="89">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
-      <c r="C68" s="60" t="s">
-        <v>209</v>
-      </c>
-      <c r="D68" s="61">
+      <c r="C68" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="D68" s="58">
         <v>1</v>
       </c>
-      <c r="E68" s="62" t="s">
-        <v>216</v>
-      </c>
-      <c r="F68" s="62" t="s">
-        <v>218</v>
-      </c>
-      <c r="G68" s="93" t="s">
-        <v>352</v>
+      <c r="E68" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="F68" s="59" t="s">
+        <v>201</v>
+      </c>
+      <c r="G68" s="90" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B69" s="92">
+      <c r="B69" s="89">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="C69" s="60" t="s">
-        <v>211</v>
-      </c>
-      <c r="D69" s="61">
+      <c r="C69" s="57" t="s">
+        <v>363</v>
+      </c>
+      <c r="D69" s="58">
         <v>1</v>
       </c>
-      <c r="E69" s="62" t="s">
-        <v>216</v>
-      </c>
-      <c r="F69" s="62" t="s">
-        <v>203</v>
-      </c>
-      <c r="G69" s="93" t="s">
-        <v>353</v>
+      <c r="E69" s="126" t="s">
+        <v>365</v>
+      </c>
+      <c r="F69" s="126" t="s">
+        <v>368</v>
+      </c>
+      <c r="G69" s="98" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B70" s="92">
+      <c r="B70" s="89">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
-      <c r="C70" s="60" t="s">
-        <v>212</v>
-      </c>
-      <c r="D70" s="59">
+      <c r="C70" s="57" t="s">
+        <v>364</v>
+      </c>
+      <c r="D70" s="58">
         <v>1</v>
       </c>
-      <c r="E70" s="60" t="s">
-        <v>206</v>
-      </c>
-      <c r="F70" s="62" t="s">
-        <v>197</v>
-      </c>
-      <c r="G70" s="93" t="s">
-        <v>354</v>
+      <c r="E70" s="126" t="s">
+        <v>365</v>
+      </c>
+      <c r="F70" s="126" t="s">
+        <v>368</v>
+      </c>
+      <c r="G70" s="98" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B71" s="92">
+      <c r="B71" s="89">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="C71" s="60" t="s">
-        <v>80</v>
-      </c>
-      <c r="D71" s="61">
-        <v>4</v>
-      </c>
-      <c r="E71" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="F71" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="G71" s="93" t="s">
-        <v>92</v>
+      <c r="C71" s="57" t="s">
+        <v>209</v>
+      </c>
+      <c r="D71" s="56">
+        <v>1</v>
+      </c>
+      <c r="E71" s="57" t="s">
+        <v>203</v>
+      </c>
+      <c r="F71" s="59" t="s">
+        <v>196</v>
+      </c>
+      <c r="G71" s="90" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B72" s="92">
+      <c r="B72" s="89">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="C72" s="75" t="s">
-        <v>368</v>
-      </c>
-      <c r="D72" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E72" s="77" t="s">
-        <v>299</v>
-      </c>
-      <c r="F72" s="77" t="s">
-        <v>116</v>
-      </c>
-      <c r="G72" s="101" t="s">
-        <v>319</v>
+      <c r="C72" s="57" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72" s="58">
+        <v>4</v>
+      </c>
+      <c r="E72" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="F72" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="G72" s="90" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B73" s="92">
+      <c r="B73" s="89">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="C73" s="60" t="s">
-        <v>86</v>
-      </c>
-      <c r="D73" s="61">
-        <v>3</v>
-      </c>
-      <c r="E73" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="F73" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="G73" s="93" t="s">
-        <v>99</v>
+      <c r="C73" s="72" t="s">
+        <v>358</v>
+      </c>
+      <c r="D73" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="E73" s="74" t="s">
+        <v>293</v>
+      </c>
+      <c r="F73" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="G73" s="98" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B74" s="92">
+      <c r="B74" s="89">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
-      <c r="C74" s="60" t="s">
-        <v>81</v>
-      </c>
-      <c r="D74" s="61">
-        <v>1</v>
-      </c>
-      <c r="E74" s="60" t="s">
+      <c r="C74" s="57" t="s">
+        <v>86</v>
+      </c>
+      <c r="D74" s="58">
+        <v>3</v>
+      </c>
+      <c r="E74" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="F74" s="62" t="s">
-        <v>116</v>
-      </c>
-      <c r="G74" s="93" t="s">
-        <v>94</v>
+      <c r="F74" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="G74" s="90" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B75" s="92">
+      <c r="B75" s="89">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="C75" s="60" t="s">
-        <v>358</v>
-      </c>
-      <c r="D75" s="61">
+      <c r="C75" s="57" t="s">
+        <v>81</v>
+      </c>
+      <c r="D75" s="58">
         <v>1</v>
       </c>
-      <c r="E75" s="60" t="s">
+      <c r="E75" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="F75" s="60" t="s">
-        <v>62</v>
-      </c>
-      <c r="G75" s="93" t="s">
-        <v>93</v>
+      <c r="F75" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="G75" s="90" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B76" s="92">
+      <c r="B76" s="89">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
-      <c r="C76" s="60" t="s">
-        <v>165</v>
-      </c>
-      <c r="D76" s="58" t="s">
-        <v>56</v>
-      </c>
-      <c r="E76" s="60" t="s">
-        <v>43</v>
-      </c>
-      <c r="F76" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G76" s="93" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="77" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B77" s="92">
+      <c r="C76" s="57" t="s">
+        <v>351</v>
+      </c>
+      <c r="D76" s="58">
+        <v>1</v>
+      </c>
+      <c r="E76" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="F76" s="57" t="s">
+        <v>62</v>
+      </c>
+      <c r="G76" s="90" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B77" s="89">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="C77" s="60" t="s">
-        <v>121</v>
-      </c>
-      <c r="D77" s="61">
-        <v>6</v>
-      </c>
-      <c r="E77" s="60" t="s">
+      <c r="C77" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="D77" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="E77" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="F77" s="74" t="s">
-        <v>234</v>
-      </c>
-      <c r="G77" s="93" t="s">
-        <v>122</v>
+      <c r="F77" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="G77" s="90" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="78" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B78" s="92">
+      <c r="B78" s="89">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
-      <c r="C78" s="64" t="s">
-        <v>154</v>
-      </c>
-      <c r="D78" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="E78" s="64" t="s">
+      <c r="C78" s="57" t="s">
+        <v>121</v>
+      </c>
+      <c r="D78" s="58">
+        <v>6</v>
+      </c>
+      <c r="E78" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="F78" s="81" t="s">
-        <v>41</v>
-      </c>
-      <c r="G78" s="94" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="79" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B79" s="92">
+      <c r="F78" s="71" t="s">
+        <v>231</v>
+      </c>
+      <c r="G78" s="90" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B79" s="89">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="C79" s="60" t="s">
-        <v>160</v>
-      </c>
-      <c r="D79" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="E79" s="60" t="s">
+      <c r="C79" s="61" t="s">
+        <v>154</v>
+      </c>
+      <c r="D79" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="E79" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="F79" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="G79" s="93" t="s">
-        <v>58</v>
+      <c r="F79" s="78" t="s">
+        <v>41</v>
+      </c>
+      <c r="G79" s="91" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B80" s="92">
+      <c r="B80" s="89">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="C80" s="60" t="s">
-        <v>163</v>
-      </c>
-      <c r="D80" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="E80" s="60" t="s">
+      <c r="C80" s="57" t="s">
+        <v>160</v>
+      </c>
+      <c r="D80" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="E80" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="F80" s="62" t="s">
-        <v>62</v>
-      </c>
-      <c r="G80" s="93" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="81" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B81" s="92">
+      <c r="F80" s="59" t="s">
+        <v>57</v>
+      </c>
+      <c r="G80" s="90" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B81" s="89">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="C81" s="60" t="s">
-        <v>161</v>
-      </c>
-      <c r="D81" s="58" t="s">
+      <c r="C81" s="57" t="s">
+        <v>163</v>
+      </c>
+      <c r="D81" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="E81" s="60" t="s">
+      <c r="E81" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="F81" s="74" t="s">
-        <v>230</v>
-      </c>
-      <c r="G81" s="93" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B82" s="92">
+      <c r="F81" s="59" t="s">
+        <v>62</v>
+      </c>
+      <c r="G81" s="90" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B82" s="89">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="C82" s="60" t="s">
-        <v>162</v>
-      </c>
-      <c r="D82" s="58" t="s">
+      <c r="C82" s="57" t="s">
+        <v>161</v>
+      </c>
+      <c r="D82" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="E82" s="60" t="s">
+      <c r="E82" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="F82" s="74" t="s">
-        <v>357</v>
-      </c>
-      <c r="G82" s="93" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B83" s="92">
+      <c r="F82" s="71" t="s">
+        <v>227</v>
+      </c>
+      <c r="G82" s="90" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B83" s="89">
         <f t="shared" ref="B83:B114" si="2">IF(C83="","",B82+1)</f>
         <v>64</v>
       </c>
-      <c r="C83" s="60" t="s">
-        <v>164</v>
-      </c>
-      <c r="D83" s="61">
-        <v>5</v>
-      </c>
-      <c r="E83" s="60" t="s">
+      <c r="C83" s="57" t="s">
+        <v>162</v>
+      </c>
+      <c r="D83" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E83" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="F83" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="G83" s="93" t="s">
-        <v>59</v>
+      <c r="F83" s="71" t="s">
+        <v>350</v>
+      </c>
+      <c r="G83" s="90" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B84" s="92">
+      <c r="B84" s="89">
         <f t="shared" si="2"/>
         <v>65</v>
       </c>
-      <c r="C84" s="60" t="s">
-        <v>355</v>
-      </c>
-      <c r="D84" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E84" s="60" t="s">
-        <v>117</v>
-      </c>
-      <c r="F84" s="62" t="s">
+      <c r="C84" s="57" t="s">
+        <v>164</v>
+      </c>
+      <c r="D84" s="58">
+        <v>5</v>
+      </c>
+      <c r="E84" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="G84" s="93" t="s">
-        <v>356</v>
+      <c r="F84" s="59" t="s">
+        <v>63</v>
+      </c>
+      <c r="G84" s="90" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B85" s="92">
+      <c r="B85" s="89">
         <f t="shared" si="2"/>
         <v>66</v>
       </c>
-      <c r="C85" s="60" t="s">
-        <v>224</v>
-      </c>
-      <c r="D85" s="61">
-        <v>2</v>
-      </c>
-      <c r="E85" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="F85" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="G85" s="93" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B86" s="92">
+      <c r="C85" s="57" t="s">
+        <v>348</v>
+      </c>
+      <c r="D85" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E85" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="F85" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="G85" s="90" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B86" s="89">
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="C86" s="60" t="s">
-        <v>112</v>
-      </c>
-      <c r="D86" s="63" t="s">
-        <v>20</v>
-      </c>
-      <c r="E86" s="77" t="s">
-        <v>227</v>
-      </c>
-      <c r="F86" s="62" t="s">
+      <c r="C86" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="D86" s="58">
+        <v>2</v>
+      </c>
+      <c r="E86" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="F86" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="G86" s="93" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B87" s="92">
+      <c r="G86" s="90" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B87" s="89">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="C87" s="75" t="s">
-        <v>283</v>
-      </c>
-      <c r="D87" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E87" s="77" t="s">
-        <v>299</v>
-      </c>
-      <c r="F87" s="77" t="s">
-        <v>116</v>
-      </c>
-      <c r="G87" s="101" t="s">
-        <v>320</v>
+      <c r="C87" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="D87" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E87" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="F87" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="G87" s="90" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B88" s="92">
+      <c r="B88" s="89">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="C88" s="60" t="s">
-        <v>84</v>
-      </c>
-      <c r="D88" s="61">
-        <v>1</v>
-      </c>
-      <c r="E88" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="F88" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="G88" s="93" t="s">
-        <v>97</v>
+      <c r="C88" s="72" t="s">
+        <v>277</v>
+      </c>
+      <c r="D88" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="E88" s="74" t="s">
+        <v>293</v>
+      </c>
+      <c r="F88" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="G88" s="98" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B89" s="92">
+      <c r="B89" s="89">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="C89" s="60" t="s">
-        <v>263</v>
-      </c>
-      <c r="D89" s="58" t="s">
-        <v>264</v>
-      </c>
-      <c r="E89" s="60" t="s">
-        <v>265</v>
+      <c r="C89" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="D89" s="58">
+        <v>1</v>
+      </c>
+      <c r="E89" s="57" t="s">
+        <v>57</v>
       </c>
       <c r="F89" s="62" t="s">
-        <v>266</v>
-      </c>
-      <c r="G89" s="93" t="s">
-        <v>267</v>
+        <v>118</v>
+      </c>
+      <c r="G89" s="90" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B90" s="92">
+      <c r="B90" s="89">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="C90" s="60" t="s">
-        <v>82</v>
-      </c>
-      <c r="D90" s="61">
-        <v>1</v>
-      </c>
-      <c r="E90" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="F90" s="62" t="s">
-        <v>116</v>
-      </c>
-      <c r="G90" s="93" t="s">
-        <v>95</v>
+      <c r="C90" s="57" t="s">
+        <v>258</v>
+      </c>
+      <c r="D90" s="55" t="s">
+        <v>259</v>
+      </c>
+      <c r="E90" s="57" t="s">
+        <v>260</v>
+      </c>
+      <c r="F90" s="59" t="s">
+        <v>261</v>
+      </c>
+      <c r="G90" s="90" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B91" s="92">
+      <c r="B91" s="89">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="C91" s="60" t="s">
-        <v>85</v>
-      </c>
-      <c r="D91" s="61">
+      <c r="C91" s="57" t="s">
+        <v>82</v>
+      </c>
+      <c r="D91" s="58">
         <v>1</v>
       </c>
-      <c r="E91" s="60" t="s">
+      <c r="E91" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="F91" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="G91" s="93" t="s">
-        <v>98</v>
+      <c r="F91" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="G91" s="90" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B92" s="92">
+      <c r="B92" s="89">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="C92" s="60" t="s">
-        <v>268</v>
-      </c>
-      <c r="D92" s="58" t="s">
-        <v>264</v>
-      </c>
-      <c r="E92" s="60" t="s">
-        <v>265</v>
+      <c r="C92" s="57" t="s">
+        <v>85</v>
+      </c>
+      <c r="D92" s="58">
+        <v>1</v>
+      </c>
+      <c r="E92" s="57" t="s">
+        <v>57</v>
       </c>
       <c r="F92" s="62" t="s">
-        <v>269</v>
-      </c>
-      <c r="G92" s="93" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B93" s="92">
+        <v>118</v>
+      </c>
+      <c r="G92" s="90" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B93" s="89">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="C93" s="60" t="s">
-        <v>226</v>
-      </c>
-      <c r="D93" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="E93" s="60" t="s">
-        <v>117</v>
-      </c>
-      <c r="F93" s="74" t="s">
-        <v>258</v>
-      </c>
-      <c r="G93" s="94" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B94" s="92">
+      <c r="C93" s="57" t="s">
+        <v>263</v>
+      </c>
+      <c r="D93" s="55" t="s">
+        <v>259</v>
+      </c>
+      <c r="E93" s="57" t="s">
+        <v>260</v>
+      </c>
+      <c r="F93" s="59" t="s">
+        <v>264</v>
+      </c>
+      <c r="G93" s="90" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B94" s="89">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C94" s="60" t="s">
-        <v>88</v>
-      </c>
-      <c r="D94" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E94" s="60" t="s">
-        <v>61</v>
-      </c>
-      <c r="F94" s="66" t="s">
-        <v>116</v>
-      </c>
-      <c r="G94" s="93" t="s">
-        <v>90</v>
+      <c r="C94" s="57" t="s">
+        <v>223</v>
+      </c>
+      <c r="D94" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="F94" s="71" t="s">
+        <v>253</v>
+      </c>
+      <c r="G94" s="91" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B95" s="92">
+      <c r="B95" s="89">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="C95" s="66" t="s">
-        <v>89</v>
-      </c>
-      <c r="D95" s="67" t="s">
+      <c r="C95" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="D95" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E95" s="60" t="s">
+      <c r="E95" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="F95" s="66" t="s">
+      <c r="F95" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="G95" s="96" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B96" s="92">
+      <c r="G95" s="90" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B96" s="89">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="C96" s="75" t="s">
-        <v>369</v>
-      </c>
-      <c r="D96" s="58" t="s">
-        <v>300</v>
-      </c>
-      <c r="E96" s="77" t="s">
-        <v>301</v>
-      </c>
-      <c r="F96" s="77" t="s">
-        <v>302</v>
-      </c>
-      <c r="G96" s="101" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B97" s="92">
+      <c r="C96" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="D96" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="F96" s="63" t="s">
+        <v>116</v>
+      </c>
+      <c r="G96" s="93" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B97" s="89">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C97" s="60" t="s">
-        <v>83</v>
-      </c>
-      <c r="D97" s="61">
-        <v>1</v>
-      </c>
-      <c r="E97" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="F97" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="G97" s="93" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B98" s="92">
+      <c r="C97" s="72" t="s">
+        <v>359</v>
+      </c>
+      <c r="D97" s="55" t="s">
+        <v>294</v>
+      </c>
+      <c r="E97" s="74" t="s">
+        <v>295</v>
+      </c>
+      <c r="F97" s="74" t="s">
+        <v>296</v>
+      </c>
+      <c r="G97" s="98" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B98" s="89">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
-      <c r="C98" s="60" t="s">
-        <v>156</v>
-      </c>
-      <c r="D98" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="E98" s="60" t="s">
-        <v>41</v>
-      </c>
-      <c r="F98" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="G98" s="93" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B99" s="92">
+      <c r="C98" s="57" t="s">
+        <v>83</v>
+      </c>
+      <c r="D98" s="58">
+        <v>1</v>
+      </c>
+      <c r="E98" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="F98" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="G98" s="90" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B99" s="89">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
-      <c r="C99" s="60" t="s">
-        <v>87</v>
-      </c>
-      <c r="D99" s="61">
-        <v>1</v>
-      </c>
-      <c r="E99" s="60" t="s">
-        <v>57</v>
-      </c>
-      <c r="F99" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G99" s="93" t="s">
-        <v>101</v>
+      <c r="C99" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="D99" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="E99" s="57" t="s">
+        <v>41</v>
+      </c>
+      <c r="F99" s="59" t="s">
+        <v>112</v>
+      </c>
+      <c r="G99" s="90" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B100" s="92">
+      <c r="B100" s="89">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="C100" s="60" t="s">
-        <v>109</v>
-      </c>
-      <c r="D100" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E100" s="60" t="s">
+      <c r="C100" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="D100" s="58">
+        <v>1</v>
+      </c>
+      <c r="E100" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="F100" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="F100" s="74" t="s">
-        <v>116</v>
-      </c>
-      <c r="G100" s="93" t="s">
-        <v>107</v>
+      <c r="G100" s="90" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B101" s="92">
+      <c r="B101" s="89">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C101" s="64" t="s">
-        <v>77</v>
-      </c>
-      <c r="D101" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="E101" s="64" t="s">
-        <v>38</v>
-      </c>
-      <c r="F101" s="81" t="s">
-        <v>192</v>
-      </c>
-      <c r="G101" s="94" t="s">
-        <v>78</v>
+      <c r="C101" s="57" t="s">
+        <v>109</v>
+      </c>
+      <c r="D101" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" s="71" t="s">
+        <v>116</v>
+      </c>
+      <c r="G101" s="90" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B102" s="92">
+      <c r="B102" s="89">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="C102" s="68" t="s">
-        <v>254</v>
-      </c>
-      <c r="D102" s="12" t="s">
+      <c r="C102" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="D102" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="E102" s="68" t="s">
-        <v>259</v>
-      </c>
-      <c r="F102" s="83" t="s">
-        <v>11</v>
-      </c>
-      <c r="G102" s="97" t="s">
-        <v>36</v>
+      <c r="E102" s="61" t="s">
+        <v>38</v>
+      </c>
+      <c r="F102" s="78" t="s">
+        <v>191</v>
+      </c>
+      <c r="G102" s="91" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B103" s="92">
+      <c r="B103" s="89">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="C103" s="69" t="s">
-        <v>155</v>
-      </c>
-      <c r="D103" s="70">
-        <v>1</v>
-      </c>
-      <c r="E103" s="69" t="s">
-        <v>34</v>
-      </c>
-      <c r="F103" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="G103" s="98" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B104" s="92">
+      <c r="C103" s="65" t="s">
+        <v>250</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E103" s="65" t="s">
+        <v>254</v>
+      </c>
+      <c r="F103" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="G103" s="94" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B104" s="89">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="C104" s="64" t="s">
-        <v>253</v>
-      </c>
-      <c r="D104" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="E104" s="64" t="s">
+      <c r="C104" s="66" t="s">
+        <v>155</v>
+      </c>
+      <c r="D104" s="67">
+        <v>1</v>
+      </c>
+      <c r="E104" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="F104" s="81" t="s">
-        <v>260</v>
-      </c>
-      <c r="G104" s="94" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B105" s="92">
+      <c r="F104" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="G104" s="95" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B105" s="89">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="C105" s="60" t="s">
-        <v>191</v>
-      </c>
-      <c r="D105" s="58" t="s">
+      <c r="C105" s="61" t="s">
+        <v>249</v>
+      </c>
+      <c r="D105" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="E105" s="60" t="s">
-        <v>192</v>
-      </c>
-      <c r="F105" s="62" t="s">
-        <v>250</v>
-      </c>
-      <c r="G105" s="93" t="s">
-        <v>252</v>
+      <c r="E105" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F105" s="78" t="s">
+        <v>255</v>
+      </c>
+      <c r="G105" s="91" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B106" s="92">
+      <c r="B106" s="89">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
-      <c r="C106" s="60" t="s">
-        <v>251</v>
-      </c>
-      <c r="D106" s="58" t="s">
+      <c r="C106" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="D106" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="E106" s="60" t="s">
-        <v>250</v>
-      </c>
-      <c r="F106" s="62" t="s">
-        <v>34</v>
-      </c>
-      <c r="G106" s="93" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B107" s="92">
+      <c r="E106" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="F106" s="59" t="s">
+        <v>246</v>
+      </c>
+      <c r="G106" s="90" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B107" s="89">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
-      <c r="C107" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="D107" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E107" s="71" t="s">
-        <v>119</v>
-      </c>
-      <c r="F107" s="84" t="s">
-        <v>256</v>
-      </c>
-      <c r="G107" s="99" t="s">
-        <v>138</v>
+      <c r="C107" s="57" t="s">
+        <v>247</v>
+      </c>
+      <c r="D107" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E107" s="57" t="s">
+        <v>246</v>
+      </c>
+      <c r="F107" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="G107" s="90" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B108" s="92">
+      <c r="B108" s="89">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
-      <c r="C108" s="78" t="s">
-        <v>284</v>
-      </c>
-      <c r="D108" s="79" t="s">
-        <v>294</v>
-      </c>
-      <c r="E108" s="88" t="s">
-        <v>272</v>
-      </c>
-      <c r="F108" s="89" t="s">
-        <v>303</v>
-      </c>
-      <c r="G108" s="102" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B109" s="92">
+      <c r="C108" s="57" t="s">
+        <v>377</v>
+      </c>
+      <c r="D108" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" s="126" t="s">
+        <v>368</v>
+      </c>
+      <c r="F108" s="126" t="s">
+        <v>35</v>
+      </c>
+      <c r="G108" s="98" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B109" s="89">
         <f>IF(C109="","",B108+1)</f>
         <v>90</v>
       </c>
-      <c r="C109" s="75" t="s">
-        <v>285</v>
-      </c>
-      <c r="D109" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E109" s="77" t="s">
-        <v>272</v>
-      </c>
-      <c r="F109" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="G109" s="101" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B110" s="92">
+      <c r="C109" s="57" t="s">
+        <v>362</v>
+      </c>
+      <c r="D109" s="58">
+        <v>1</v>
+      </c>
+      <c r="E109" s="57" t="s">
+        <v>228</v>
+      </c>
+      <c r="F109" s="71" t="s">
+        <v>252</v>
+      </c>
+      <c r="G109" s="90" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B110" s="89">
         <f>IF(C110="","",B109+1)</f>
         <v>91</v>
       </c>
-      <c r="C110" s="60" t="s">
-        <v>182</v>
-      </c>
-      <c r="D110" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="E110" s="74" t="s">
+      <c r="C110" s="68" t="s">
+        <v>135</v>
+      </c>
+      <c r="D110" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E110" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="F110" s="74" t="s">
-        <v>206</v>
-      </c>
-      <c r="G110" s="93" t="s">
-        <v>183</v>
+      <c r="F110" s="81" t="s">
+        <v>370</v>
+      </c>
+      <c r="G110" s="96" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B111" s="92">
+      <c r="B111" s="89">
         <f>IF(C111="","",B110+1)</f>
         <v>92</v>
       </c>
-      <c r="C111" s="60" t="s">
-        <v>207</v>
-      </c>
-      <c r="D111" s="61">
-        <v>1</v>
-      </c>
-      <c r="E111" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="F111" s="74" t="s">
-        <v>197</v>
-      </c>
-      <c r="G111" s="93" t="s">
-        <v>359</v>
+      <c r="C111" s="75" t="s">
+        <v>278</v>
+      </c>
+      <c r="D111" s="76" t="s">
+        <v>288</v>
+      </c>
+      <c r="E111" s="85" t="s">
+        <v>266</v>
+      </c>
+      <c r="F111" s="86" t="s">
+        <v>297</v>
+      </c>
+      <c r="G111" s="99" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B112" s="92">
+      <c r="B112" s="89">
         <f>IF(C112="","",B111+1)</f>
         <v>93</v>
       </c>
-      <c r="C112" s="60" t="s">
-        <v>236</v>
-      </c>
-      <c r="D112" s="61">
-        <v>2</v>
-      </c>
-      <c r="E112" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="F112" s="62" t="s">
-        <v>120</v>
-      </c>
-      <c r="G112" s="93" t="s">
-        <v>237</v>
+      <c r="C112" s="72" t="s">
+        <v>279</v>
+      </c>
+      <c r="D112" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="E112" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="F112" s="74" t="s">
+        <v>267</v>
+      </c>
+      <c r="G112" s="98" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B113" s="92">
+      <c r="B113" s="89">
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="C113" s="75" t="s">
-        <v>286</v>
-      </c>
-      <c r="D113" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E113" s="77" t="s">
-        <v>272</v>
-      </c>
-      <c r="F113" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="G113" s="101" t="s">
-        <v>324</v>
+      <c r="C113" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="D113" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E113" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="F113" s="71" t="s">
+        <v>203</v>
+      </c>
+      <c r="G113" s="90" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B114" s="92">
+      <c r="B114" s="89">
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
-      <c r="C114" s="71" t="s">
-        <v>131</v>
-      </c>
-      <c r="D114" s="72">
+      <c r="C114" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="D114" s="58">
         <v>1</v>
       </c>
-      <c r="E114" s="71" t="s">
+      <c r="E114" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="F114" s="85" t="s">
-        <v>13</v>
-      </c>
-      <c r="G114" s="99" t="s">
-        <v>133</v>
+      <c r="F114" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="G114" s="90" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B115" s="92">
+      <c r="B115" s="89">
         <f>IF(C115="","",B114+1)</f>
         <v>96</v>
       </c>
-      <c r="C115" s="75" t="s">
-        <v>287</v>
-      </c>
-      <c r="D115" s="58" t="s">
-        <v>298</v>
-      </c>
-      <c r="E115" s="77" t="s">
-        <v>272</v>
-      </c>
-      <c r="F115" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="G115" s="101" t="s">
-        <v>325</v>
+      <c r="C115" s="57" t="s">
+        <v>232</v>
+      </c>
+      <c r="D115" s="58">
+        <v>2</v>
+      </c>
+      <c r="E115" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="F115" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G115" s="90" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B116" s="92">
+      <c r="B116" s="89">
         <f>IF(C116="","",B115+1)</f>
         <v>97</v>
       </c>
-      <c r="C116" s="60" t="s">
-        <v>146</v>
-      </c>
-      <c r="D116" s="61">
-        <v>1</v>
-      </c>
-      <c r="E116" s="62" t="s">
-        <v>119</v>
-      </c>
-      <c r="F116" s="62" t="s">
-        <v>120</v>
-      </c>
-      <c r="G116" s="93" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="117" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B117" s="92">
+      <c r="C116" s="72" t="s">
+        <v>280</v>
+      </c>
+      <c r="D116" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="E116" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="F116" s="74" t="s">
+        <v>267</v>
+      </c>
+      <c r="G116" s="98" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B117" s="89">
         <f t="shared" ref="B117:B141" si="3">IF(C117="","",B116+1)</f>
         <v>98</v>
       </c>
-      <c r="C117" s="71" t="s">
-        <v>132</v>
-      </c>
-      <c r="D117" s="72">
+      <c r="C117" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="D117" s="69">
         <v>1</v>
       </c>
-      <c r="E117" s="71" t="s">
+      <c r="E117" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="F117" s="86" t="s">
-        <v>64</v>
-      </c>
-      <c r="G117" s="99" t="s">
-        <v>134</v>
+      <c r="F117" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="G117" s="96" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="118" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B118" s="92">
+      <c r="B118" s="89">
         <f t="shared" si="3"/>
         <v>99</v>
       </c>
-      <c r="C118" s="80" t="s">
-        <v>288</v>
-      </c>
-      <c r="D118" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="E118" s="90" t="s">
-        <v>272</v>
-      </c>
-      <c r="F118" s="91" t="s">
-        <v>304</v>
-      </c>
-      <c r="G118" s="103" t="s">
-        <v>326</v>
+      <c r="C118" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="D118" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="E118" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="F118" s="74" t="s">
+        <v>267</v>
+      </c>
+      <c r="G118" s="98" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="119" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B119" s="92">
+      <c r="B119" s="89">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="C119" s="60" t="s">
-        <v>242</v>
-      </c>
-      <c r="D119" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="E119" s="62" t="s">
+      <c r="C119" s="57" t="s">
+        <v>146</v>
+      </c>
+      <c r="D119" s="58">
+        <v>1</v>
+      </c>
+      <c r="E119" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="F119" s="62" t="s">
+      <c r="F119" s="59" t="s">
         <v>120</v>
       </c>
-      <c r="G119" s="93" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="120" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B120" s="92">
+      <c r="G119" s="90" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B120" s="89">
         <f t="shared" si="3"/>
         <v>101</v>
       </c>
-      <c r="C120" s="66" t="s">
-        <v>139</v>
-      </c>
-      <c r="D120" s="67" t="s">
-        <v>19</v>
-      </c>
-      <c r="E120" s="66" t="s">
+      <c r="C120" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="D120" s="69">
+        <v>1</v>
+      </c>
+      <c r="E120" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="F120" s="87" t="s">
-        <v>197</v>
+      <c r="F120" s="83" t="s">
+        <v>64</v>
       </c>
       <c r="G120" s="96" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="121" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B121" s="92">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B121" s="89">
         <f t="shared" si="3"/>
         <v>102</v>
       </c>
-      <c r="C121" s="60" t="s">
-        <v>189</v>
-      </c>
-      <c r="D121" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="E121" s="60" t="s">
-        <v>119</v>
-      </c>
-      <c r="F121" s="74" t="s">
-        <v>201</v>
-      </c>
-      <c r="G121" s="93" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="122" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B122" s="92">
+      <c r="C121" s="77" t="s">
+        <v>282</v>
+      </c>
+      <c r="D121" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="E121" s="87" t="s">
+        <v>266</v>
+      </c>
+      <c r="F121" s="88" t="s">
+        <v>298</v>
+      </c>
+      <c r="G121" s="100" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B122" s="89">
         <f t="shared" si="3"/>
         <v>103</v>
       </c>
-      <c r="C122" s="60" t="s">
-        <v>194</v>
-      </c>
-      <c r="D122" s="61">
-        <v>1</v>
-      </c>
-      <c r="E122" s="62" t="s">
+      <c r="C122" s="57" t="s">
+        <v>238</v>
+      </c>
+      <c r="D122" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E122" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="F122" s="74" t="s">
-        <v>195</v>
-      </c>
-      <c r="G122" s="93" t="s">
-        <v>177</v>
+      <c r="F122" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="G122" s="90" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B123" s="92">
+      <c r="B123" s="89">
         <f t="shared" si="3"/>
         <v>104</v>
       </c>
-      <c r="C123" s="71" t="s">
-        <v>213</v>
-      </c>
-      <c r="D123" s="18" t="s">
+      <c r="C123" s="63" t="s">
+        <v>139</v>
+      </c>
+      <c r="D123" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="E123" s="73" t="s">
-        <v>197</v>
-      </c>
-      <c r="F123" s="85" t="s">
-        <v>16</v>
-      </c>
-      <c r="G123" s="99" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="124" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B124" s="92">
+      <c r="E123" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="F123" s="84" t="s">
+        <v>196</v>
+      </c>
+      <c r="G123" s="93" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B124" s="89">
         <f t="shared" si="3"/>
         <v>105</v>
       </c>
-      <c r="C124" s="60" t="s">
-        <v>215</v>
-      </c>
-      <c r="D124" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E124" s="60" t="s">
+      <c r="C124" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="D124" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E124" s="57" t="s">
         <v>119</v>
       </c>
-      <c r="F124" s="60" t="s">
-        <v>197</v>
-      </c>
-      <c r="G124" s="93" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="125" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B125" s="92">
+      <c r="F124" s="71" t="s">
+        <v>374</v>
+      </c>
+      <c r="G124" s="90" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="125" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B125" s="89">
         <f t="shared" si="3"/>
         <v>106</v>
       </c>
-      <c r="C125" s="60" t="s">
-        <v>150</v>
-      </c>
-      <c r="D125" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E125" s="60" t="s">
-        <v>120</v>
-      </c>
-      <c r="F125" s="74" t="s">
-        <v>360</v>
-      </c>
-      <c r="G125" s="93" t="s">
-        <v>151</v>
+      <c r="C125" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="D125" s="58">
+        <v>1</v>
+      </c>
+      <c r="E125" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="F125" s="71" t="s">
+        <v>194</v>
+      </c>
+      <c r="G125" s="90" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="126" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B126" s="92">
+      <c r="B126" s="89">
         <f t="shared" si="3"/>
         <v>107</v>
       </c>
-      <c r="C126" s="75" t="s">
-        <v>289</v>
-      </c>
-      <c r="D126" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E126" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="F126" s="77" t="s">
-        <v>290</v>
-      </c>
-      <c r="G126" s="101" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="127" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B127" s="92">
+      <c r="C126" s="68" t="s">
+        <v>210</v>
+      </c>
+      <c r="D126" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" s="70" t="s">
+        <v>196</v>
+      </c>
+      <c r="F126" s="82" t="s">
+        <v>16</v>
+      </c>
+      <c r="G126" s="96" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B127" s="89">
         <f t="shared" si="3"/>
         <v>108</v>
       </c>
-      <c r="C127" s="75" t="s">
-        <v>290</v>
-      </c>
-      <c r="D127" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E127" s="77" t="s">
-        <v>305</v>
-      </c>
-      <c r="F127" s="77" t="s">
-        <v>306</v>
-      </c>
-      <c r="G127" s="101" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="128" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B128" s="92">
+      <c r="C127" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="D127" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="F127" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="G127" s="90" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B128" s="89">
         <f t="shared" si="3"/>
         <v>109</v>
       </c>
-      <c r="C128" s="60" t="s">
-        <v>365</v>
-      </c>
-      <c r="D128" s="61">
-        <v>1</v>
-      </c>
-      <c r="E128" s="62" t="s">
+      <c r="C128" s="57" t="s">
+        <v>150</v>
+      </c>
+      <c r="D128" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="F128" s="62" t="s">
-        <v>69</v>
-      </c>
-      <c r="G128" s="93" t="s">
-        <v>149</v>
+      <c r="F128" s="71" t="s">
+        <v>353</v>
+      </c>
+      <c r="G128" s="90" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="129" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B129" s="92">
+      <c r="B129" s="89">
         <f t="shared" si="3"/>
         <v>110</v>
       </c>
-      <c r="C129" s="75" t="s">
-        <v>291</v>
+      <c r="C129" s="72" t="s">
+        <v>283</v>
       </c>
       <c r="D129" s="58" t="s">
-        <v>307</v>
-      </c>
-      <c r="E129" s="77" t="s">
-        <v>308</v>
-      </c>
-      <c r="F129" s="77" t="s">
-        <v>309</v>
-      </c>
-      <c r="G129" s="101" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="130" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B130" s="92">
+        <v>288</v>
+      </c>
+      <c r="E129" s="74" t="s">
+        <v>267</v>
+      </c>
+      <c r="F129" s="74" t="s">
+        <v>284</v>
+      </c>
+      <c r="G129" s="98" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B130" s="89">
         <f t="shared" si="3"/>
         <v>111</v>
       </c>
-      <c r="C130" s="60" t="s">
-        <v>361</v>
-      </c>
-      <c r="D130" s="61">
-        <v>2</v>
-      </c>
-      <c r="E130" s="62" t="s">
-        <v>120</v>
+      <c r="C130" s="72" t="s">
+        <v>284</v>
+      </c>
+      <c r="D130" s="58" t="s">
+        <v>288</v>
+      </c>
+      <c r="E130" s="74" t="s">
+        <v>299</v>
       </c>
       <c r="F130" s="74" t="s">
-        <v>362</v>
-      </c>
-      <c r="G130" s="93" t="s">
-        <v>238</v>
+        <v>300</v>
+      </c>
+      <c r="G130" s="98" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="131" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B131" s="92">
+      <c r="B131" s="89">
         <f t="shared" si="3"/>
         <v>112</v>
       </c>
-      <c r="C131" s="75" t="s">
-        <v>292</v>
-      </c>
-      <c r="D131" s="61" t="s">
-        <v>294</v>
-      </c>
-      <c r="E131" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="F131" s="77" t="s">
-        <v>308</v>
-      </c>
-      <c r="G131" s="101" t="s">
-        <v>330</v>
+      <c r="C131" s="57" t="s">
+        <v>357</v>
+      </c>
+      <c r="D131" s="58">
+        <v>1</v>
+      </c>
+      <c r="E131" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="F131" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="G131" s="90" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="132" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B132" s="92">
+      <c r="B132" s="89">
         <f t="shared" si="3"/>
         <v>113</v>
       </c>
-      <c r="C132" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="D132" s="58" t="s">
-        <v>298</v>
-      </c>
-      <c r="E132" s="77" t="s">
-        <v>273</v>
-      </c>
-      <c r="F132" s="77" t="s">
-        <v>308</v>
-      </c>
-      <c r="G132" s="101" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="133" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B133" s="92">
+      <c r="C132" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="D132" s="55" t="s">
+        <v>301</v>
+      </c>
+      <c r="E132" s="74" t="s">
+        <v>302</v>
+      </c>
+      <c r="F132" s="74" t="s">
+        <v>303</v>
+      </c>
+      <c r="G132" s="98" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B133" s="89">
         <f t="shared" si="3"/>
         <v>114</v>
       </c>
-      <c r="C133" s="60" t="s">
-        <v>167</v>
-      </c>
-      <c r="D133" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E133" s="60" t="s">
-        <v>69</v>
-      </c>
-      <c r="F133" s="74" t="s">
-        <v>366</v>
-      </c>
-      <c r="G133" s="93" t="s">
-        <v>168</v>
+      <c r="C133" s="57" t="s">
+        <v>354</v>
+      </c>
+      <c r="D133" s="58">
+        <v>2</v>
+      </c>
+      <c r="E133" s="59" t="s">
+        <v>120</v>
+      </c>
+      <c r="F133" s="71" t="s">
+        <v>379</v>
+      </c>
+      <c r="G133" s="90" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="134" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B134" s="92">
+      <c r="B134" s="89">
         <f t="shared" si="3"/>
         <v>115</v>
       </c>
-      <c r="C134" s="60" t="s">
-        <v>243</v>
+      <c r="C134" s="72" t="s">
+        <v>286</v>
       </c>
       <c r="D134" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="E134" s="62" t="s">
-        <v>120</v>
+        <v>288</v>
+      </c>
+      <c r="E134" s="74" t="s">
+        <v>267</v>
       </c>
       <c r="F134" s="74" t="s">
-        <v>69</v>
-      </c>
-      <c r="G134" s="93" t="s">
-        <v>246</v>
+        <v>302</v>
+      </c>
+      <c r="G134" s="98" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B135" s="92">
+      <c r="B135" s="89">
         <f t="shared" si="3"/>
         <v>116</v>
       </c>
-      <c r="C135" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="D135" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="E135" s="62" t="s">
-        <v>240</v>
+      <c r="C135" s="72" t="s">
+        <v>287</v>
+      </c>
+      <c r="D135" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="E135" s="74" t="s">
+        <v>267</v>
       </c>
       <c r="F135" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="G135" s="93" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="136" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B136" s="92">
+        <v>302</v>
+      </c>
+      <c r="G135" s="98" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B136" s="89">
         <f t="shared" si="3"/>
         <v>117</v>
       </c>
-      <c r="C136" s="60" t="s">
-        <v>184</v>
-      </c>
-      <c r="D136" s="58" t="s">
-        <v>55</v>
-      </c>
-      <c r="E136" s="60" t="s">
-        <v>120</v>
-      </c>
-      <c r="F136" s="74" t="s">
-        <v>367</v>
-      </c>
-      <c r="G136" s="93" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="137" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B137" s="104">
+      <c r="C136" s="57" t="s">
+        <v>167</v>
+      </c>
+      <c r="D136" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E136" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="F136" s="71" t="s">
+        <v>371</v>
+      </c>
+      <c r="G136" s="90" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B137" s="121">
         <f t="shared" si="3"/>
         <v>118</v>
       </c>
-      <c r="C137" s="123" t="s">
-        <v>364</v>
-      </c>
-      <c r="D137" s="124">
+      <c r="C137" s="122" t="s">
+        <v>239</v>
+      </c>
+      <c r="D137" s="127" t="s">
+        <v>20</v>
+      </c>
+      <c r="E137" s="123" t="s">
+        <v>120</v>
+      </c>
+      <c r="F137" s="124" t="s">
+        <v>69</v>
+      </c>
+      <c r="G137" s="125" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B138" s="89">
+        <f t="shared" si="3"/>
+        <v>119</v>
+      </c>
+      <c r="C138" s="57" t="s">
+        <v>235</v>
+      </c>
+      <c r="D138" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E138" s="59" t="s">
+        <v>236</v>
+      </c>
+      <c r="F138" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="G138" s="90" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="139" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B139" s="89">
+        <f t="shared" si="3"/>
+        <v>120</v>
+      </c>
+      <c r="C139" s="57" t="s">
+        <v>183</v>
+      </c>
+      <c r="D139" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E139" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="F139" s="71" t="s">
+        <v>375</v>
+      </c>
+      <c r="G139" s="90" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="140" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B140" s="101">
+        <f t="shared" si="3"/>
+        <v>121</v>
+      </c>
+      <c r="C140" s="116" t="s">
+        <v>356</v>
+      </c>
+      <c r="D140" s="117">
         <v>1</v>
       </c>
-      <c r="E137" s="125" t="s">
+      <c r="E140" s="118" t="s">
         <v>120</v>
       </c>
-      <c r="F137" s="126" t="s">
-        <v>363</v>
-      </c>
-      <c r="G137" s="127" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B138" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="C138"/>
-      <c r="D138"/>
-      <c r="E138" s="57"/>
-      <c r="F138" s="57"/>
-      <c r="G138" s="57"/>
-    </row>
-    <row r="139" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B139" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="C139"/>
-      <c r="D139"/>
-      <c r="E139" s="57"/>
-      <c r="F139" s="57"/>
-      <c r="G139" s="57"/>
-    </row>
-    <row r="140" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B140" s="21" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="C140"/>
-      <c r="D140"/>
-      <c r="E140" s="57"/>
-      <c r="F140" s="57"/>
-      <c r="G140" s="57"/>
+      <c r="F140" s="119" t="s">
+        <v>355</v>
+      </c>
+      <c r="G140" s="120" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="141" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B141" s="21" t="str">
@@ -5603,9 +5693,9 @@
       </c>
       <c r="C141"/>
       <c r="D141"/>
-      <c r="E141" s="57"/>
-      <c r="F141" s="57"/>
-      <c r="G141" s="57"/>
+      <c r="E141" s="54"/>
+      <c r="F141" s="54"/>
+      <c r="G141" s="54"/>
     </row>
   </sheetData>
   <autoFilter ref="C19:G140" xr:uid="{00000000-0009-0000-0000-000000000000}">

--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418539D3-F409-41F5-B301-D138C163D561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D16C1C-4E28-4F74-A8C8-EA60B194CC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -808,11 +808,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>u_mem_wb_bridge
-u_alu_forwarding_unit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>u_alu_src_mux</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1428,12 +1423,6 @@
   </si>
   <si>
     <t>w_wb_jump</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>u_registers
-u_wdata_forwarding_unit
-u_alu_forwarding_unit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1573,6 +1562,19 @@
   <si>
     <t>w_wb_ctr_link_ret_addr
 u_regdst_jal_mux</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_mem_wb_bridge
+u_alu_forwarding_unit
+u_jump_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_registers
+u_wdata_forwarding_unit
+u_alu_forwarding_unit
+u_jump_forwarding_unit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2826,7 +2828,7 @@
     <row r="1" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="129" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C2" s="130"/>
       <c r="D2" s="130"/>
@@ -3059,10 +3061,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="51" t="s">
+        <v>255</v>
+      </c>
+      <c r="D14" s="37" t="s">
         <v>256</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>257</v>
       </c>
       <c r="E14" s="53" t="s">
         <v>22</v>
@@ -3117,7 +3119,7 @@
     <row r="17" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="132" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C18" s="133"/>
       <c r="D18" s="133"/>
@@ -3178,7 +3180,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="57" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F21" s="71" t="s">
         <v>65</v>
@@ -3193,19 +3195,19 @@
         <v>3</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D22" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E22" s="57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F22" s="71" t="s">
         <v>65</v>
       </c>
       <c r="G22" s="90" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
@@ -3214,19 +3216,19 @@
         <v>4</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D23" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="57" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F23" s="71" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G23" s="90" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -3235,7 +3237,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D24" s="58">
         <v>1</v>
@@ -3244,10 +3246,10 @@
         <v>67</v>
       </c>
       <c r="F24" s="71" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G24" s="90" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
@@ -3286,7 +3288,7 @@
         <v>67</v>
       </c>
       <c r="F26" s="71" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G26" s="90" t="s">
         <v>72</v>
@@ -3307,7 +3309,7 @@
         <v>118</v>
       </c>
       <c r="F27" s="59" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G27" s="90" t="s">
         <v>126</v>
@@ -3340,19 +3342,19 @@
         <v>10</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D29" s="73" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E29" s="74" t="s">
         <v>116</v>
       </c>
       <c r="F29" s="71" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G29" s="97" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3361,19 +3363,19 @@
         <v>11</v>
       </c>
       <c r="C30" s="72" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D30" s="58" t="s">
+        <v>287</v>
+      </c>
+      <c r="E30" s="74" t="s">
         <v>288</v>
       </c>
-      <c r="E30" s="74" t="s">
+      <c r="F30" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="F30" s="74" t="s">
-        <v>290</v>
-      </c>
       <c r="G30" s="98" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3382,19 +3384,19 @@
         <v>12</v>
       </c>
       <c r="C31" s="72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D31" s="58" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E31" s="74" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F31" s="74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G31" s="98" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3403,19 +3405,19 @@
         <v>13</v>
       </c>
       <c r="C32" s="72" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D32" s="58" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E32" s="74" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F32" s="74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G32" s="98" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3424,19 +3426,19 @@
         <v>14</v>
       </c>
       <c r="C33" s="72" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D33" s="58" t="s">
+        <v>287</v>
+      </c>
+      <c r="E33" s="74" t="s">
         <v>288</v>
       </c>
-      <c r="E33" s="74" t="s">
+      <c r="F33" s="74" t="s">
         <v>289</v>
       </c>
-      <c r="F33" s="74" t="s">
-        <v>290</v>
-      </c>
       <c r="G33" s="98" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
@@ -3454,7 +3456,7 @@
         <v>118</v>
       </c>
       <c r="F34" s="71" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G34" s="90" t="s">
         <v>142</v>
@@ -3478,7 +3480,7 @@
         <v>52</v>
       </c>
       <c r="G35" s="90" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
@@ -3529,19 +3531,19 @@
         <v>19</v>
       </c>
       <c r="C38" s="57" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D38" s="58">
         <v>1</v>
       </c>
       <c r="E38" s="71" t="s">
+        <v>331</v>
+      </c>
+      <c r="F38" s="71" t="s">
         <v>332</v>
       </c>
-      <c r="F38" s="71" t="s">
+      <c r="G38" s="90" t="s">
         <v>333</v>
-      </c>
-      <c r="G38" s="90" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -3550,19 +3552,19 @@
         <v>20</v>
       </c>
       <c r="C39" s="57" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D39" s="58">
         <v>1</v>
       </c>
       <c r="E39" s="74" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F39" s="71" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G39" s="90" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -3580,7 +3582,7 @@
         <v>118</v>
       </c>
       <c r="F40" s="71" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G40" s="90" t="s">
         <v>144</v>
@@ -3601,7 +3603,7 @@
         <v>116</v>
       </c>
       <c r="F41" s="59" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G41" s="90" t="s">
         <v>124</v>
@@ -3622,7 +3624,7 @@
         <v>118</v>
       </c>
       <c r="F42" s="71" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="G42" s="90" t="s">
         <v>186</v>
@@ -3643,7 +3645,7 @@
         <v>118</v>
       </c>
       <c r="F43" s="71" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G43" s="90" t="s">
         <v>179</v>
@@ -3655,19 +3657,19 @@
         <v>25</v>
       </c>
       <c r="C44" s="57" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D44" s="58">
         <v>1</v>
       </c>
       <c r="E44" s="74" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F44" s="71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G44" s="90" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
@@ -3739,19 +3741,19 @@
         <v>29</v>
       </c>
       <c r="C48" s="72" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D48" s="58" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E48" s="74" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F48" s="74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G48" s="98" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
@@ -3781,19 +3783,19 @@
         <v>31</v>
       </c>
       <c r="C50" s="72" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D50" s="58" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E50" s="74" t="s">
         <v>116</v>
       </c>
       <c r="F50" s="74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G50" s="98" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3811,7 +3813,7 @@
         <v>118</v>
       </c>
       <c r="F51" s="78" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G51" s="90" t="s">
         <v>129</v>
@@ -3823,19 +3825,19 @@
         <v>33</v>
       </c>
       <c r="C52" s="72" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D52" s="55" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E52" s="74" t="s">
         <v>116</v>
       </c>
       <c r="F52" s="74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G52" s="98" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
@@ -3886,19 +3888,19 @@
         <v>36</v>
       </c>
       <c r="C55" s="72" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D55" s="55" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E55" s="74" t="s">
         <v>116</v>
       </c>
       <c r="F55" s="74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G55" s="98" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="56" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -3907,7 +3909,7 @@
         <v>37</v>
       </c>
       <c r="C56" s="57" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D56" s="55" t="s">
         <v>20</v>
@@ -3916,7 +3918,7 @@
         <v>116</v>
       </c>
       <c r="F56" s="71" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G56" s="91" t="s">
         <v>79</v>
@@ -3937,7 +3939,7 @@
         <v>116</v>
       </c>
       <c r="F57" s="71" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G57" s="90" t="s">
         <v>104</v>
@@ -3958,7 +3960,7 @@
         <v>116</v>
       </c>
       <c r="F58" s="79" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G58" s="93" t="s">
         <v>105</v>
@@ -3970,7 +3972,7 @@
         <v>40</v>
       </c>
       <c r="C59" s="57" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D59" s="55" t="s">
         <v>55</v>
@@ -3979,10 +3981,10 @@
         <v>118</v>
       </c>
       <c r="F59" s="71" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G59" s="90" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
@@ -4075,19 +4077,19 @@
         <v>45</v>
       </c>
       <c r="C64" s="57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D64" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E64" s="57" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F64" s="57" t="s">
         <v>119</v>
       </c>
       <c r="G64" s="90" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
@@ -4096,19 +4098,19 @@
         <v>46</v>
       </c>
       <c r="C65" s="57" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D65" s="58">
         <v>1</v>
       </c>
       <c r="E65" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="F65" s="59" t="s">
         <v>213</v>
       </c>
-      <c r="F65" s="59" t="s">
-        <v>214</v>
-      </c>
       <c r="G65" s="90" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
@@ -4117,19 +4119,19 @@
         <v>47</v>
       </c>
       <c r="C66" s="57" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D66" s="58">
         <v>1</v>
       </c>
       <c r="E66" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="F66" s="59" t="s">
         <v>213</v>
       </c>
-      <c r="F66" s="59" t="s">
-        <v>214</v>
-      </c>
       <c r="G66" s="90" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
@@ -4138,19 +4140,19 @@
         <v>48</v>
       </c>
       <c r="C67" s="57" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D67" s="58">
         <v>1</v>
       </c>
       <c r="E67" s="59" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F67" s="59" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G67" s="90" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
@@ -4159,19 +4161,19 @@
         <v>49</v>
       </c>
       <c r="C68" s="57" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D68" s="58">
         <v>1</v>
       </c>
       <c r="E68" s="59" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F68" s="59" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G68" s="90" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
@@ -4180,19 +4182,19 @@
         <v>50</v>
       </c>
       <c r="C69" s="57" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D69" s="58">
         <v>1</v>
       </c>
       <c r="E69" s="126" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F69" s="126" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G69" s="98" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
@@ -4201,19 +4203,19 @@
         <v>51</v>
       </c>
       <c r="C70" s="57" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D70" s="58">
         <v>1</v>
       </c>
       <c r="E70" s="126" t="s">
+        <v>363</v>
+      </c>
+      <c r="F70" s="126" t="s">
+        <v>366</v>
+      </c>
+      <c r="G70" s="98" t="s">
         <v>365</v>
-      </c>
-      <c r="F70" s="126" t="s">
-        <v>368</v>
-      </c>
-      <c r="G70" s="98" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
@@ -4222,19 +4224,19 @@
         <v>52</v>
       </c>
       <c r="C71" s="57" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D71" s="56">
         <v>1</v>
       </c>
       <c r="E71" s="57" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F71" s="59" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G71" s="90" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
@@ -4264,19 +4266,19 @@
         <v>54</v>
       </c>
       <c r="C73" s="72" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D73" s="58" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E73" s="74" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F73" s="74" t="s">
         <v>116</v>
       </c>
       <c r="G73" s="98" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
@@ -4327,7 +4329,7 @@
         <v>57</v>
       </c>
       <c r="C76" s="57" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D76" s="58">
         <v>1</v>
@@ -4378,7 +4380,7 @@
         <v>43</v>
       </c>
       <c r="F78" s="71" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G78" s="90" t="s">
         <v>122</v>
@@ -4462,7 +4464,7 @@
         <v>43</v>
       </c>
       <c r="F82" s="71" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G82" s="90" t="s">
         <v>187</v>
@@ -4483,7 +4485,7 @@
         <v>43</v>
       </c>
       <c r="F83" s="71" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G83" s="90" t="s">
         <v>179</v>
@@ -4516,7 +4518,7 @@
         <v>66</v>
       </c>
       <c r="C85" s="57" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D85" s="55" t="s">
         <v>19</v>
@@ -4528,7 +4530,7 @@
         <v>43</v>
       </c>
       <c r="G85" s="90" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
@@ -4537,7 +4539,7 @@
         <v>67</v>
       </c>
       <c r="C86" s="57" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D86" s="58">
         <v>2</v>
@@ -4564,7 +4566,7 @@
         <v>20</v>
       </c>
       <c r="E87" s="74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F87" s="59" t="s">
         <v>118</v>
@@ -4579,19 +4581,19 @@
         <v>69</v>
       </c>
       <c r="C88" s="72" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D88" s="58" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E88" s="74" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F88" s="74" t="s">
         <v>116</v>
       </c>
       <c r="G88" s="98" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
@@ -4621,19 +4623,19 @@
         <v>71</v>
       </c>
       <c r="C90" s="57" t="s">
+        <v>257</v>
+      </c>
+      <c r="D90" s="55" t="s">
         <v>258</v>
       </c>
-      <c r="D90" s="55" t="s">
+      <c r="E90" s="57" t="s">
         <v>259</v>
       </c>
-      <c r="E90" s="57" t="s">
+      <c r="F90" s="59" t="s">
         <v>260</v>
       </c>
-      <c r="F90" s="59" t="s">
+      <c r="G90" s="90" t="s">
         <v>261</v>
-      </c>
-      <c r="G90" s="90" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
@@ -4684,19 +4686,19 @@
         <v>74</v>
       </c>
       <c r="C93" s="57" t="s">
+        <v>262</v>
+      </c>
+      <c r="D93" s="55" t="s">
+        <v>258</v>
+      </c>
+      <c r="E93" s="57" t="s">
+        <v>259</v>
+      </c>
+      <c r="F93" s="59" t="s">
         <v>263</v>
       </c>
-      <c r="D93" s="55" t="s">
-        <v>259</v>
-      </c>
-      <c r="E93" s="57" t="s">
-        <v>260</v>
-      </c>
-      <c r="F93" s="59" t="s">
+      <c r="G93" s="90" t="s">
         <v>264</v>
-      </c>
-      <c r="G93" s="90" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="94" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -4705,7 +4707,7 @@
         <v>75</v>
       </c>
       <c r="C94" s="57" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D94" s="55" t="s">
         <v>20</v>
@@ -4714,10 +4716,10 @@
         <v>117</v>
       </c>
       <c r="F94" s="71" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G94" s="91" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
@@ -4768,19 +4770,19 @@
         <v>78</v>
       </c>
       <c r="C97" s="72" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D97" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="E97" s="74" t="s">
         <v>294</v>
       </c>
-      <c r="E97" s="74" t="s">
+      <c r="F97" s="74" t="s">
         <v>295</v>
       </c>
-      <c r="F97" s="74" t="s">
-        <v>296</v>
-      </c>
       <c r="G97" s="98" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.3">
@@ -4894,13 +4896,13 @@
         <v>84</v>
       </c>
       <c r="C103" s="65" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D103" s="12" t="s">
         <v>20</v>
       </c>
       <c r="E103" s="65" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F103" s="80" t="s">
         <v>11</v>
@@ -4936,7 +4938,7 @@
         <v>86</v>
       </c>
       <c r="C105" s="61" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D105" s="55" t="s">
         <v>20</v>
@@ -4945,10 +4947,10 @@
         <v>34</v>
       </c>
       <c r="F105" s="78" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G105" s="91" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.3">
@@ -4966,10 +4968,10 @@
         <v>191</v>
       </c>
       <c r="F106" s="59" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G106" s="90" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.3">
@@ -4978,13 +4980,13 @@
         <v>88</v>
       </c>
       <c r="C107" s="57" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D107" s="55" t="s">
         <v>20</v>
       </c>
       <c r="E107" s="57" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F107" s="59" t="s">
         <v>34</v>
@@ -4999,19 +5001,19 @@
         <v>89</v>
       </c>
       <c r="C108" s="57" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D108" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E108" s="126" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F108" s="126" t="s">
         <v>35</v>
       </c>
       <c r="G108" s="98" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="109" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -5020,19 +5022,19 @@
         <v>90</v>
       </c>
       <c r="C109" s="57" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D109" s="58">
         <v>1</v>
       </c>
       <c r="E109" s="57" t="s">
+        <v>227</v>
+      </c>
+      <c r="F109" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="G109" s="90" t="s">
         <v>228</v>
-      </c>
-      <c r="F109" s="71" t="s">
-        <v>252</v>
-      </c>
-      <c r="G109" s="90" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="110" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
@@ -5050,7 +5052,7 @@
         <v>119</v>
       </c>
       <c r="F110" s="81" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G110" s="96" t="s">
         <v>138</v>
@@ -5062,19 +5064,19 @@
         <v>92</v>
       </c>
       <c r="C111" s="75" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D111" s="76" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E111" s="85" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F111" s="86" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G111" s="99" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.3">
@@ -5083,19 +5085,19 @@
         <v>93</v>
       </c>
       <c r="C112" s="72" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D112" s="58" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E112" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="F112" s="74" t="s">
         <v>266</v>
       </c>
-      <c r="F112" s="74" t="s">
-        <v>267</v>
-      </c>
       <c r="G112" s="98" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.3">
@@ -5113,7 +5115,7 @@
         <v>119</v>
       </c>
       <c r="F113" s="71" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G113" s="90" t="s">
         <v>182</v>
@@ -5125,7 +5127,7 @@
         <v>95</v>
       </c>
       <c r="C114" s="57" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D114" s="58">
         <v>1</v>
@@ -5134,10 +5136,10 @@
         <v>119</v>
       </c>
       <c r="F114" s="71" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G114" s="90" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.3">
@@ -5146,7 +5148,7 @@
         <v>96</v>
       </c>
       <c r="C115" s="57" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D115" s="58">
         <v>2</v>
@@ -5158,7 +5160,7 @@
         <v>120</v>
       </c>
       <c r="G115" s="90" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.3">
@@ -5167,19 +5169,19 @@
         <v>97</v>
       </c>
       <c r="C116" s="72" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D116" s="58" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E116" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="F116" s="74" t="s">
         <v>266</v>
       </c>
-      <c r="F116" s="74" t="s">
-        <v>267</v>
-      </c>
       <c r="G116" s="98" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.3">
@@ -5209,19 +5211,19 @@
         <v>99</v>
       </c>
       <c r="C118" s="72" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D118" s="55" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E118" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="F118" s="74" t="s">
         <v>266</v>
       </c>
-      <c r="F118" s="74" t="s">
-        <v>267</v>
-      </c>
       <c r="G118" s="98" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="119" spans="2:7" x14ac:dyDescent="0.3">
@@ -5272,19 +5274,19 @@
         <v>102</v>
       </c>
       <c r="C121" s="77" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D121" s="18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E121" s="87" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F121" s="88" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G121" s="100" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="122" spans="2:7" x14ac:dyDescent="0.3">
@@ -5293,7 +5295,7 @@
         <v>103</v>
       </c>
       <c r="C122" s="57" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D122" s="55" t="s">
         <v>20</v>
@@ -5305,7 +5307,7 @@
         <v>120</v>
       </c>
       <c r="G122" s="90" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.3">
@@ -5323,7 +5325,7 @@
         <v>119</v>
       </c>
       <c r="F123" s="84" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G123" s="93" t="s">
         <v>140</v>
@@ -5344,13 +5346,13 @@
         <v>119</v>
       </c>
       <c r="F124" s="71" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G124" s="90" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="125" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B125" s="89">
         <f t="shared" si="3"/>
         <v>106</v>
@@ -5365,7 +5367,7 @@
         <v>119</v>
       </c>
       <c r="F125" s="71" t="s">
-        <v>194</v>
+        <v>378</v>
       </c>
       <c r="G125" s="90" t="s">
         <v>176</v>
@@ -5377,19 +5379,19 @@
         <v>107</v>
       </c>
       <c r="C126" s="68" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D126" s="18" t="s">
         <v>19</v>
       </c>
       <c r="E126" s="70" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F126" s="82" t="s">
         <v>16</v>
       </c>
       <c r="G126" s="96" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="127" spans="2:7" x14ac:dyDescent="0.3">
@@ -5398,7 +5400,7 @@
         <v>108</v>
       </c>
       <c r="C127" s="57" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D127" s="55" t="s">
         <v>19</v>
@@ -5407,10 +5409,10 @@
         <v>119</v>
       </c>
       <c r="F127" s="57" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G127" s="90" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="128" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -5428,7 +5430,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="71" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G128" s="90" t="s">
         <v>151</v>
@@ -5440,19 +5442,19 @@
         <v>110</v>
       </c>
       <c r="C129" s="72" t="s">
+        <v>282</v>
+      </c>
+      <c r="D129" s="58" t="s">
+        <v>287</v>
+      </c>
+      <c r="E129" s="74" t="s">
+        <v>266</v>
+      </c>
+      <c r="F129" s="74" t="s">
         <v>283</v>
       </c>
-      <c r="D129" s="58" t="s">
-        <v>288</v>
-      </c>
-      <c r="E129" s="74" t="s">
-        <v>267</v>
-      </c>
-      <c r="F129" s="74" t="s">
-        <v>284</v>
-      </c>
       <c r="G129" s="98" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="130" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -5461,19 +5463,19 @@
         <v>111</v>
       </c>
       <c r="C130" s="72" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D130" s="58" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E130" s="74" t="s">
+        <v>298</v>
+      </c>
+      <c r="F130" s="74" t="s">
         <v>299</v>
       </c>
-      <c r="F130" s="74" t="s">
-        <v>300</v>
-      </c>
       <c r="G130" s="98" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="131" spans="2:7" x14ac:dyDescent="0.3">
@@ -5482,7 +5484,7 @@
         <v>112</v>
       </c>
       <c r="C131" s="57" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D131" s="58">
         <v>1</v>
@@ -5503,19 +5505,19 @@
         <v>113</v>
       </c>
       <c r="C132" s="72" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D132" s="55" t="s">
+        <v>300</v>
+      </c>
+      <c r="E132" s="74" t="s">
         <v>301</v>
       </c>
-      <c r="E132" s="74" t="s">
+      <c r="F132" s="74" t="s">
         <v>302</v>
       </c>
-      <c r="F132" s="74" t="s">
-        <v>303</v>
-      </c>
       <c r="G132" s="98" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="133" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -5524,7 +5526,7 @@
         <v>114</v>
       </c>
       <c r="C133" s="57" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D133" s="58">
         <v>2</v>
@@ -5533,10 +5535,10 @@
         <v>120</v>
       </c>
       <c r="F133" s="71" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="G133" s="90" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="134" spans="2:7" x14ac:dyDescent="0.3">
@@ -5545,19 +5547,19 @@
         <v>115</v>
       </c>
       <c r="C134" s="72" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D134" s="58" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E134" s="74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F134" s="74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G134" s="98" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.3">
@@ -5566,19 +5568,19 @@
         <v>116</v>
       </c>
       <c r="C135" s="72" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D135" s="55" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E135" s="74" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F135" s="74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G135" s="98" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="136" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -5596,10 +5598,10 @@
         <v>69</v>
       </c>
       <c r="F136" s="71" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G136" s="90" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="137" spans="2:7" x14ac:dyDescent="0.3">
@@ -5608,7 +5610,7 @@
         <v>118</v>
       </c>
       <c r="C137" s="122" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D137" s="127" t="s">
         <v>20</v>
@@ -5620,7 +5622,7 @@
         <v>69</v>
       </c>
       <c r="G137" s="125" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="138" spans="2:7" x14ac:dyDescent="0.3">
@@ -5629,19 +5631,19 @@
         <v>119</v>
       </c>
       <c r="C138" s="57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D138" s="55" t="s">
         <v>55</v>
       </c>
       <c r="E138" s="59" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F138" s="71" t="s">
         <v>61</v>
       </c>
       <c r="G138" s="90" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="139" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -5659,19 +5661,19 @@
         <v>120</v>
       </c>
       <c r="F139" s="71" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G139" s="90" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="140" spans="2:7" ht="50.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B140" s="101">
         <f t="shared" si="3"/>
         <v>121</v>
       </c>
       <c r="C140" s="116" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D140" s="117">
         <v>1</v>
@@ -5680,7 +5682,7 @@
         <v>120</v>
       </c>
       <c r="F140" s="119" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="G140" s="120" t="s">
         <v>177</v>

--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D16C1C-4E28-4F74-A8C8-EA60B194CC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2EBC6C-9D03-459A-8574-BF7AC61684FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="381">
   <si>
     <t>Signal</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -295,11 +295,6 @@
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>o_d_mem_en
-o_d_mem_wren</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1575,6 +1570,39 @@
 u_wdata_forwarding_unit
 u_alu_forwarding_unit
 u_jump_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>u_wdata_forwarding_unit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+o_d_mem_en
+o_d_mem_wren</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>u_ex_mem_bridge
+u_wdata_forwarding_unit</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2828,7 +2856,7 @@
     <row r="1" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="129" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C2" s="130"/>
       <c r="D2" s="130"/>
@@ -3061,10 +3089,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="51" t="s">
+        <v>254</v>
+      </c>
+      <c r="D14" s="37" t="s">
         <v>255</v>
-      </c>
-      <c r="D14" s="37" t="s">
-        <v>256</v>
       </c>
       <c r="E14" s="53" t="s">
         <v>22</v>
@@ -3119,7 +3147,7 @@
     <row r="17" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="132" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C18" s="133"/>
       <c r="D18" s="133"/>
@@ -3153,19 +3181,19 @@
         <v>1</v>
       </c>
       <c r="C20" s="103" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D20" s="104">
         <v>1</v>
       </c>
       <c r="E20" s="103" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F20" s="128" t="s">
         <v>63</v>
       </c>
       <c r="G20" s="105" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3174,19 +3202,19 @@
         <v>2</v>
       </c>
       <c r="C21" s="57" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D21" s="58">
         <v>4</v>
       </c>
       <c r="E21" s="57" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F21" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="90" t="s">
         <v>65</v>
-      </c>
-      <c r="G21" s="90" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3195,19 +3223,19 @@
         <v>3</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D22" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E22" s="57" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F22" s="71" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G22" s="90" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.3">
@@ -3216,19 +3244,19 @@
         <v>4</v>
       </c>
       <c r="C23" s="57" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D23" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="57" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F23" s="71" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G23" s="90" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -3237,19 +3265,19 @@
         <v>5</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D24" s="58">
         <v>1</v>
       </c>
       <c r="E24" s="57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F24" s="71" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G24" s="90" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.3">
@@ -3258,19 +3286,19 @@
         <v>6</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D25" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E25" s="57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F25" s="71" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G25" s="90" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3279,19 +3307,19 @@
         <v>7</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D26" s="58">
         <v>1</v>
       </c>
       <c r="E26" s="57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F26" s="71" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G26" s="90" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.3">
@@ -3300,19 +3328,19 @@
         <v>8</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D27" s="58">
         <v>4</v>
       </c>
       <c r="E27" s="57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F27" s="59" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G27" s="90" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3321,19 +3349,19 @@
         <v>9</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D28" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E28" s="57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F28" s="71" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G28" s="90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.3">
@@ -3342,19 +3370,19 @@
         <v>10</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D29" s="73" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E29" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F29" s="71" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G29" s="97" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3363,19 +3391,19 @@
         <v>11</v>
       </c>
       <c r="C30" s="72" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D30" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E30" s="74" t="s">
         <v>287</v>
       </c>
-      <c r="E30" s="74" t="s">
+      <c r="F30" s="74" t="s">
         <v>288</v>
       </c>
-      <c r="F30" s="74" t="s">
-        <v>289</v>
-      </c>
       <c r="G30" s="98" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3384,19 +3412,19 @@
         <v>12</v>
       </c>
       <c r="C31" s="72" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D31" s="58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E31" s="74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F31" s="74" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G31" s="98" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3405,19 +3433,19 @@
         <v>13</v>
       </c>
       <c r="C32" s="72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D32" s="58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E32" s="74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F32" s="74" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G32" s="98" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3426,19 +3454,19 @@
         <v>14</v>
       </c>
       <c r="C33" s="72" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D33" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E33" s="74" t="s">
         <v>287</v>
       </c>
-      <c r="E33" s="74" t="s">
+      <c r="F33" s="74" t="s">
         <v>288</v>
       </c>
-      <c r="F33" s="74" t="s">
-        <v>289</v>
-      </c>
       <c r="G33" s="98" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
@@ -3447,19 +3475,19 @@
         <v>15</v>
       </c>
       <c r="C34" s="57" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D34" s="58">
         <v>3</v>
       </c>
       <c r="E34" s="59" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F34" s="71" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G34" s="90" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.3">
@@ -3468,7 +3496,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="57" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D35" s="55" t="s">
         <v>19</v>
@@ -3480,7 +3508,7 @@
         <v>52</v>
       </c>
       <c r="G35" s="90" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
@@ -3489,7 +3517,7 @@
         <v>17</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D36" s="55" t="s">
         <v>20</v>
@@ -3501,7 +3529,7 @@
         <v>35</v>
       </c>
       <c r="G36" s="90" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
@@ -3510,19 +3538,19 @@
         <v>18</v>
       </c>
       <c r="C37" s="57" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D37" s="58">
         <v>1</v>
       </c>
       <c r="E37" s="57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F37" s="59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G37" s="90" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -3531,19 +3559,19 @@
         <v>19</v>
       </c>
       <c r="C38" s="57" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D38" s="58">
         <v>1</v>
       </c>
       <c r="E38" s="71" t="s">
+        <v>330</v>
+      </c>
+      <c r="F38" s="71" t="s">
         <v>331</v>
       </c>
-      <c r="F38" s="71" t="s">
+      <c r="G38" s="90" t="s">
         <v>332</v>
-      </c>
-      <c r="G38" s="90" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -3552,19 +3580,19 @@
         <v>20</v>
       </c>
       <c r="C39" s="57" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D39" s="58">
         <v>1</v>
       </c>
       <c r="E39" s="74" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F39" s="71" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G39" s="90" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -3573,19 +3601,19 @@
         <v>21</v>
       </c>
       <c r="C40" s="57" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D40" s="58">
         <v>2</v>
       </c>
       <c r="E40" s="59" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F40" s="71" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G40" s="90" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.3">
@@ -3594,19 +3622,19 @@
         <v>22</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D41" s="58">
         <v>6</v>
       </c>
       <c r="E41" s="57" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F41" s="59" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G41" s="90" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3615,19 +3643,19 @@
         <v>23</v>
       </c>
       <c r="C42" s="57" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D42" s="55" t="s">
         <v>55</v>
       </c>
       <c r="E42" s="57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F42" s="71" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G42" s="90" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -3636,19 +3664,19 @@
         <v>24</v>
       </c>
       <c r="C43" s="57" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D43" s="55" t="s">
         <v>55</v>
       </c>
       <c r="E43" s="57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F43" s="71" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G43" s="90" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3657,19 +3685,19 @@
         <v>25</v>
       </c>
       <c r="C44" s="57" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D44" s="58">
         <v>1</v>
       </c>
       <c r="E44" s="74" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F44" s="71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G44" s="90" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.3">
@@ -3678,19 +3706,19 @@
         <v>26</v>
       </c>
       <c r="C45" s="57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D45" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E45" s="57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F45" s="59" t="s">
         <v>63</v>
       </c>
       <c r="G45" s="90" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
@@ -3699,19 +3727,19 @@
         <v>27</v>
       </c>
       <c r="C46" s="57" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D46" s="60" t="s">
         <v>19</v>
       </c>
       <c r="E46" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F46" s="59" t="s">
         <v>35</v>
       </c>
       <c r="G46" s="90" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
@@ -3720,7 +3748,7 @@
         <v>28</v>
       </c>
       <c r="C47" s="61" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D47" s="55" t="s">
         <v>20</v>
@@ -3729,10 +3757,10 @@
         <v>35</v>
       </c>
       <c r="F47" s="78" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G47" s="91" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3741,19 +3769,19 @@
         <v>29</v>
       </c>
       <c r="C48" s="72" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D48" s="58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E48" s="74" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F48" s="74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G48" s="98" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.3">
@@ -3762,19 +3790,19 @@
         <v>30</v>
       </c>
       <c r="C49" s="57" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D49" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E49" s="57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F49" s="59" t="s">
         <v>63</v>
       </c>
       <c r="G49" s="90" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
@@ -3783,19 +3811,19 @@
         <v>31</v>
       </c>
       <c r="C50" s="72" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D50" s="58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E50" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F50" s="74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G50" s="98" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3804,19 +3832,19 @@
         <v>32</v>
       </c>
       <c r="C51" s="57" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D51" s="58">
         <v>1</v>
       </c>
       <c r="E51" s="62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F51" s="78" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G51" s="90" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52" spans="2:7" x14ac:dyDescent="0.3">
@@ -3825,19 +3853,19 @@
         <v>33</v>
       </c>
       <c r="C52" s="72" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D52" s="55" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E52" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F52" s="74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G52" s="98" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
@@ -3846,40 +3874,40 @@
         <v>34</v>
       </c>
       <c r="C53" s="57" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D53" s="58">
         <v>1</v>
       </c>
       <c r="E53" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F53" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="F53" s="71" t="s">
-        <v>119</v>
-      </c>
       <c r="G53" s="90" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B54" s="89">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="C54" s="57" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D54" s="58">
         <v>1</v>
       </c>
       <c r="E54" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="F54" s="62" t="s">
-        <v>119</v>
+        <v>117</v>
+      </c>
+      <c r="F54" s="78" t="s">
+        <v>380</v>
       </c>
       <c r="G54" s="90" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.3">
@@ -3888,19 +3916,19 @@
         <v>36</v>
       </c>
       <c r="C55" s="72" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D55" s="55" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E55" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F55" s="74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G55" s="98" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -3909,19 +3937,19 @@
         <v>37</v>
       </c>
       <c r="C56" s="57" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D56" s="55" t="s">
         <v>20</v>
       </c>
       <c r="E56" s="59" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F56" s="71" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G56" s="91" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3930,19 +3958,19 @@
         <v>38</v>
       </c>
       <c r="C57" s="57" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D57" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E57" s="57" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F57" s="71" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G57" s="90" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -3951,19 +3979,19 @@
         <v>39</v>
       </c>
       <c r="C58" s="63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D58" s="64" t="s">
         <v>19</v>
       </c>
       <c r="E58" s="63" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F58" s="79" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G58" s="93" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -3972,19 +4000,19 @@
         <v>40</v>
       </c>
       <c r="C59" s="57" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D59" s="55" t="s">
         <v>55</v>
       </c>
       <c r="E59" s="57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F59" s="71" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G59" s="90" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.3">
@@ -3993,19 +4021,19 @@
         <v>41</v>
       </c>
       <c r="C60" s="57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D60" s="58">
         <v>1</v>
       </c>
       <c r="E60" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F60" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="F60" s="71" t="s">
-        <v>119</v>
-      </c>
       <c r="G60" s="90" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
@@ -4014,7 +4042,7 @@
         <v>42</v>
       </c>
       <c r="C61" s="57" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D61" s="55" t="s">
         <v>48</v>
@@ -4023,7 +4051,7 @@
         <v>46</v>
       </c>
       <c r="F61" s="57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G61" s="90" t="s">
         <v>53</v>
@@ -4035,13 +4063,13 @@
         <v>43</v>
       </c>
       <c r="C62" s="57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D62" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E62" s="57" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F62" s="59" t="s">
         <v>39</v>
@@ -4056,19 +4084,19 @@
         <v>44</v>
       </c>
       <c r="C63" s="57" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D63" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E63" s="57" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F63" s="71" t="s">
         <v>47</v>
       </c>
       <c r="G63" s="90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.3">
@@ -4077,19 +4105,19 @@
         <v>45</v>
       </c>
       <c r="C64" s="57" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D64" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E64" s="57" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F64" s="57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G64" s="90" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
@@ -4098,19 +4126,19 @@
         <v>46</v>
       </c>
       <c r="C65" s="57" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D65" s="58">
         <v>1</v>
       </c>
       <c r="E65" s="59" t="s">
+        <v>211</v>
+      </c>
+      <c r="F65" s="59" t="s">
         <v>212</v>
       </c>
-      <c r="F65" s="59" t="s">
-        <v>213</v>
-      </c>
       <c r="G65" s="90" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
@@ -4119,19 +4147,19 @@
         <v>47</v>
       </c>
       <c r="C66" s="57" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D66" s="58">
         <v>1</v>
       </c>
       <c r="E66" s="59" t="s">
+        <v>211</v>
+      </c>
+      <c r="F66" s="59" t="s">
         <v>212</v>
       </c>
-      <c r="F66" s="59" t="s">
-        <v>213</v>
-      </c>
       <c r="G66" s="90" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
@@ -4140,19 +4168,19 @@
         <v>48</v>
       </c>
       <c r="C67" s="57" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D67" s="58">
         <v>1</v>
       </c>
       <c r="E67" s="59" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F67" s="59" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G67" s="90" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
@@ -4161,19 +4189,19 @@
         <v>49</v>
       </c>
       <c r="C68" s="57" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D68" s="58">
         <v>1</v>
       </c>
       <c r="E68" s="59" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F68" s="59" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G68" s="90" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
@@ -4182,19 +4210,19 @@
         <v>50</v>
       </c>
       <c r="C69" s="57" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D69" s="58">
         <v>1</v>
       </c>
       <c r="E69" s="126" t="s">
+        <v>362</v>
+      </c>
+      <c r="F69" s="126" t="s">
+        <v>365</v>
+      </c>
+      <c r="G69" s="98" t="s">
         <v>363</v>
-      </c>
-      <c r="F69" s="126" t="s">
-        <v>366</v>
-      </c>
-      <c r="G69" s="98" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
@@ -4203,19 +4231,19 @@
         <v>51</v>
       </c>
       <c r="C70" s="57" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D70" s="58">
         <v>1</v>
       </c>
       <c r="E70" s="126" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F70" s="126" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G70" s="98" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
@@ -4224,19 +4252,19 @@
         <v>52</v>
       </c>
       <c r="C71" s="57" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D71" s="56">
         <v>1</v>
       </c>
       <c r="E71" s="57" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F71" s="59" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G71" s="90" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
@@ -4245,7 +4273,7 @@
         <v>53</v>
       </c>
       <c r="C72" s="57" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D72" s="58">
         <v>4</v>
@@ -4254,10 +4282,10 @@
         <v>57</v>
       </c>
       <c r="F72" s="59" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G72" s="90" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
@@ -4266,19 +4294,19 @@
         <v>54</v>
       </c>
       <c r="C73" s="72" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D73" s="58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E73" s="74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F73" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G73" s="98" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
@@ -4287,7 +4315,7 @@
         <v>55</v>
       </c>
       <c r="C74" s="57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D74" s="58">
         <v>3</v>
@@ -4296,10 +4324,10 @@
         <v>57</v>
       </c>
       <c r="F74" s="59" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G74" s="90" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
@@ -4308,7 +4336,7 @@
         <v>56</v>
       </c>
       <c r="C75" s="57" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D75" s="58">
         <v>1</v>
@@ -4317,10 +4345,10 @@
         <v>57</v>
       </c>
       <c r="F75" s="59" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G75" s="90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
@@ -4329,7 +4357,7 @@
         <v>57</v>
       </c>
       <c r="C76" s="57" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D76" s="58">
         <v>1</v>
@@ -4341,7 +4369,7 @@
         <v>62</v>
       </c>
       <c r="G76" s="90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.3">
@@ -4350,7 +4378,7 @@
         <v>58</v>
       </c>
       <c r="C77" s="57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D77" s="55" t="s">
         <v>56</v>
@@ -4371,7 +4399,7 @@
         <v>59</v>
       </c>
       <c r="C78" s="57" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D78" s="58">
         <v>6</v>
@@ -4380,10 +4408,10 @@
         <v>43</v>
       </c>
       <c r="F78" s="71" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G78" s="90" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="79" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -4392,7 +4420,7 @@
         <v>60</v>
       </c>
       <c r="C79" s="61" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D79" s="60" t="s">
         <v>44</v>
@@ -4413,7 +4441,7 @@
         <v>61</v>
       </c>
       <c r="C80" s="57" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D80" s="55" t="s">
         <v>54</v>
@@ -4434,7 +4462,7 @@
         <v>62</v>
       </c>
       <c r="C81" s="57" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D81" s="55" t="s">
         <v>55</v>
@@ -4446,7 +4474,7 @@
         <v>62</v>
       </c>
       <c r="G81" s="90" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -4455,7 +4483,7 @@
         <v>63</v>
       </c>
       <c r="C82" s="57" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D82" s="55" t="s">
         <v>55</v>
@@ -4464,10 +4492,10 @@
         <v>43</v>
       </c>
       <c r="F82" s="71" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G82" s="90" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="83" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
@@ -4476,7 +4504,7 @@
         <v>64</v>
       </c>
       <c r="C83" s="57" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D83" s="55" t="s">
         <v>55</v>
@@ -4485,10 +4513,10 @@
         <v>43</v>
       </c>
       <c r="F83" s="71" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G83" s="90" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
@@ -4497,7 +4525,7 @@
         <v>65</v>
       </c>
       <c r="C84" s="57" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D84" s="58">
         <v>5</v>
@@ -4518,19 +4546,19 @@
         <v>66</v>
       </c>
       <c r="C85" s="57" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D85" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E85" s="57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F85" s="59" t="s">
         <v>43</v>
       </c>
       <c r="G85" s="90" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
@@ -4539,7 +4567,7 @@
         <v>67</v>
       </c>
       <c r="C86" s="57" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D86" s="58">
         <v>2</v>
@@ -4548,10 +4576,10 @@
         <v>57</v>
       </c>
       <c r="F86" s="59" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G86" s="90" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="87" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -4560,19 +4588,19 @@
         <v>68</v>
       </c>
       <c r="C87" s="57" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D87" s="60" t="s">
         <v>20</v>
       </c>
       <c r="E87" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F87" s="59" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G87" s="90" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="88" spans="2:7" x14ac:dyDescent="0.3">
@@ -4581,19 +4609,19 @@
         <v>69</v>
       </c>
       <c r="C88" s="72" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D88" s="58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E88" s="74" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F88" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G88" s="98" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
@@ -4602,7 +4630,7 @@
         <v>70</v>
       </c>
       <c r="C89" s="57" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D89" s="58">
         <v>1</v>
@@ -4611,10 +4639,10 @@
         <v>57</v>
       </c>
       <c r="F89" s="62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G89" s="90" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
@@ -4623,19 +4651,19 @@
         <v>71</v>
       </c>
       <c r="C90" s="57" t="s">
+        <v>256</v>
+      </c>
+      <c r="D90" s="55" t="s">
         <v>257</v>
       </c>
-      <c r="D90" s="55" t="s">
+      <c r="E90" s="57" t="s">
         <v>258</v>
       </c>
-      <c r="E90" s="57" t="s">
+      <c r="F90" s="59" t="s">
         <v>259</v>
       </c>
-      <c r="F90" s="59" t="s">
+      <c r="G90" s="90" t="s">
         <v>260</v>
-      </c>
-      <c r="G90" s="90" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
@@ -4644,7 +4672,7 @@
         <v>72</v>
       </c>
       <c r="C91" s="57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D91" s="58">
         <v>1</v>
@@ -4653,10 +4681,10 @@
         <v>57</v>
       </c>
       <c r="F91" s="59" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G91" s="90" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
@@ -4665,7 +4693,7 @@
         <v>73</v>
       </c>
       <c r="C92" s="57" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D92" s="58">
         <v>1</v>
@@ -4674,10 +4702,10 @@
         <v>57</v>
       </c>
       <c r="F92" s="62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G92" s="90" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
@@ -4686,19 +4714,19 @@
         <v>74</v>
       </c>
       <c r="C93" s="57" t="s">
+        <v>261</v>
+      </c>
+      <c r="D93" s="55" t="s">
+        <v>257</v>
+      </c>
+      <c r="E93" s="57" t="s">
+        <v>258</v>
+      </c>
+      <c r="F93" s="59" t="s">
         <v>262</v>
       </c>
-      <c r="D93" s="55" t="s">
-        <v>258</v>
-      </c>
-      <c r="E93" s="57" t="s">
-        <v>259</v>
-      </c>
-      <c r="F93" s="59" t="s">
+      <c r="G93" s="90" t="s">
         <v>263</v>
-      </c>
-      <c r="G93" s="90" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="94" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -4707,19 +4735,19 @@
         <v>75</v>
       </c>
       <c r="C94" s="57" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D94" s="55" t="s">
         <v>20</v>
       </c>
       <c r="E94" s="57" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F94" s="71" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G94" s="91" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
@@ -4728,7 +4756,7 @@
         <v>76</v>
       </c>
       <c r="C95" s="57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D95" s="55" t="s">
         <v>19</v>
@@ -4737,10 +4765,10 @@
         <v>61</v>
       </c>
       <c r="F95" s="63" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G95" s="90" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
@@ -4749,7 +4777,7 @@
         <v>77</v>
       </c>
       <c r="C96" s="63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D96" s="64" t="s">
         <v>19</v>
@@ -4758,10 +4786,10 @@
         <v>61</v>
       </c>
       <c r="F96" s="63" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G96" s="93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -4770,19 +4798,19 @@
         <v>78</v>
       </c>
       <c r="C97" s="72" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D97" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="E97" s="74" t="s">
         <v>293</v>
       </c>
-      <c r="E97" s="74" t="s">
+      <c r="F97" s="74" t="s">
         <v>294</v>
       </c>
-      <c r="F97" s="74" t="s">
-        <v>295</v>
-      </c>
       <c r="G97" s="98" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="98" spans="2:7" x14ac:dyDescent="0.3">
@@ -4791,7 +4819,7 @@
         <v>79</v>
       </c>
       <c r="C98" s="57" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D98" s="58">
         <v>1</v>
@@ -4800,10 +4828,10 @@
         <v>57</v>
       </c>
       <c r="F98" s="59" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G98" s="90" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -4812,7 +4840,7 @@
         <v>80</v>
       </c>
       <c r="C99" s="57" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D99" s="60" t="s">
         <v>45</v>
@@ -4821,7 +4849,7 @@
         <v>41</v>
       </c>
       <c r="F99" s="59" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G99" s="90" t="s">
         <v>50</v>
@@ -4833,7 +4861,7 @@
         <v>81</v>
       </c>
       <c r="C100" s="57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D100" s="58">
         <v>1</v>
@@ -4845,7 +4873,7 @@
         <v>42</v>
       </c>
       <c r="G100" s="90" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.3">
@@ -4854,7 +4882,7 @@
         <v>82</v>
       </c>
       <c r="C101" s="57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D101" s="55" t="s">
         <v>19</v>
@@ -4863,10 +4891,10 @@
         <v>42</v>
       </c>
       <c r="F101" s="71" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G101" s="90" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
@@ -4875,7 +4903,7 @@
         <v>83</v>
       </c>
       <c r="C102" s="61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D102" s="55" t="s">
         <v>20</v>
@@ -4884,10 +4912,10 @@
         <v>38</v>
       </c>
       <c r="F102" s="78" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G102" s="91" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
@@ -4896,13 +4924,13 @@
         <v>84</v>
       </c>
       <c r="C103" s="65" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D103" s="12" t="s">
         <v>20</v>
       </c>
       <c r="E103" s="65" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F103" s="80" t="s">
         <v>11</v>
@@ -4917,7 +4945,7 @@
         <v>85</v>
       </c>
       <c r="C104" s="66" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D104" s="67">
         <v>1</v>
@@ -4938,7 +4966,7 @@
         <v>86</v>
       </c>
       <c r="C105" s="61" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D105" s="55" t="s">
         <v>20</v>
@@ -4947,10 +4975,10 @@
         <v>34</v>
       </c>
       <c r="F105" s="78" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G105" s="91" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="106" spans="2:7" x14ac:dyDescent="0.3">
@@ -4959,19 +4987,19 @@
         <v>87</v>
       </c>
       <c r="C106" s="57" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D106" s="55" t="s">
         <v>20</v>
       </c>
       <c r="E106" s="57" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F106" s="59" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G106" s="90" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.3">
@@ -4980,19 +5008,19 @@
         <v>88</v>
       </c>
       <c r="C107" s="57" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D107" s="55" t="s">
         <v>20</v>
       </c>
       <c r="E107" s="57" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F107" s="59" t="s">
         <v>34</v>
       </c>
       <c r="G107" s="90" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
@@ -5001,19 +5029,19 @@
         <v>89</v>
       </c>
       <c r="C108" s="57" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D108" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E108" s="126" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F108" s="126" t="s">
         <v>35</v>
       </c>
       <c r="G108" s="98" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -5022,19 +5050,19 @@
         <v>90</v>
       </c>
       <c r="C109" s="57" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D109" s="58">
         <v>1</v>
       </c>
       <c r="E109" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="F109" s="71" t="s">
+        <v>250</v>
+      </c>
+      <c r="G109" s="90" t="s">
         <v>227</v>
-      </c>
-      <c r="F109" s="71" t="s">
-        <v>251</v>
-      </c>
-      <c r="G109" s="90" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="110" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
@@ -5043,19 +5071,19 @@
         <v>91</v>
       </c>
       <c r="C110" s="68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D110" s="18" t="s">
         <v>19</v>
       </c>
       <c r="E110" s="68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F110" s="81" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G110" s="96" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
@@ -5064,19 +5092,19 @@
         <v>92</v>
       </c>
       <c r="C111" s="75" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D111" s="76" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E111" s="85" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F111" s="86" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G111" s="99" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.3">
@@ -5085,19 +5113,19 @@
         <v>93</v>
       </c>
       <c r="C112" s="72" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D112" s="58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E112" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="F112" s="74" t="s">
         <v>265</v>
       </c>
-      <c r="F112" s="74" t="s">
-        <v>266</v>
-      </c>
       <c r="G112" s="98" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.3">
@@ -5106,19 +5134,19 @@
         <v>94</v>
       </c>
       <c r="C113" s="57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D113" s="55" t="s">
         <v>55</v>
       </c>
       <c r="E113" s="71" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F113" s="71" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G113" s="90" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.3">
@@ -5127,19 +5155,19 @@
         <v>95</v>
       </c>
       <c r="C114" s="57" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D114" s="58">
         <v>1</v>
       </c>
       <c r="E114" s="59" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F114" s="71" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G114" s="90" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.3">
@@ -5148,19 +5176,19 @@
         <v>96</v>
       </c>
       <c r="C115" s="57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D115" s="58">
         <v>2</v>
       </c>
       <c r="E115" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="F115" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="F115" s="59" t="s">
-        <v>120</v>
-      </c>
       <c r="G115" s="90" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.3">
@@ -5169,19 +5197,19 @@
         <v>97</v>
       </c>
       <c r="C116" s="72" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D116" s="58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E116" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="F116" s="74" t="s">
         <v>265</v>
       </c>
-      <c r="F116" s="74" t="s">
-        <v>266</v>
-      </c>
       <c r="G116" s="98" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.3">
@@ -5190,19 +5218,19 @@
         <v>98</v>
       </c>
       <c r="C117" s="68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D117" s="69">
         <v>1</v>
       </c>
       <c r="E117" s="68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F117" s="82" t="s">
         <v>13</v>
       </c>
       <c r="G117" s="96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="118" spans="2:7" x14ac:dyDescent="0.3">
@@ -5211,19 +5239,19 @@
         <v>99</v>
       </c>
       <c r="C118" s="72" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D118" s="55" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E118" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="F118" s="74" t="s">
         <v>265</v>
       </c>
-      <c r="F118" s="74" t="s">
-        <v>266</v>
-      </c>
       <c r="G118" s="98" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="119" spans="2:7" x14ac:dyDescent="0.3">
@@ -5232,40 +5260,40 @@
         <v>100</v>
       </c>
       <c r="C119" s="57" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D119" s="58">
         <v>1</v>
       </c>
       <c r="E119" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="F119" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="F119" s="59" t="s">
-        <v>120</v>
-      </c>
       <c r="G119" s="90" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="120" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B120" s="89">
         <f t="shared" si="3"/>
         <v>101</v>
       </c>
       <c r="C120" s="68" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D120" s="69">
         <v>1</v>
       </c>
       <c r="E120" s="68" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F120" s="83" t="s">
-        <v>64</v>
+        <v>379</v>
       </c>
       <c r="G120" s="96" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="121" spans="2:7" x14ac:dyDescent="0.3">
@@ -5274,19 +5302,19 @@
         <v>102</v>
       </c>
       <c r="C121" s="77" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D121" s="18" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E121" s="87" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F121" s="88" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G121" s="100" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="122" spans="2:7" x14ac:dyDescent="0.3">
@@ -5295,19 +5323,19 @@
         <v>103</v>
       </c>
       <c r="C122" s="57" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D122" s="55" t="s">
         <v>20</v>
       </c>
       <c r="E122" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="F122" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="F122" s="59" t="s">
-        <v>120</v>
-      </c>
       <c r="G122" s="90" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.3">
@@ -5316,19 +5344,19 @@
         <v>104</v>
       </c>
       <c r="C123" s="63" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D123" s="64" t="s">
         <v>19</v>
       </c>
       <c r="E123" s="63" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F123" s="84" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G123" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="124" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -5337,19 +5365,19 @@
         <v>105</v>
       </c>
       <c r="C124" s="57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D124" s="55" t="s">
         <v>55</v>
       </c>
       <c r="E124" s="57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F124" s="71" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G124" s="90" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="125" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -5358,19 +5386,19 @@
         <v>106</v>
       </c>
       <c r="C125" s="57" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D125" s="58">
         <v>1</v>
       </c>
       <c r="E125" s="59" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F125" s="71" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G125" s="90" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="126" spans="2:7" x14ac:dyDescent="0.3">
@@ -5379,19 +5407,19 @@
         <v>107</v>
       </c>
       <c r="C126" s="68" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D126" s="18" t="s">
         <v>19</v>
       </c>
       <c r="E126" s="70" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F126" s="82" t="s">
         <v>16</v>
       </c>
       <c r="G126" s="96" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="127" spans="2:7" x14ac:dyDescent="0.3">
@@ -5400,19 +5428,19 @@
         <v>108</v>
       </c>
       <c r="C127" s="57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D127" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E127" s="57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F127" s="57" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G127" s="90" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="128" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
@@ -5421,19 +5449,19 @@
         <v>109</v>
       </c>
       <c r="C128" s="57" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D128" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E128" s="57" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F128" s="71" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G128" s="90" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="129" spans="2:7" x14ac:dyDescent="0.3">
@@ -5442,19 +5470,19 @@
         <v>110</v>
       </c>
       <c r="C129" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="D129" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E129" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="F129" s="74" t="s">
         <v>282</v>
       </c>
-      <c r="D129" s="58" t="s">
-        <v>287</v>
-      </c>
-      <c r="E129" s="74" t="s">
-        <v>266</v>
-      </c>
-      <c r="F129" s="74" t="s">
-        <v>283</v>
-      </c>
       <c r="G129" s="98" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="130" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -5463,19 +5491,19 @@
         <v>111</v>
       </c>
       <c r="C130" s="72" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D130" s="58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E130" s="74" t="s">
+        <v>297</v>
+      </c>
+      <c r="F130" s="74" t="s">
         <v>298</v>
       </c>
-      <c r="F130" s="74" t="s">
-        <v>299</v>
-      </c>
       <c r="G130" s="98" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="131" spans="2:7" x14ac:dyDescent="0.3">
@@ -5484,19 +5512,19 @@
         <v>112</v>
       </c>
       <c r="C131" s="57" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D131" s="58">
         <v>1</v>
       </c>
       <c r="E131" s="59" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F131" s="59" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G131" s="90" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="132" spans="2:7" x14ac:dyDescent="0.3">
@@ -5505,19 +5533,19 @@
         <v>113</v>
       </c>
       <c r="C132" s="72" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D132" s="55" t="s">
+        <v>299</v>
+      </c>
+      <c r="E132" s="74" t="s">
         <v>300</v>
       </c>
-      <c r="E132" s="74" t="s">
+      <c r="F132" s="74" t="s">
         <v>301</v>
       </c>
-      <c r="F132" s="74" t="s">
-        <v>302</v>
-      </c>
       <c r="G132" s="98" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="133" spans="2:7" ht="33" x14ac:dyDescent="0.3">
@@ -5526,19 +5554,19 @@
         <v>114</v>
       </c>
       <c r="C133" s="57" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D133" s="58">
         <v>2</v>
       </c>
       <c r="E133" s="59" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F133" s="71" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G133" s="90" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="134" spans="2:7" x14ac:dyDescent="0.3">
@@ -5547,19 +5575,19 @@
         <v>115</v>
       </c>
       <c r="C134" s="72" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D134" s="58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E134" s="74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F134" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G134" s="98" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.3">
@@ -5568,19 +5596,19 @@
         <v>116</v>
       </c>
       <c r="C135" s="72" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D135" s="55" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E135" s="74" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F135" s="74" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G135" s="98" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="136" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -5589,19 +5617,19 @@
         <v>117</v>
       </c>
       <c r="C136" s="57" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D136" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E136" s="57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F136" s="71" t="s">
+        <v>368</v>
+      </c>
+      <c r="G136" s="90" t="s">
         <v>369</v>
-      </c>
-      <c r="G136" s="90" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="137" spans="2:7" x14ac:dyDescent="0.3">
@@ -5610,19 +5638,19 @@
         <v>118</v>
       </c>
       <c r="C137" s="122" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D137" s="127" t="s">
         <v>20</v>
       </c>
       <c r="E137" s="123" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F137" s="124" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G137" s="125" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="138" spans="2:7" x14ac:dyDescent="0.3">
@@ -5631,19 +5659,19 @@
         <v>119</v>
       </c>
       <c r="C138" s="57" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D138" s="55" t="s">
         <v>55</v>
       </c>
       <c r="E138" s="59" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F138" s="71" t="s">
         <v>61</v>
       </c>
       <c r="G138" s="90" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="139" spans="2:7" ht="66" x14ac:dyDescent="0.3">
@@ -5652,19 +5680,19 @@
         <v>120</v>
       </c>
       <c r="C139" s="57" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D139" s="55" t="s">
         <v>55</v>
       </c>
       <c r="E139" s="57" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F139" s="71" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G139" s="90" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="140" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
@@ -5673,19 +5701,19 @@
         <v>121</v>
       </c>
       <c r="C140" s="116" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D140" s="117">
         <v>1</v>
       </c>
       <c r="E140" s="118" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F140" s="119" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G140" s="120" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="141" spans="2:7" x14ac:dyDescent="0.3">

--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B2EBC6C-9D03-459A-8574-BF7AC61684FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1559E386-A115-4D21-BDF5-69990F8F99FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CPU!$C$19:$G$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CPU!$C$20:$G$141</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="386">
   <si>
     <t>Signal</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1603,6 +1603,26 @@
   <si>
     <t>u_ex_mem_bridge
 u_wdata_forwarding_unit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AXI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{AXI5.MASTER}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CPU/NoC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NoC/CPU</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AXI-NoC Interface</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1655,7 +1675,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1692,6 +1712,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -2094,7 +2120,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2499,6 +2525,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2839,7 +2880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:H141"/>
+  <dimension ref="B1:H142"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
@@ -3144,296 +3185,295 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="132" t="s">
+    <row r="17" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="135">
+        <v>14</v>
+      </c>
+      <c r="C17" s="136" t="s">
+        <v>381</v>
+      </c>
+      <c r="D17" s="137" t="s">
+        <v>382</v>
+      </c>
+      <c r="E17" s="136" t="s">
+        <v>383</v>
+      </c>
+      <c r="F17" s="138" t="s">
+        <v>384</v>
+      </c>
+      <c r="G17" s="139" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="132" t="s">
         <v>357</v>
       </c>
-      <c r="C18" s="133"/>
-      <c r="D18" s="133"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="134"/>
-    </row>
-    <row r="19" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="107" t="s">
+      <c r="C19" s="133"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="134"/>
+    </row>
+    <row r="20" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="107" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D20" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E20" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F20" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G20" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B20" s="102">
-        <f>IF(C20="","",1)</f>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="102">
+        <f>IF(C21="","",1)</f>
         <v>1</v>
       </c>
-      <c r="C20" s="103" t="s">
+      <c r="C21" s="103" t="s">
         <v>168</v>
       </c>
-      <c r="D20" s="104">
+      <c r="D21" s="104">
         <v>1</v>
       </c>
-      <c r="E20" s="103" t="s">
+      <c r="E21" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="128" t="s">
+      <c r="F21" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="G20" s="105" t="s">
+      <c r="G21" s="105" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B21" s="89">
-        <f t="shared" ref="B21:B50" si="0">IF(C21="","",B20+1)</f>
-        <v>2</v>
-      </c>
-      <c r="C21" s="57" t="s">
-        <v>165</v>
-      </c>
-      <c r="D21" s="58">
-        <v>4</v>
-      </c>
-      <c r="E21" s="57" t="s">
-        <v>324</v>
-      </c>
-      <c r="F21" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21" s="90" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B22" s="89">
+        <f t="shared" ref="B22:B51" si="0">IF(C22="","",B21+1)</f>
+        <v>2</v>
+      </c>
+      <c r="C22" s="57" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" s="58">
+        <v>4</v>
+      </c>
+      <c r="E22" s="57" t="s">
+        <v>324</v>
+      </c>
+      <c r="F22" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="90" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B23" s="89">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C22" s="57" t="s">
+      <c r="C23" s="57" t="s">
         <v>325</v>
       </c>
-      <c r="D22" s="55" t="s">
+      <c r="D23" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="57" t="s">
+      <c r="E23" s="57" t="s">
         <v>198</v>
       </c>
-      <c r="F22" s="71" t="s">
+      <c r="F23" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="G22" s="90" t="s">
+      <c r="G23" s="90" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" s="89">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="89">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C23" s="57" t="s">
+      <c r="C24" s="57" t="s">
         <v>209</v>
       </c>
-      <c r="D23" s="55" t="s">
+      <c r="D24" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E23" s="57" t="s">
+      <c r="E24" s="57" t="s">
         <v>199</v>
       </c>
-      <c r="F23" s="71" t="s">
+      <c r="F24" s="71" t="s">
         <v>193</v>
       </c>
-      <c r="G23" s="90" t="s">
+      <c r="G24" s="90" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B24" s="89">
+    <row r="25" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B25" s="89">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C24" s="57" t="s">
+      <c r="C25" s="57" t="s">
         <v>241</v>
       </c>
-      <c r="D24" s="58">
+      <c r="D25" s="58">
         <v>1</v>
       </c>
-      <c r="E24" s="57" t="s">
+      <c r="E25" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="71" t="s">
+      <c r="F25" s="71" t="s">
         <v>326</v>
       </c>
-      <c r="G24" s="90" t="s">
+      <c r="G25" s="90" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" s="89">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="89">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C25" s="57" t="s">
+      <c r="C26" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="D25" s="55" t="s">
+      <c r="D26" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E25" s="57" t="s">
+      <c r="E26" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="F25" s="71" t="s">
+      <c r="F26" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="G25" s="90" t="s">
+      <c r="G26" s="90" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B26" s="89">
+    <row r="27" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B27" s="89">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C26" s="57" t="s">
+      <c r="C27" s="57" t="s">
         <v>169</v>
       </c>
-      <c r="D26" s="58">
+      <c r="D27" s="58">
         <v>1</v>
       </c>
-      <c r="E26" s="57" t="s">
+      <c r="E27" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="71" t="s">
+      <c r="F27" s="71" t="s">
         <v>327</v>
       </c>
-      <c r="G26" s="90" t="s">
+      <c r="G27" s="90" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B27" s="89">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B28" s="89">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C28" s="57" t="s">
         <v>124</v>
       </c>
-      <c r="D27" s="58">
+      <c r="D28" s="58">
         <v>4</v>
       </c>
-      <c r="E27" s="57" t="s">
+      <c r="E28" s="57" t="s">
         <v>117</v>
       </c>
-      <c r="F27" s="59" t="s">
+      <c r="F28" s="59" t="s">
         <v>324</v>
       </c>
-      <c r="G27" s="90" t="s">
+      <c r="G28" s="90" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B28" s="89">
+    <row r="29" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B29" s="89">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C28" s="57" t="s">
+      <c r="C29" s="57" t="s">
         <v>167</v>
       </c>
-      <c r="D28" s="55" t="s">
+      <c r="D29" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E29" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="71" t="s">
+      <c r="F29" s="71" t="s">
         <v>64</v>
       </c>
-      <c r="G28" s="90" t="s">
+      <c r="G29" s="90" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B29" s="89">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B30" s="89">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C29" s="57" t="s">
+      <c r="C30" s="57" t="s">
         <v>266</v>
       </c>
-      <c r="D29" s="73" t="s">
+      <c r="D30" s="73" t="s">
         <v>286</v>
       </c>
-      <c r="E29" s="74" t="s">
+      <c r="E30" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="F29" s="71" t="s">
+      <c r="F30" s="71" t="s">
         <v>264</v>
       </c>
-      <c r="G29" s="97" t="s">
+      <c r="G30" s="97" t="s">
         <v>302</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B30" s="89">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C30" s="72" t="s">
-        <v>267</v>
-      </c>
-      <c r="D30" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E30" s="74" t="s">
-        <v>287</v>
-      </c>
-      <c r="F30" s="74" t="s">
-        <v>288</v>
-      </c>
-      <c r="G30" s="98" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B31" s="89">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31" s="72" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D31" s="58" t="s">
         <v>286</v>
       </c>
       <c r="E31" s="74" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F31" s="74" t="s">
         <v>288</v>
       </c>
       <c r="G31" s="98" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B32" s="89">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" s="72" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D32" s="58" t="s">
         <v>286</v>
@@ -3445,226 +3485,226 @@
         <v>288</v>
       </c>
       <c r="G32" s="98" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B33" s="89">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33" s="72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D33" s="58" t="s">
         <v>286</v>
       </c>
       <c r="E33" s="74" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F33" s="74" t="s">
         <v>288</v>
       </c>
       <c r="G33" s="98" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B34" s="89">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C34" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" s="58">
-        <v>3</v>
-      </c>
-      <c r="E34" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="F34" s="71" t="s">
-        <v>328</v>
-      </c>
-      <c r="G34" s="90" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="C34" s="72" t="s">
+        <v>270</v>
+      </c>
+      <c r="D34" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E34" s="74" t="s">
+        <v>287</v>
+      </c>
+      <c r="F34" s="74" t="s">
+        <v>288</v>
+      </c>
+      <c r="G34" s="98" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B35" s="89">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C35" s="57" t="s">
-        <v>158</v>
-      </c>
-      <c r="D35" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="F35" s="59" t="s">
-        <v>52</v>
+        <v>140</v>
+      </c>
+      <c r="D35" s="58">
+        <v>3</v>
+      </c>
+      <c r="E35" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F35" s="71" t="s">
+        <v>328</v>
       </c>
       <c r="G35" s="90" t="s">
-        <v>333</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B36" s="89">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E36" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="F36" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="F36" s="59" t="s">
-        <v>35</v>
-      </c>
       <c r="G36" s="90" t="s">
-        <v>75</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B37" s="89">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C37" s="57" t="s">
-        <v>109</v>
-      </c>
-      <c r="D37" s="58">
-        <v>1</v>
+        <v>172</v>
+      </c>
+      <c r="D37" s="55" t="s">
+        <v>20</v>
       </c>
       <c r="E37" s="57" t="s">
-        <v>117</v>
+        <v>52</v>
       </c>
       <c r="F37" s="59" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="G37" s="90" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B38" s="89">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C38" s="57" t="s">
-        <v>329</v>
+        <v>109</v>
       </c>
       <c r="D38" s="58">
         <v>1</v>
       </c>
-      <c r="E38" s="71" t="s">
-        <v>330</v>
-      </c>
-      <c r="F38" s="71" t="s">
-        <v>331</v>
+      <c r="E38" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="F38" s="59" t="s">
+        <v>67</v>
       </c>
       <c r="G38" s="90" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B39" s="89">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C39" s="57" t="s">
-        <v>243</v>
+        <v>329</v>
       </c>
       <c r="D39" s="58">
         <v>1</v>
       </c>
-      <c r="E39" s="74" t="s">
-        <v>336</v>
+      <c r="E39" s="71" t="s">
+        <v>330</v>
       </c>
       <c r="F39" s="71" t="s">
-        <v>228</v>
+        <v>331</v>
       </c>
       <c r="G39" s="90" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B40" s="89">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C40" s="57" t="s">
-        <v>142</v>
+        <v>243</v>
       </c>
       <c r="D40" s="58">
-        <v>2</v>
-      </c>
-      <c r="E40" s="59" t="s">
-        <v>117</v>
+        <v>1</v>
+      </c>
+      <c r="E40" s="74" t="s">
+        <v>336</v>
       </c>
       <c r="F40" s="71" t="s">
-        <v>370</v>
+        <v>228</v>
       </c>
       <c r="G40" s="90" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B41" s="89">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="D41" s="58">
-        <v>6</v>
-      </c>
-      <c r="E41" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="F41" s="59" t="s">
-        <v>324</v>
+        <v>2</v>
+      </c>
+      <c r="E41" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F41" s="71" t="s">
+        <v>370</v>
       </c>
       <c r="G41" s="90" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B42" s="89">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C42" s="57" t="s">
-        <v>184</v>
-      </c>
-      <c r="D42" s="55" t="s">
-        <v>55</v>
+        <v>122</v>
+      </c>
+      <c r="D42" s="58">
+        <v>6</v>
       </c>
       <c r="E42" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="F42" s="71" t="s">
-        <v>373</v>
+        <v>115</v>
+      </c>
+      <c r="F42" s="59" t="s">
+        <v>324</v>
       </c>
       <c r="G42" s="90" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B43" s="89">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C43" s="57" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D43" s="55" t="s">
         <v>55</v>
@@ -3673,481 +3713,481 @@
         <v>117</v>
       </c>
       <c r="F43" s="71" t="s">
-        <v>337</v>
+        <v>373</v>
       </c>
       <c r="G43" s="90" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B44" s="89">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="57" t="s">
-        <v>200</v>
-      </c>
-      <c r="D44" s="58">
-        <v>1</v>
-      </c>
-      <c r="E44" s="74" t="s">
-        <v>201</v>
+        <v>179</v>
+      </c>
+      <c r="D44" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E44" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="F44" s="71" t="s">
-        <v>215</v>
+        <v>337</v>
       </c>
       <c r="G44" s="90" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B45" s="89">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C45" s="57" t="s">
-        <v>170</v>
-      </c>
-      <c r="D45" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="57" t="s">
-        <v>72</v>
-      </c>
-      <c r="F45" s="59" t="s">
-        <v>63</v>
+        <v>200</v>
+      </c>
+      <c r="D45" s="58">
+        <v>1</v>
+      </c>
+      <c r="E45" s="74" t="s">
+        <v>201</v>
+      </c>
+      <c r="F45" s="71" t="s">
+        <v>215</v>
       </c>
       <c r="G45" s="90" t="s">
-        <v>73</v>
+        <v>338</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B46" s="89">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C46" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="D46" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E46" s="74" t="s">
-        <v>115</v>
+      <c r="E46" s="57" t="s">
+        <v>72</v>
       </c>
       <c r="F46" s="59" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="G46" s="90" t="s">
-        <v>114</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B47" s="89">
         <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="C47" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="D47" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="E47" s="61" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="D47" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E47" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="F47" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="F47" s="78" t="s">
-        <v>190</v>
-      </c>
-      <c r="G47" s="91" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="G47" s="90" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B48" s="89">
         <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="C48" s="72" t="s">
-        <v>271</v>
-      </c>
-      <c r="D48" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E48" s="74" t="s">
-        <v>289</v>
-      </c>
-      <c r="F48" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="G48" s="98" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="C48" s="61" t="s">
+        <v>151</v>
+      </c>
+      <c r="D48" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="F48" s="78" t="s">
+        <v>190</v>
+      </c>
+      <c r="G48" s="91" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B49" s="89">
         <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C49" s="72" t="s">
+        <v>271</v>
+      </c>
+      <c r="D49" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E49" s="74" t="s">
+        <v>289</v>
+      </c>
+      <c r="F49" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="G49" s="98" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B50" s="89">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C49" s="57" t="s">
+      <c r="C50" s="57" t="s">
         <v>171</v>
       </c>
-      <c r="D49" s="55" t="s">
+      <c r="D50" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E49" s="57" t="s">
+      <c r="E50" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="F49" s="59" t="s">
+      <c r="F50" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="G49" s="90" t="s">
+      <c r="G50" s="90" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B50" s="92">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B51" s="92">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C50" s="72" t="s">
+      <c r="C51" s="72" t="s">
         <v>272</v>
       </c>
-      <c r="D50" s="58" t="s">
+      <c r="D51" s="58" t="s">
         <v>286</v>
       </c>
-      <c r="E50" s="74" t="s">
+      <c r="E51" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="F50" s="74" t="s">
+      <c r="F51" s="74" t="s">
         <v>264</v>
       </c>
-      <c r="G50" s="98" t="s">
+      <c r="G51" s="98" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="51" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B51" s="89">
-        <f t="shared" ref="B51:B82" si="1">IF(C51="","",B50+1)</f>
+    <row r="52" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B52" s="89">
+        <f t="shared" ref="B52:B83" si="1">IF(C52="","",B51+1)</f>
         <v>32</v>
       </c>
-      <c r="C51" s="57" t="s">
+      <c r="C52" s="57" t="s">
         <v>126</v>
       </c>
-      <c r="D51" s="58">
+      <c r="D52" s="58">
         <v>1</v>
       </c>
-      <c r="E51" s="62" t="s">
+      <c r="E52" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="F51" s="78" t="s">
+      <c r="F52" s="78" t="s">
         <v>224</v>
       </c>
-      <c r="G51" s="90" t="s">
+      <c r="G52" s="90" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B52" s="89">
-        <f t="shared" si="1"/>
-        <v>33</v>
-      </c>
-      <c r="C52" s="72" t="s">
-        <v>273</v>
-      </c>
-      <c r="D52" s="55" t="s">
-        <v>290</v>
-      </c>
-      <c r="E52" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="F52" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="G52" s="98" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B53" s="89">
         <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="C53" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="D53" s="58">
-        <v>1</v>
-      </c>
-      <c r="E53" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="F53" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="G53" s="90" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="C53" s="72" t="s">
+        <v>273</v>
+      </c>
+      <c r="D53" s="55" t="s">
+        <v>290</v>
+      </c>
+      <c r="E53" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="F53" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="G53" s="98" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B54" s="89">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C54" s="57" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D54" s="58">
         <v>1</v>
       </c>
-      <c r="E54" s="62" t="s">
+      <c r="E54" s="59" t="s">
         <v>117</v>
       </c>
-      <c r="F54" s="78" t="s">
-        <v>380</v>
+      <c r="F54" s="71" t="s">
+        <v>118</v>
       </c>
       <c r="G54" s="90" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B55" s="89">
         <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-      <c r="C55" s="72" t="s">
-        <v>274</v>
-      </c>
-      <c r="D55" s="55" t="s">
-        <v>290</v>
-      </c>
-      <c r="E55" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="F55" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="G55" s="98" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="C55" s="57" t="s">
+        <v>127</v>
+      </c>
+      <c r="D55" s="58">
+        <v>1</v>
+      </c>
+      <c r="E55" s="62" t="s">
+        <v>117</v>
+      </c>
+      <c r="F55" s="78" t="s">
+        <v>380</v>
+      </c>
+      <c r="G55" s="90" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B56" s="89">
         <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-      <c r="C56" s="57" t="s">
-        <v>223</v>
+        <v>36</v>
+      </c>
+      <c r="C56" s="72" t="s">
+        <v>274</v>
       </c>
       <c r="D56" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="E56" s="59" t="s">
+        <v>290</v>
+      </c>
+      <c r="E56" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="F56" s="71" t="s">
-        <v>339</v>
-      </c>
-      <c r="G56" s="91" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F56" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="G56" s="98" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B57" s="89">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C57" s="57" t="s">
-        <v>101</v>
+        <v>223</v>
       </c>
       <c r="D57" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E57" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" s="59" t="s">
         <v>115</v>
       </c>
       <c r="F57" s="71" t="s">
-        <v>366</v>
-      </c>
-      <c r="G57" s="90" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>339</v>
+      </c>
+      <c r="G57" s="91" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B58" s="89">
         <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="C58" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="D58" s="64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C58" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="D58" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="63" t="s">
+      <c r="E58" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="F58" s="79" t="s">
-        <v>340</v>
-      </c>
-      <c r="G58" s="93" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="F58" s="71" t="s">
+        <v>366</v>
+      </c>
+      <c r="G58" s="90" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B59" s="89">
         <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="C59" s="57" t="s">
-        <v>196</v>
-      </c>
-      <c r="D59" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="E59" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="F59" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="G59" s="90" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="C59" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="D59" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="E59" s="63" t="s">
+        <v>115</v>
+      </c>
+      <c r="F59" s="79" t="s">
+        <v>340</v>
+      </c>
+      <c r="G59" s="93" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B60" s="89">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C60" s="57" t="s">
-        <v>173</v>
-      </c>
-      <c r="D60" s="58">
-        <v>1</v>
-      </c>
-      <c r="E60" s="59" t="s">
+        <v>196</v>
+      </c>
+      <c r="D60" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E60" s="57" t="s">
         <v>117</v>
       </c>
       <c r="F60" s="71" t="s">
-        <v>118</v>
+        <v>224</v>
       </c>
       <c r="G60" s="90" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B61" s="89">
         <f t="shared" si="1"/>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C61" s="57" t="s">
-        <v>156</v>
-      </c>
-      <c r="D61" s="55" t="s">
-        <v>48</v>
-      </c>
-      <c r="E61" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="F61" s="57" t="s">
-        <v>157</v>
+        <v>173</v>
+      </c>
+      <c r="D61" s="58">
+        <v>1</v>
+      </c>
+      <c r="E61" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="F61" s="71" t="s">
+        <v>118</v>
       </c>
       <c r="G61" s="90" t="s">
-        <v>53</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B62" s="89">
         <f t="shared" si="1"/>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C62" s="57" t="s">
+        <v>156</v>
+      </c>
+      <c r="D62" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" s="57" t="s">
+        <v>46</v>
+      </c>
+      <c r="F62" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="D62" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E62" s="57" t="s">
-        <v>156</v>
-      </c>
-      <c r="F62" s="59" t="s">
-        <v>39</v>
-      </c>
       <c r="G62" s="90" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B63" s="89">
         <f t="shared" si="1"/>
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C63" s="57" t="s">
-        <v>105</v>
+        <v>157</v>
       </c>
       <c r="D63" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E63" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="F63" s="71" t="s">
-        <v>47</v>
+        <v>156</v>
+      </c>
+      <c r="F63" s="59" t="s">
+        <v>39</v>
       </c>
       <c r="G63" s="90" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B64" s="89">
         <f t="shared" si="1"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C64" s="57" t="s">
-        <v>216</v>
+        <v>105</v>
       </c>
       <c r="D64" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E64" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="F64" s="57" t="s">
-        <v>118</v>
+        <v>115</v>
+      </c>
+      <c r="F64" s="71" t="s">
+        <v>47</v>
       </c>
       <c r="G64" s="90" t="s">
-        <v>217</v>
+        <v>107</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B65" s="89">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C65" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="D65" s="58">
-        <v>1</v>
-      </c>
-      <c r="E65" s="59" t="s">
-        <v>211</v>
-      </c>
-      <c r="F65" s="59" t="s">
-        <v>212</v>
+        <v>216</v>
+      </c>
+      <c r="D65" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E65" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="F65" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="G65" s="90" t="s">
-        <v>341</v>
+        <v>217</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B66" s="89">
         <f t="shared" si="1"/>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C66" s="57" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D66" s="58">
         <v>1</v>
@@ -4159,16 +4199,16 @@
         <v>212</v>
       </c>
       <c r="G66" s="90" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B67" s="89">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C67" s="57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D67" s="58">
         <v>1</v>
@@ -4177,19 +4217,19 @@
         <v>211</v>
       </c>
       <c r="F67" s="59" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G67" s="90" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B68" s="89">
         <f t="shared" si="1"/>
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C68" s="57" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D68" s="58">
         <v>1</v>
@@ -4198,40 +4238,40 @@
         <v>211</v>
       </c>
       <c r="F68" s="59" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="G68" s="90" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B69" s="89">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C69" s="57" t="s">
-        <v>360</v>
+        <v>206</v>
       </c>
       <c r="D69" s="58">
         <v>1</v>
       </c>
-      <c r="E69" s="126" t="s">
-        <v>362</v>
-      </c>
-      <c r="F69" s="126" t="s">
-        <v>365</v>
-      </c>
-      <c r="G69" s="98" t="s">
-        <v>363</v>
+      <c r="E69" s="59" t="s">
+        <v>211</v>
+      </c>
+      <c r="F69" s="59" t="s">
+        <v>199</v>
+      </c>
+      <c r="G69" s="90" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B70" s="89">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C70" s="57" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D70" s="58">
         <v>1</v>
@@ -4243,121 +4283,121 @@
         <v>365</v>
       </c>
       <c r="G70" s="98" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B71" s="89">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C71" s="57" t="s">
-        <v>207</v>
-      </c>
-      <c r="D71" s="56">
+        <v>361</v>
+      </c>
+      <c r="D71" s="58">
         <v>1</v>
       </c>
-      <c r="E71" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="F71" s="59" t="s">
-        <v>194</v>
-      </c>
-      <c r="G71" s="90" t="s">
-        <v>345</v>
+      <c r="E71" s="126" t="s">
+        <v>362</v>
+      </c>
+      <c r="F71" s="126" t="s">
+        <v>365</v>
+      </c>
+      <c r="G71" s="98" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B72" s="89">
         <f t="shared" si="1"/>
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C72" s="57" t="s">
-        <v>79</v>
-      </c>
-      <c r="D72" s="58">
-        <v>4</v>
+        <v>207</v>
+      </c>
+      <c r="D72" s="56">
+        <v>1</v>
       </c>
       <c r="E72" s="57" t="s">
-        <v>57</v>
+        <v>201</v>
       </c>
       <c r="F72" s="59" t="s">
-        <v>117</v>
+        <v>194</v>
       </c>
       <c r="G72" s="90" t="s">
-        <v>91</v>
+        <v>345</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B73" s="89">
         <f t="shared" si="1"/>
-        <v>54</v>
-      </c>
-      <c r="C73" s="72" t="s">
-        <v>355</v>
-      </c>
-      <c r="D73" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E73" s="74" t="s">
-        <v>291</v>
-      </c>
-      <c r="F73" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="G73" s="98" t="s">
-        <v>311</v>
+        <v>53</v>
+      </c>
+      <c r="C73" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73" s="58">
+        <v>4</v>
+      </c>
+      <c r="E73" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="F73" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="G73" s="90" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B74" s="89">
         <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
-      <c r="C74" s="57" t="s">
-        <v>85</v>
-      </c>
-      <c r="D74" s="58">
-        <v>3</v>
-      </c>
-      <c r="E74" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="F74" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="G74" s="90" t="s">
-        <v>98</v>
+        <v>54</v>
+      </c>
+      <c r="C74" s="72" t="s">
+        <v>355</v>
+      </c>
+      <c r="D74" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E74" s="74" t="s">
+        <v>291</v>
+      </c>
+      <c r="F74" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="G74" s="98" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B75" s="89">
         <f t="shared" si="1"/>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C75" s="57" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D75" s="58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" s="57" t="s">
         <v>57</v>
       </c>
       <c r="F75" s="59" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G75" s="90" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B76" s="89">
         <f t="shared" si="1"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C76" s="57" t="s">
-        <v>349</v>
+        <v>80</v>
       </c>
       <c r="D76" s="58">
         <v>1</v>
@@ -4365,125 +4405,125 @@
       <c r="E76" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="F76" s="57" t="s">
-        <v>62</v>
+      <c r="F76" s="59" t="s">
+        <v>115</v>
       </c>
       <c r="G76" s="90" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="77" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B77" s="89">
         <f t="shared" si="1"/>
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C77" s="57" t="s">
-        <v>164</v>
-      </c>
-      <c r="D77" s="55" t="s">
-        <v>56</v>
+        <v>349</v>
+      </c>
+      <c r="D77" s="58">
+        <v>1</v>
       </c>
       <c r="E77" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="F77" s="59" t="s">
-        <v>42</v>
+        <v>57</v>
+      </c>
+      <c r="F77" s="57" t="s">
+        <v>62</v>
       </c>
       <c r="G77" s="90" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B78" s="89">
         <f t="shared" si="1"/>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C78" s="57" t="s">
-        <v>120</v>
-      </c>
-      <c r="D78" s="58">
-        <v>6</v>
+        <v>164</v>
+      </c>
+      <c r="D78" s="55" t="s">
+        <v>56</v>
       </c>
       <c r="E78" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="F78" s="71" t="s">
-        <v>229</v>
+      <c r="F78" s="59" t="s">
+        <v>42</v>
       </c>
       <c r="G78" s="90" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B79" s="89">
         <f t="shared" si="1"/>
-        <v>60</v>
-      </c>
-      <c r="C79" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="D79" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="E79" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="C79" s="57" t="s">
+        <v>120</v>
+      </c>
+      <c r="D79" s="58">
+        <v>6</v>
+      </c>
+      <c r="E79" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="F79" s="78" t="s">
-        <v>41</v>
-      </c>
-      <c r="G79" s="91" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="80" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F79" s="71" t="s">
+        <v>229</v>
+      </c>
+      <c r="G79" s="90" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B80" s="89">
         <f t="shared" si="1"/>
-        <v>61</v>
-      </c>
-      <c r="C80" s="57" t="s">
-        <v>159</v>
-      </c>
-      <c r="D80" s="55" t="s">
-        <v>54</v>
-      </c>
-      <c r="E80" s="57" t="s">
+        <v>60</v>
+      </c>
+      <c r="C80" s="61" t="s">
+        <v>153</v>
+      </c>
+      <c r="D80" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="E80" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="F80" s="59" t="s">
-        <v>57</v>
-      </c>
-      <c r="G80" s="90" t="s">
-        <v>58</v>
+      <c r="F80" s="78" t="s">
+        <v>41</v>
+      </c>
+      <c r="G80" s="91" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="89">
         <f t="shared" si="1"/>
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C81" s="57" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D81" s="55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E81" s="57" t="s">
         <v>43</v>
       </c>
       <c r="F81" s="59" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G81" s="90" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="89">
         <f t="shared" si="1"/>
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C82" s="57" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D82" s="55" t="s">
         <v>55</v>
@@ -4491,20 +4531,20 @@
       <c r="E82" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="F82" s="71" t="s">
-        <v>225</v>
+      <c r="F82" s="59" t="s">
+        <v>62</v>
       </c>
       <c r="G82" s="90" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B83" s="89">
-        <f t="shared" ref="B83:B114" si="2">IF(C83="","",B82+1)</f>
-        <v>64</v>
+        <f t="shared" si="1"/>
+        <v>63</v>
       </c>
       <c r="C83" s="57" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D83" s="55" t="s">
         <v>55</v>
@@ -4513,187 +4553,187 @@
         <v>43</v>
       </c>
       <c r="F83" s="71" t="s">
-        <v>348</v>
+        <v>225</v>
       </c>
       <c r="G83" s="90" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B84" s="89">
-        <f t="shared" si="2"/>
-        <v>65</v>
+        <f t="shared" ref="B84:B115" si="2">IF(C84="","",B83+1)</f>
+        <v>64</v>
       </c>
       <c r="C84" s="57" t="s">
-        <v>163</v>
-      </c>
-      <c r="D84" s="58">
-        <v>5</v>
+        <v>161</v>
+      </c>
+      <c r="D84" s="55" t="s">
+        <v>55</v>
       </c>
       <c r="E84" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="F84" s="59" t="s">
-        <v>63</v>
+      <c r="F84" s="71" t="s">
+        <v>348</v>
       </c>
       <c r="G84" s="90" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B85" s="89">
         <f t="shared" si="2"/>
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C85" s="57" t="s">
-        <v>346</v>
-      </c>
-      <c r="D85" s="55" t="s">
-        <v>19</v>
+        <v>163</v>
+      </c>
+      <c r="D85" s="58">
+        <v>5</v>
       </c>
       <c r="E85" s="57" t="s">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="F85" s="59" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="G85" s="90" t="s">
-        <v>347</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B86" s="89">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C86" s="57" t="s">
-        <v>219</v>
-      </c>
-      <c r="D86" s="58">
-        <v>2</v>
+        <v>346</v>
+      </c>
+      <c r="D86" s="55" t="s">
+        <v>19</v>
       </c>
       <c r="E86" s="57" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="F86" s="59" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="G86" s="90" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="87" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B87" s="89">
         <f t="shared" si="2"/>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C87" s="57" t="s">
-        <v>111</v>
-      </c>
-      <c r="D87" s="60" t="s">
-        <v>20</v>
-      </c>
-      <c r="E87" s="74" t="s">
-        <v>222</v>
+        <v>219</v>
+      </c>
+      <c r="D87" s="58">
+        <v>2</v>
+      </c>
+      <c r="E87" s="57" t="s">
+        <v>57</v>
       </c>
       <c r="F87" s="59" t="s">
         <v>117</v>
       </c>
       <c r="G87" s="90" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B88" s="89">
         <f t="shared" si="2"/>
-        <v>69</v>
-      </c>
-      <c r="C88" s="72" t="s">
-        <v>275</v>
-      </c>
-      <c r="D88" s="58" t="s">
-        <v>286</v>
+        <v>68</v>
+      </c>
+      <c r="C88" s="57" t="s">
+        <v>111</v>
+      </c>
+      <c r="D88" s="60" t="s">
+        <v>20</v>
       </c>
       <c r="E88" s="74" t="s">
-        <v>291</v>
-      </c>
-      <c r="F88" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="G88" s="98" t="s">
-        <v>312</v>
+        <v>222</v>
+      </c>
+      <c r="F88" s="59" t="s">
+        <v>117</v>
+      </c>
+      <c r="G88" s="90" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B89" s="89">
         <f t="shared" si="2"/>
-        <v>70</v>
-      </c>
-      <c r="C89" s="57" t="s">
-        <v>83</v>
-      </c>
-      <c r="D89" s="58">
-        <v>1</v>
-      </c>
-      <c r="E89" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="F89" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="G89" s="90" t="s">
-        <v>96</v>
+        <v>69</v>
+      </c>
+      <c r="C89" s="72" t="s">
+        <v>275</v>
+      </c>
+      <c r="D89" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E89" s="74" t="s">
+        <v>291</v>
+      </c>
+      <c r="F89" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="G89" s="98" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B90" s="89">
         <f t="shared" si="2"/>
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C90" s="57" t="s">
-        <v>256</v>
-      </c>
-      <c r="D90" s="55" t="s">
-        <v>257</v>
+        <v>83</v>
+      </c>
+      <c r="D90" s="58">
+        <v>1</v>
       </c>
       <c r="E90" s="57" t="s">
-        <v>258</v>
-      </c>
-      <c r="F90" s="59" t="s">
-        <v>259</v>
+        <v>57</v>
+      </c>
+      <c r="F90" s="62" t="s">
+        <v>117</v>
       </c>
       <c r="G90" s="90" t="s">
-        <v>260</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B91" s="89">
         <f t="shared" si="2"/>
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C91" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D91" s="58">
-        <v>1</v>
+        <v>256</v>
+      </c>
+      <c r="D91" s="55" t="s">
+        <v>257</v>
       </c>
       <c r="E91" s="57" t="s">
-        <v>57</v>
+        <v>258</v>
       </c>
       <c r="F91" s="59" t="s">
-        <v>115</v>
+        <v>259</v>
       </c>
       <c r="G91" s="90" t="s">
-        <v>94</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B92" s="89">
         <f t="shared" si="2"/>
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C92" s="57" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D92" s="58">
         <v>1</v>
@@ -4701,85 +4741,85 @@
       <c r="E92" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="F92" s="62" t="s">
-        <v>117</v>
+      <c r="F92" s="59" t="s">
+        <v>115</v>
       </c>
       <c r="G92" s="90" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B93" s="89">
         <f t="shared" si="2"/>
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C93" s="57" t="s">
-        <v>261</v>
-      </c>
-      <c r="D93" s="55" t="s">
-        <v>257</v>
+        <v>84</v>
+      </c>
+      <c r="D93" s="58">
+        <v>1</v>
       </c>
       <c r="E93" s="57" t="s">
-        <v>258</v>
-      </c>
-      <c r="F93" s="59" t="s">
-        <v>262</v>
+        <v>57</v>
+      </c>
+      <c r="F93" s="62" t="s">
+        <v>117</v>
       </c>
       <c r="G93" s="90" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B94" s="89">
         <f t="shared" si="2"/>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C94" s="57" t="s">
-        <v>221</v>
+        <v>261</v>
       </c>
       <c r="D94" s="55" t="s">
-        <v>20</v>
+        <v>257</v>
       </c>
       <c r="E94" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="F94" s="71" t="s">
-        <v>251</v>
-      </c>
-      <c r="G94" s="91" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
+        <v>258</v>
+      </c>
+      <c r="F94" s="59" t="s">
+        <v>262</v>
+      </c>
+      <c r="G94" s="90" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B95" s="89">
         <f t="shared" si="2"/>
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C95" s="57" t="s">
-        <v>87</v>
+        <v>221</v>
       </c>
       <c r="D95" s="55" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E95" s="57" t="s">
-        <v>61</v>
-      </c>
-      <c r="F95" s="63" t="s">
-        <v>115</v>
-      </c>
-      <c r="G95" s="90" t="s">
-        <v>89</v>
+        <v>116</v>
+      </c>
+      <c r="F95" s="71" t="s">
+        <v>251</v>
+      </c>
+      <c r="G95" s="91" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="96" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B96" s="89">
         <f t="shared" si="2"/>
-        <v>77</v>
-      </c>
-      <c r="C96" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="D96" s="64" t="s">
+        <v>76</v>
+      </c>
+      <c r="C96" s="57" t="s">
+        <v>87</v>
+      </c>
+      <c r="D96" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E96" s="57" t="s">
@@ -4788,818 +4828,818 @@
       <c r="F96" s="63" t="s">
         <v>115</v>
       </c>
-      <c r="G96" s="93" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="97" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="G96" s="90" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B97" s="89">
         <f t="shared" si="2"/>
-        <v>78</v>
-      </c>
-      <c r="C97" s="72" t="s">
-        <v>356</v>
-      </c>
-      <c r="D97" s="55" t="s">
-        <v>292</v>
-      </c>
-      <c r="E97" s="74" t="s">
-        <v>293</v>
-      </c>
-      <c r="F97" s="74" t="s">
-        <v>294</v>
-      </c>
-      <c r="G97" s="98" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="C97" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="D97" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="E97" s="57" t="s">
+        <v>61</v>
+      </c>
+      <c r="F97" s="63" t="s">
+        <v>115</v>
+      </c>
+      <c r="G97" s="93" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B98" s="89">
         <f t="shared" si="2"/>
-        <v>79</v>
-      </c>
-      <c r="C98" s="57" t="s">
-        <v>82</v>
-      </c>
-      <c r="D98" s="58">
-        <v>1</v>
-      </c>
-      <c r="E98" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="F98" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="G98" s="90" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+      <c r="C98" s="72" t="s">
+        <v>356</v>
+      </c>
+      <c r="D98" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="E98" s="74" t="s">
+        <v>293</v>
+      </c>
+      <c r="F98" s="74" t="s">
+        <v>294</v>
+      </c>
+      <c r="G98" s="98" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B99" s="89">
         <f t="shared" si="2"/>
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C99" s="57" t="s">
-        <v>155</v>
-      </c>
-      <c r="D99" s="60" t="s">
-        <v>45</v>
+        <v>82</v>
+      </c>
+      <c r="D99" s="58">
+        <v>1</v>
       </c>
       <c r="E99" s="57" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F99" s="59" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G99" s="90" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B100" s="89">
         <f t="shared" si="2"/>
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C100" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="D100" s="58">
-        <v>1</v>
+        <v>155</v>
+      </c>
+      <c r="D100" s="60" t="s">
+        <v>45</v>
       </c>
       <c r="E100" s="57" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="F100" s="59" t="s">
-        <v>42</v>
+        <v>111</v>
       </c>
       <c r="G100" s="90" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B101" s="89">
         <f t="shared" si="2"/>
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C101" s="57" t="s">
-        <v>108</v>
-      </c>
-      <c r="D101" s="55" t="s">
-        <v>19</v>
+        <v>86</v>
+      </c>
+      <c r="D101" s="58">
+        <v>1</v>
       </c>
       <c r="E101" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="F101" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="F101" s="71" t="s">
-        <v>115</v>
-      </c>
       <c r="G101" s="90" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B102" s="89">
         <f t="shared" si="2"/>
-        <v>83</v>
-      </c>
-      <c r="C102" s="61" t="s">
-        <v>76</v>
+        <v>82</v>
+      </c>
+      <c r="C102" s="57" t="s">
+        <v>108</v>
       </c>
       <c r="D102" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="E102" s="61" t="s">
-        <v>38</v>
-      </c>
-      <c r="F102" s="78" t="s">
-        <v>190</v>
-      </c>
-      <c r="G102" s="91" t="s">
-        <v>77</v>
+        <v>19</v>
+      </c>
+      <c r="E102" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="F102" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="G102" s="90" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B103" s="89">
         <f t="shared" si="2"/>
-        <v>84</v>
-      </c>
-      <c r="C103" s="65" t="s">
-        <v>248</v>
-      </c>
-      <c r="D103" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C103" s="61" t="s">
+        <v>76</v>
+      </c>
+      <c r="D103" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="E103" s="65" t="s">
-        <v>252</v>
-      </c>
-      <c r="F103" s="80" t="s">
-        <v>11</v>
-      </c>
-      <c r="G103" s="94" t="s">
-        <v>36</v>
+      <c r="E103" s="61" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" s="78" t="s">
+        <v>190</v>
+      </c>
+      <c r="G103" s="91" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B104" s="89">
         <f t="shared" si="2"/>
-        <v>85</v>
-      </c>
-      <c r="C104" s="66" t="s">
-        <v>154</v>
-      </c>
-      <c r="D104" s="67">
-        <v>1</v>
-      </c>
-      <c r="E104" s="66" t="s">
-        <v>34</v>
+        <v>84</v>
+      </c>
+      <c r="C104" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="D104" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E104" s="65" t="s">
+        <v>252</v>
       </c>
       <c r="F104" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="G104" s="95" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G104" s="94" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B105" s="89">
         <f t="shared" si="2"/>
-        <v>86</v>
-      </c>
-      <c r="C105" s="61" t="s">
-        <v>247</v>
-      </c>
-      <c r="D105" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="E105" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="C105" s="66" t="s">
+        <v>154</v>
+      </c>
+      <c r="D105" s="67">
+        <v>1</v>
+      </c>
+      <c r="E105" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="F105" s="78" t="s">
-        <v>253</v>
-      </c>
-      <c r="G105" s="91" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F105" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="G105" s="95" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B106" s="89">
         <f t="shared" si="2"/>
-        <v>87</v>
-      </c>
-      <c r="C106" s="57" t="s">
-        <v>189</v>
+        <v>86</v>
+      </c>
+      <c r="C106" s="61" t="s">
+        <v>247</v>
       </c>
       <c r="D106" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="E106" s="57" t="s">
-        <v>190</v>
-      </c>
-      <c r="F106" s="59" t="s">
-        <v>244</v>
-      </c>
-      <c r="G106" s="90" t="s">
-        <v>246</v>
+      <c r="E106" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F106" s="78" t="s">
+        <v>253</v>
+      </c>
+      <c r="G106" s="91" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B107" s="89">
         <f t="shared" si="2"/>
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C107" s="57" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="D107" s="55" t="s">
         <v>20</v>
       </c>
       <c r="E107" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="F107" s="59" t="s">
         <v>244</v>
       </c>
-      <c r="F107" s="59" t="s">
-        <v>34</v>
-      </c>
       <c r="G107" s="90" t="s">
-        <v>191</v>
+        <v>246</v>
       </c>
     </row>
     <row r="108" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B108" s="89">
         <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="C108" s="57" t="s">
+        <v>245</v>
+      </c>
+      <c r="D108" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E108" s="57" t="s">
+        <v>244</v>
+      </c>
+      <c r="F108" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="G108" s="90" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B109" s="89">
+        <f t="shared" si="2"/>
         <v>89</v>
       </c>
-      <c r="C108" s="57" t="s">
+      <c r="C109" s="57" t="s">
         <v>374</v>
       </c>
-      <c r="D108" s="55" t="s">
+      <c r="D109" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E108" s="126" t="s">
+      <c r="E109" s="126" t="s">
         <v>365</v>
       </c>
-      <c r="F108" s="126" t="s">
+      <c r="F109" s="126" t="s">
         <v>35</v>
       </c>
-      <c r="G108" s="98" t="s">
+      <c r="G109" s="98" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="109" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B109" s="89">
-        <f>IF(C109="","",B108+1)</f>
-        <v>90</v>
-      </c>
-      <c r="C109" s="57" t="s">
-        <v>359</v>
-      </c>
-      <c r="D109" s="58">
-        <v>1</v>
-      </c>
-      <c r="E109" s="57" t="s">
-        <v>226</v>
-      </c>
-      <c r="F109" s="71" t="s">
-        <v>250</v>
-      </c>
-      <c r="G109" s="90" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:7" ht="66" x14ac:dyDescent="0.3">
       <c r="B110" s="89">
         <f>IF(C110="","",B109+1)</f>
-        <v>91</v>
-      </c>
-      <c r="C110" s="68" t="s">
-        <v>134</v>
-      </c>
-      <c r="D110" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E110" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="F110" s="81" t="s">
-        <v>367</v>
-      </c>
-      <c r="G110" s="96" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="C110" s="57" t="s">
+        <v>359</v>
+      </c>
+      <c r="D110" s="58">
+        <v>1</v>
+      </c>
+      <c r="E110" s="57" t="s">
+        <v>226</v>
+      </c>
+      <c r="F110" s="71" t="s">
+        <v>250</v>
+      </c>
+      <c r="G110" s="90" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
       <c r="B111" s="89">
         <f>IF(C111="","",B110+1)</f>
-        <v>92</v>
-      </c>
-      <c r="C111" s="75" t="s">
-        <v>276</v>
-      </c>
-      <c r="D111" s="76" t="s">
-        <v>286</v>
-      </c>
-      <c r="E111" s="85" t="s">
-        <v>264</v>
-      </c>
-      <c r="F111" s="86" t="s">
-        <v>295</v>
-      </c>
-      <c r="G111" s="99" t="s">
-        <v>314</v>
+        <v>91</v>
+      </c>
+      <c r="C111" s="68" t="s">
+        <v>134</v>
+      </c>
+      <c r="D111" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F111" s="81" t="s">
+        <v>367</v>
+      </c>
+      <c r="G111" s="96" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="112" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B112" s="89">
         <f>IF(C112="","",B111+1)</f>
-        <v>93</v>
-      </c>
-      <c r="C112" s="72" t="s">
-        <v>277</v>
-      </c>
-      <c r="D112" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="C112" s="75" t="s">
+        <v>276</v>
+      </c>
+      <c r="D112" s="76" t="s">
         <v>286</v>
       </c>
-      <c r="E112" s="74" t="s">
+      <c r="E112" s="85" t="s">
         <v>264</v>
       </c>
-      <c r="F112" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="G112" s="98" t="s">
-        <v>315</v>
+      <c r="F112" s="86" t="s">
+        <v>295</v>
+      </c>
+      <c r="G112" s="99" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B113" s="89">
-        <f t="shared" si="2"/>
-        <v>94</v>
-      </c>
-      <c r="C113" s="57" t="s">
-        <v>180</v>
-      </c>
-      <c r="D113" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="E113" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="F113" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="G113" s="90" t="s">
-        <v>181</v>
+        <f>IF(C113="","",B112+1)</f>
+        <v>93</v>
+      </c>
+      <c r="C113" s="72" t="s">
+        <v>277</v>
+      </c>
+      <c r="D113" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E113" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="F113" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="G113" s="98" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B114" s="89">
         <f t="shared" si="2"/>
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C114" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="D114" s="58">
-        <v>1</v>
-      </c>
-      <c r="E114" s="59" t="s">
+        <v>180</v>
+      </c>
+      <c r="D114" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E114" s="71" t="s">
         <v>118</v>
       </c>
       <c r="F114" s="71" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G114" s="90" t="s">
-        <v>350</v>
+        <v>181</v>
       </c>
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B115" s="89">
-        <f>IF(C115="","",B114+1)</f>
-        <v>96</v>
+        <f t="shared" si="2"/>
+        <v>95</v>
       </c>
       <c r="C115" s="57" t="s">
-        <v>230</v>
+        <v>202</v>
       </c>
       <c r="D115" s="58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="F115" s="59" t="s">
-        <v>119</v>
+      <c r="F115" s="71" t="s">
+        <v>194</v>
       </c>
       <c r="G115" s="90" t="s">
-        <v>231</v>
+        <v>350</v>
       </c>
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B116" s="89">
         <f>IF(C116="","",B115+1)</f>
-        <v>97</v>
-      </c>
-      <c r="C116" s="72" t="s">
-        <v>278</v>
-      </c>
-      <c r="D116" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E116" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="F116" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="G116" s="98" t="s">
-        <v>316</v>
+        <v>96</v>
+      </c>
+      <c r="C116" s="57" t="s">
+        <v>230</v>
+      </c>
+      <c r="D116" s="58">
+        <v>2</v>
+      </c>
+      <c r="E116" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="F116" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="G116" s="90" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B117" s="89">
-        <f t="shared" ref="B117:B141" si="3">IF(C117="","",B116+1)</f>
-        <v>98</v>
-      </c>
-      <c r="C117" s="68" t="s">
-        <v>130</v>
-      </c>
-      <c r="D117" s="69">
-        <v>1</v>
-      </c>
-      <c r="E117" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="F117" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="G117" s="96" t="s">
-        <v>132</v>
+        <f>IF(C117="","",B116+1)</f>
+        <v>97</v>
+      </c>
+      <c r="C117" s="72" t="s">
+        <v>278</v>
+      </c>
+      <c r="D117" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E117" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="F117" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="G117" s="98" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="118" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B118" s="89">
-        <f t="shared" si="3"/>
-        <v>99</v>
-      </c>
-      <c r="C118" s="72" t="s">
-        <v>279</v>
-      </c>
-      <c r="D118" s="55" t="s">
-        <v>290</v>
-      </c>
-      <c r="E118" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="F118" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="G118" s="98" t="s">
-        <v>317</v>
+        <f t="shared" ref="B118:B142" si="3">IF(C118="","",B117+1)</f>
+        <v>98</v>
+      </c>
+      <c r="C118" s="68" t="s">
+        <v>130</v>
+      </c>
+      <c r="D118" s="69">
+        <v>1</v>
+      </c>
+      <c r="E118" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F118" s="82" t="s">
+        <v>13</v>
+      </c>
+      <c r="G118" s="96" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="119" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B119" s="89">
         <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-      <c r="C119" s="57" t="s">
-        <v>145</v>
-      </c>
-      <c r="D119" s="58">
-        <v>1</v>
-      </c>
-      <c r="E119" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="F119" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="G119" s="90" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="120" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+      <c r="C119" s="72" t="s">
+        <v>279</v>
+      </c>
+      <c r="D119" s="55" t="s">
+        <v>290</v>
+      </c>
+      <c r="E119" s="74" t="s">
+        <v>264</v>
+      </c>
+      <c r="F119" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="G119" s="98" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B120" s="89">
         <f t="shared" si="3"/>
-        <v>101</v>
-      </c>
-      <c r="C120" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="D120" s="69">
+        <v>100</v>
+      </c>
+      <c r="C120" s="57" t="s">
+        <v>145</v>
+      </c>
+      <c r="D120" s="58">
         <v>1</v>
       </c>
-      <c r="E120" s="68" t="s">
+      <c r="E120" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="F120" s="83" t="s">
-        <v>379</v>
-      </c>
-      <c r="G120" s="96" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="121" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F120" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="G120" s="90" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B121" s="89">
         <f t="shared" si="3"/>
-        <v>102</v>
-      </c>
-      <c r="C121" s="77" t="s">
-        <v>280</v>
-      </c>
-      <c r="D121" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="E121" s="87" t="s">
-        <v>264</v>
-      </c>
-      <c r="F121" s="88" t="s">
-        <v>296</v>
-      </c>
-      <c r="G121" s="100" t="s">
-        <v>318</v>
+        <v>101</v>
+      </c>
+      <c r="C121" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="D121" s="69">
+        <v>1</v>
+      </c>
+      <c r="E121" s="68" t="s">
+        <v>118</v>
+      </c>
+      <c r="F121" s="83" t="s">
+        <v>379</v>
+      </c>
+      <c r="G121" s="96" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="122" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B122" s="89">
         <f t="shared" si="3"/>
-        <v>103</v>
-      </c>
-      <c r="C122" s="57" t="s">
-        <v>236</v>
-      </c>
-      <c r="D122" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="E122" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="F122" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="G122" s="90" t="s">
-        <v>239</v>
+        <v>102</v>
+      </c>
+      <c r="C122" s="77" t="s">
+        <v>280</v>
+      </c>
+      <c r="D122" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="E122" s="87" t="s">
+        <v>264</v>
+      </c>
+      <c r="F122" s="88" t="s">
+        <v>296</v>
+      </c>
+      <c r="G122" s="100" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B123" s="89">
         <f t="shared" si="3"/>
-        <v>104</v>
-      </c>
-      <c r="C123" s="63" t="s">
-        <v>138</v>
-      </c>
-      <c r="D123" s="64" t="s">
-        <v>19</v>
-      </c>
-      <c r="E123" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="C123" s="57" t="s">
+        <v>236</v>
+      </c>
+      <c r="D123" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E123" s="59" t="s">
         <v>118</v>
       </c>
-      <c r="F123" s="84" t="s">
-        <v>194</v>
-      </c>
-      <c r="G123" s="93" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="124" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="F123" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="G123" s="90" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="124" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B124" s="89">
         <f t="shared" si="3"/>
-        <v>105</v>
-      </c>
-      <c r="C124" s="57" t="s">
-        <v>187</v>
-      </c>
-      <c r="D124" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="E124" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="C124" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="D124" s="64" t="s">
+        <v>19</v>
+      </c>
+      <c r="E124" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="F124" s="71" t="s">
-        <v>371</v>
-      </c>
-      <c r="G124" s="90" t="s">
-        <v>188</v>
+      <c r="F124" s="84" t="s">
+        <v>194</v>
+      </c>
+      <c r="G124" s="93" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="125" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B125" s="89">
         <f t="shared" si="3"/>
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C125" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="D125" s="58">
-        <v>1</v>
-      </c>
-      <c r="E125" s="59" t="s">
+        <v>187</v>
+      </c>
+      <c r="D125" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E125" s="57" t="s">
         <v>118</v>
       </c>
       <c r="F125" s="71" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="G125" s="90" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="126" spans="2:7" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="126" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B126" s="89">
         <f t="shared" si="3"/>
-        <v>107</v>
-      </c>
-      <c r="C126" s="68" t="s">
-        <v>208</v>
-      </c>
-      <c r="D126" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E126" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="F126" s="82" t="s">
-        <v>16</v>
-      </c>
-      <c r="G126" s="96" t="s">
-        <v>195</v>
+        <v>106</v>
+      </c>
+      <c r="C126" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="D126" s="58">
+        <v>1</v>
+      </c>
+      <c r="E126" s="59" t="s">
+        <v>118</v>
+      </c>
+      <c r="F126" s="71" t="s">
+        <v>377</v>
+      </c>
+      <c r="G126" s="90" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="127" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B127" s="89">
         <f t="shared" si="3"/>
-        <v>108</v>
-      </c>
-      <c r="C127" s="57" t="s">
-        <v>210</v>
-      </c>
-      <c r="D127" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="C127" s="68" t="s">
+        <v>208</v>
+      </c>
+      <c r="D127" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E127" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="F127" s="57" t="s">
+      <c r="E127" s="70" t="s">
         <v>194</v>
       </c>
-      <c r="G127" s="90" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="128" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="F127" s="82" t="s">
+        <v>16</v>
+      </c>
+      <c r="G127" s="96" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B128" s="89">
         <f t="shared" si="3"/>
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C128" s="57" t="s">
-        <v>149</v>
+        <v>210</v>
       </c>
       <c r="D128" s="55" t="s">
         <v>19</v>
       </c>
       <c r="E128" s="57" t="s">
-        <v>119</v>
-      </c>
-      <c r="F128" s="71" t="s">
-        <v>351</v>
+        <v>118</v>
+      </c>
+      <c r="F128" s="57" t="s">
+        <v>194</v>
       </c>
       <c r="G128" s="90" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="129" spans="2:7" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="129" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B129" s="89">
         <f t="shared" si="3"/>
-        <v>110</v>
-      </c>
-      <c r="C129" s="72" t="s">
-        <v>281</v>
-      </c>
-      <c r="D129" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E129" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="F129" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="G129" s="98" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="130" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="C129" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="D129" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129" s="57" t="s">
+        <v>119</v>
+      </c>
+      <c r="F129" s="71" t="s">
+        <v>351</v>
+      </c>
+      <c r="G129" s="90" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B130" s="89">
         <f t="shared" si="3"/>
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C130" s="72" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D130" s="58" t="s">
         <v>286</v>
       </c>
       <c r="E130" s="74" t="s">
-        <v>297</v>
+        <v>265</v>
       </c>
       <c r="F130" s="74" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="G130" s="98" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="131" spans="2:7" x14ac:dyDescent="0.3">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B131" s="89">
         <f t="shared" si="3"/>
-        <v>112</v>
-      </c>
-      <c r="C131" s="57" t="s">
-        <v>354</v>
-      </c>
-      <c r="D131" s="58">
-        <v>1</v>
-      </c>
-      <c r="E131" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="F131" s="59" t="s">
-        <v>68</v>
-      </c>
-      <c r="G131" s="90" t="s">
-        <v>148</v>
+        <v>111</v>
+      </c>
+      <c r="C131" s="72" t="s">
+        <v>282</v>
+      </c>
+      <c r="D131" s="58" t="s">
+        <v>286</v>
+      </c>
+      <c r="E131" s="74" t="s">
+        <v>297</v>
+      </c>
+      <c r="F131" s="74" t="s">
+        <v>298</v>
+      </c>
+      <c r="G131" s="98" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="132" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B132" s="89">
         <f t="shared" si="3"/>
-        <v>113</v>
-      </c>
-      <c r="C132" s="72" t="s">
-        <v>283</v>
-      </c>
-      <c r="D132" s="55" t="s">
-        <v>299</v>
-      </c>
-      <c r="E132" s="74" t="s">
-        <v>300</v>
-      </c>
-      <c r="F132" s="74" t="s">
-        <v>301</v>
-      </c>
-      <c r="G132" s="98" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="133" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+      <c r="C132" s="57" t="s">
+        <v>354</v>
+      </c>
+      <c r="D132" s="58">
+        <v>1</v>
+      </c>
+      <c r="E132" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="F132" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="G132" s="90" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="133" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B133" s="89">
         <f t="shared" si="3"/>
-        <v>114</v>
-      </c>
-      <c r="C133" s="57" t="s">
-        <v>352</v>
-      </c>
-      <c r="D133" s="58">
-        <v>2</v>
-      </c>
-      <c r="E133" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="F133" s="71" t="s">
-        <v>376</v>
-      </c>
-      <c r="G133" s="90" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="134" spans="2:7" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+      <c r="C133" s="72" t="s">
+        <v>283</v>
+      </c>
+      <c r="D133" s="55" t="s">
+        <v>299</v>
+      </c>
+      <c r="E133" s="74" t="s">
+        <v>300</v>
+      </c>
+      <c r="F133" s="74" t="s">
+        <v>301</v>
+      </c>
+      <c r="G133" s="98" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7" ht="33" x14ac:dyDescent="0.3">
       <c r="B134" s="89">
         <f t="shared" si="3"/>
-        <v>115</v>
-      </c>
-      <c r="C134" s="72" t="s">
-        <v>284</v>
-      </c>
-      <c r="D134" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E134" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="F134" s="74" t="s">
-        <v>300</v>
-      </c>
-      <c r="G134" s="98" t="s">
-        <v>322</v>
+        <v>114</v>
+      </c>
+      <c r="C134" s="57" t="s">
+        <v>352</v>
+      </c>
+      <c r="D134" s="58">
+        <v>2</v>
+      </c>
+      <c r="E134" s="59" t="s">
+        <v>119</v>
+      </c>
+      <c r="F134" s="71" t="s">
+        <v>376</v>
+      </c>
+      <c r="G134" s="90" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B135" s="89">
         <f t="shared" si="3"/>
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C135" s="72" t="s">
-        <v>285</v>
-      </c>
-      <c r="D135" s="55" t="s">
-        <v>290</v>
+        <v>284</v>
+      </c>
+      <c r="D135" s="58" t="s">
+        <v>286</v>
       </c>
       <c r="E135" s="74" t="s">
         <v>265</v>
@@ -5608,134 +5648,155 @@
         <v>300</v>
       </c>
       <c r="G135" s="98" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="136" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B136" s="89">
         <f t="shared" si="3"/>
+        <v>116</v>
+      </c>
+      <c r="C136" s="72" t="s">
+        <v>285</v>
+      </c>
+      <c r="D136" s="55" t="s">
+        <v>290</v>
+      </c>
+      <c r="E136" s="74" t="s">
+        <v>265</v>
+      </c>
+      <c r="F136" s="74" t="s">
+        <v>300</v>
+      </c>
+      <c r="G136" s="98" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B137" s="89">
+        <f t="shared" si="3"/>
         <v>117</v>
       </c>
-      <c r="C136" s="57" t="s">
+      <c r="C137" s="57" t="s">
         <v>166</v>
       </c>
-      <c r="D136" s="55" t="s">
+      <c r="D137" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="E136" s="57" t="s">
+      <c r="E137" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="F136" s="71" t="s">
+      <c r="F137" s="71" t="s">
         <v>368</v>
       </c>
-      <c r="G136" s="90" t="s">
+      <c r="G137" s="90" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="137" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B137" s="121">
+    <row r="138" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B138" s="121">
         <f t="shared" si="3"/>
         <v>118</v>
       </c>
-      <c r="C137" s="122" t="s">
+      <c r="C138" s="122" t="s">
         <v>237</v>
       </c>
-      <c r="D137" s="127" t="s">
+      <c r="D138" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="E137" s="123" t="s">
+      <c r="E138" s="123" t="s">
         <v>119</v>
       </c>
-      <c r="F137" s="124" t="s">
+      <c r="F138" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="G137" s="125" t="s">
+      <c r="G138" s="125" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B138" s="89">
+    <row r="139" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B139" s="89">
         <f t="shared" si="3"/>
         <v>119</v>
       </c>
-      <c r="C138" s="57" t="s">
+      <c r="C139" s="57" t="s">
         <v>233</v>
       </c>
-      <c r="D138" s="55" t="s">
+      <c r="D139" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="E138" s="59" t="s">
+      <c r="E139" s="59" t="s">
         <v>234</v>
       </c>
-      <c r="F138" s="71" t="s">
+      <c r="F139" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="G138" s="90" t="s">
+      <c r="G139" s="90" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="139" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B139" s="89">
+    <row r="140" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B140" s="89">
         <f t="shared" si="3"/>
         <v>120</v>
       </c>
-      <c r="C139" s="57" t="s">
+      <c r="C140" s="57" t="s">
         <v>182</v>
       </c>
-      <c r="D139" s="55" t="s">
+      <c r="D140" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="57" t="s">
+      <c r="E140" s="57" t="s">
         <v>119</v>
       </c>
-      <c r="F139" s="71" t="s">
+      <c r="F140" s="71" t="s">
         <v>372</v>
       </c>
-      <c r="G139" s="90" t="s">
+      <c r="G140" s="90" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="140" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B140" s="101">
+    <row r="141" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B141" s="101">
         <f t="shared" si="3"/>
         <v>121</v>
       </c>
-      <c r="C140" s="116" t="s">
+      <c r="C141" s="116" t="s">
         <v>353</v>
       </c>
-      <c r="D140" s="117">
+      <c r="D141" s="117">
         <v>1</v>
       </c>
-      <c r="E140" s="118" t="s">
+      <c r="E141" s="118" t="s">
         <v>119</v>
       </c>
-      <c r="F140" s="119" t="s">
+      <c r="F141" s="119" t="s">
         <v>378</v>
       </c>
-      <c r="G140" s="120" t="s">
+      <c r="G141" s="120" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="141" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B141" s="21" t="str">
+    <row r="142" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B142" s="21" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="C141"/>
-      <c r="D141"/>
-      <c r="E141" s="54"/>
-      <c r="F141" s="54"/>
-      <c r="G141" s="54"/>
+      <c r="C142"/>
+      <c r="D142"/>
+      <c r="E142" s="54"/>
+      <c r="F142" s="54"/>
+      <c r="G142" s="54"/>
     </row>
   </sheetData>
-  <autoFilter ref="C19:G140" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C20:G141">
-      <sortCondition ref="C19:C140"/>
+  <autoFilter ref="C20:G141" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C21:G142">
+      <sortCondition ref="C20:C141"/>
     </sortState>
   </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:G19"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/document/IDD.xlsx
+++ b/document/IDD.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\SoC_Design\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1559E386-A115-4D21-BDF5-69990F8F99FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80560313-BE1B-4977-BABB-45AB0B7B0638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6405" yWindow="2040" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPU" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CPU!$C$20:$G$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CPU!$C$20:$G$138</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="621" uniqueCount="378">
   <si>
     <t>Signal</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -109,14 +109,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>o_arbiter_req</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>i_arbiter_gnt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>DATA_BIT</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -154,10 +146,6 @@
   </si>
   <si>
     <t>to D-MEM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>to Arbiter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1102,9 +1090,6 @@
     <t>u_mem_wb_bridge</t>
   </si>
   <si>
-    <t>w_ex_arbiter_req</t>
-  </si>
-  <si>
     <t>w_ex_beq_taken</t>
   </si>
   <si>
@@ -1130,9 +1115,6 @@
   </si>
   <si>
     <t>w_id_load_unsigned</t>
-  </si>
-  <si>
-    <t>w_mem_arbiter_req</t>
   </si>
   <si>
     <t>w_mem_branch_taken</t>
@@ -1192,9 +1174,6 @@
 u_load_stall_unit</t>
   </si>
   <si>
-    <t>o_arbiter_req</t>
-  </si>
-  <si>
     <t>o_d_mem_strb</t>
   </si>
   <si>
@@ -1215,9 +1194,6 @@
     <t>u_memtoreg_mux</t>
   </si>
   <si>
-    <t>Arbiter Request (EX)</t>
-  </si>
-  <si>
     <t>Branch Equal Taken Flag</t>
   </si>
   <si>
@@ -1242,16 +1218,10 @@
     <t>MemWrite Strobe (EX)</t>
   </si>
   <si>
-    <t>Arbiter Request (ID)</t>
-  </si>
-  <si>
     <t>Load Unsigned Flag (ID)</t>
   </si>
   <si>
     <t>rt or rd Register (ID)</t>
-  </si>
-  <si>
-    <t>Arbiter Request (MEM)</t>
   </si>
   <si>
     <t>Total Branch Taken Flag (MEM)</t>
@@ -1426,10 +1396,6 @@
   </si>
   <si>
     <t>w_wb_ctr_memtoreg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w_id_arbiter_req</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1625,6 +1591,14 @@
     <t>AXI-NoC Interface</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>i_arbiter_wr_gnt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i_arbiter_rd_gnt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -1634,7 +1608,7 @@
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="177" formatCode="0&quot;일&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1667,15 +1641,8 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1708,12 +1675,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC1F0C8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2120,7 +2081,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2340,18 +2301,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2376,12 +2328,6 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2412,15 +2358,9 @@
     <xf numFmtId="176" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2508,6 +2448,21 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2525,21 +2480,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2880,7 +2820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:H142"/>
+  <dimension ref="B1:H139"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
@@ -2896,18 +2836,18 @@
   <sheetData>
     <row r="1" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="129" t="s">
-        <v>358</v>
-      </c>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="131"/>
+      <c r="B2" s="127" t="s">
+        <v>348</v>
+      </c>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="128"/>
+      <c r="F2" s="128"/>
+      <c r="G2" s="129"/>
     </row>
     <row r="3" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="106" t="s">
-        <v>40</v>
+      <c r="B3" s="99" t="s">
+        <v>37</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>0</v>
@@ -2935,11 +2875,11 @@
       <c r="D4" s="30">
         <v>1</v>
       </c>
-      <c r="E4" s="108" t="s">
+      <c r="E4" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="109" t="s">
-        <v>22</v>
+      <c r="F4" s="102" t="s">
+        <v>20</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>8</v>
@@ -2955,11 +2895,11 @@
       <c r="D5" s="31">
         <v>1</v>
       </c>
-      <c r="E5" s="110" t="s">
+      <c r="E5" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="111" t="s">
-        <v>22</v>
+      <c r="F5" s="104" t="s">
+        <v>20</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>8</v>
@@ -2973,16 +2913,16 @@
         <v>9</v>
       </c>
       <c r="D6" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="48" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="48" t="s">
-        <v>21</v>
-      </c>
       <c r="F6" s="48" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -2996,13 +2936,13 @@
         <v>1</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3013,16 +2953,16 @@
         <v>11</v>
       </c>
       <c r="D8" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="49" t="s">
-        <v>22</v>
-      </c>
       <c r="F8" s="49" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -3033,16 +2973,16 @@
         <v>12</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="112" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="113" t="s">
-        <v>22</v>
+        <v>17</v>
+      </c>
+      <c r="E9" s="105" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="106" t="s">
+        <v>20</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.3">
@@ -3056,13 +2996,13 @@
         <v>1</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.3">
@@ -3076,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.3">
@@ -3093,16 +3033,16 @@
         <v>15</v>
       </c>
       <c r="D12" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="27" t="s">
-        <v>22</v>
-      </c>
       <c r="F12" s="27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.3">
@@ -3113,16 +3053,16 @@
         <v>16</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E13" s="53" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3130,19 +3070,19 @@
         <v>11</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E14" s="53" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F14" s="53" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.3">
@@ -3150,19 +3090,19 @@
         <v>12</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>17</v>
+        <v>376</v>
       </c>
       <c r="D15" s="45">
         <v>1</v>
       </c>
-      <c r="E15" s="114" t="s">
+      <c r="E15" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="114" t="s">
-        <v>24</v>
+      <c r="F15" s="107" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -3170,2628 +3110,2565 @@
         <v>13</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>18</v>
+        <v>377</v>
       </c>
       <c r="D16" s="46">
         <v>1</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="115" t="s">
         <v>22</v>
       </c>
+      <c r="F16" s="108" t="s">
+        <v>20</v>
+      </c>
       <c r="G16" s="16" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="135">
+      <c r="B17" s="122">
         <v>14</v>
       </c>
-      <c r="C17" s="136" t="s">
-        <v>381</v>
-      </c>
-      <c r="D17" s="137" t="s">
-        <v>382</v>
-      </c>
-      <c r="E17" s="136" t="s">
-        <v>383</v>
-      </c>
-      <c r="F17" s="138" t="s">
-        <v>384</v>
-      </c>
-      <c r="G17" s="139" t="s">
-        <v>385</v>
+      <c r="C17" s="123" t="s">
+        <v>371</v>
+      </c>
+      <c r="D17" s="124" t="s">
+        <v>372</v>
+      </c>
+      <c r="E17" s="123" t="s">
+        <v>373</v>
+      </c>
+      <c r="F17" s="125" t="s">
+        <v>374</v>
+      </c>
+      <c r="G17" s="126" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="19" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="132" t="s">
-        <v>357</v>
-      </c>
-      <c r="C19" s="133"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="134"/>
+      <c r="B19" s="130" t="s">
+        <v>347</v>
+      </c>
+      <c r="C19" s="131"/>
+      <c r="D19" s="131"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="132"/>
     </row>
     <row r="20" spans="2:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="107" t="s">
-        <v>40</v>
+      <c r="B20" s="100" t="s">
+        <v>37</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="102">
+      <c r="B21" s="95">
         <f>IF(C21="","",1)</f>
         <v>1</v>
       </c>
-      <c r="C21" s="103" t="s">
-        <v>168</v>
-      </c>
-      <c r="D21" s="104">
+      <c r="C21" s="96" t="s">
+        <v>165</v>
+      </c>
+      <c r="D21" s="97">
         <v>1</v>
       </c>
-      <c r="E21" s="103" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="128" t="s">
+      <c r="E21" s="96" t="s">
         <v>63</v>
       </c>
-      <c r="G21" s="105" t="s">
-        <v>70</v>
+      <c r="F21" s="121" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="98" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B22" s="89">
-        <f t="shared" ref="B22:B51" si="0">IF(C22="","",B21+1)</f>
+      <c r="B22" s="84">
+        <f t="shared" ref="B22:B50" si="0">IF(C22="","",B21+1)</f>
         <v>2</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D22" s="58">
         <v>4</v>
       </c>
       <c r="E22" s="57" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="F22" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22" s="90" t="s">
-        <v>65</v>
+        <v>61</v>
+      </c>
+      <c r="G22" s="85" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B23" s="89">
+      <c r="B23" s="84">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="C23" s="57" t="s">
+        <v>316</v>
+      </c>
+      <c r="D23" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="71" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="85" t="s">
         <v>325</v>
       </c>
-      <c r="D23" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="57" t="s">
-        <v>198</v>
-      </c>
-      <c r="F23" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" s="90" t="s">
-        <v>334</v>
-      </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" s="89">
+      <c r="B24" s="84">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D24" s="55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24" s="57" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F24" s="71" t="s">
-        <v>193</v>
-      </c>
-      <c r="G24" s="90" t="s">
-        <v>335</v>
+        <v>190</v>
+      </c>
+      <c r="G24" s="85" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B25" s="89">
+      <c r="B25" s="84">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="C25" s="57" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D25" s="58">
         <v>1</v>
       </c>
       <c r="E25" s="57" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F25" s="71" t="s">
-        <v>326</v>
-      </c>
-      <c r="G25" s="90" t="s">
-        <v>242</v>
+        <v>317</v>
+      </c>
+      <c r="G25" s="85" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B26" s="89">
+      <c r="B26" s="84">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="C26" s="57" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D26" s="55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E26" s="57" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F26" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="G26" s="90" t="s">
-        <v>136</v>
+        <v>115</v>
+      </c>
+      <c r="G26" s="85" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B27" s="89">
+      <c r="B27" s="84">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C27" s="57" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D27" s="58">
         <v>1</v>
       </c>
       <c r="E27" s="57" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F27" s="71" t="s">
-        <v>327</v>
-      </c>
-      <c r="G27" s="90" t="s">
-        <v>71</v>
+        <v>318</v>
+      </c>
+      <c r="G27" s="85" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="89">
+      <c r="B28" s="84">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C28" s="57" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D28" s="58">
         <v>4</v>
       </c>
       <c r="E28" s="57" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F28" s="59" t="s">
-        <v>324</v>
-      </c>
-      <c r="G28" s="90" t="s">
-        <v>125</v>
+        <v>315</v>
+      </c>
+      <c r="G28" s="85" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B29" s="89">
+      <c r="B29" s="84">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="C29" s="57" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D29" s="55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E29" s="57" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F29" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="G29" s="90" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B30" s="89">
+        <v>61</v>
+      </c>
+      <c r="G29" s="85" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B30" s="84">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C30" s="57" t="s">
-        <v>266</v>
-      </c>
-      <c r="D30" s="73" t="s">
-        <v>286</v>
-      </c>
-      <c r="E30" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="F30" s="71" t="s">
-        <v>264</v>
-      </c>
-      <c r="G30" s="97" t="s">
-        <v>302</v>
+      <c r="C30" s="72" t="s">
+        <v>263</v>
+      </c>
+      <c r="D30" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="E30" s="73" t="s">
+        <v>282</v>
+      </c>
+      <c r="F30" s="73" t="s">
+        <v>283</v>
+      </c>
+      <c r="G30" s="92" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B31" s="89">
+      <c r="B31" s="84">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="C31" s="72" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D31" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E31" s="74" t="s">
-        <v>287</v>
-      </c>
-      <c r="F31" s="74" t="s">
-        <v>288</v>
-      </c>
-      <c r="G31" s="98" t="s">
-        <v>303</v>
+        <v>281</v>
+      </c>
+      <c r="E31" s="73" t="s">
+        <v>284</v>
+      </c>
+      <c r="F31" s="73" t="s">
+        <v>283</v>
+      </c>
+      <c r="G31" s="92" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B32" s="89">
+      <c r="B32" s="84">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="C32" s="72" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D32" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E32" s="74" t="s">
-        <v>289</v>
-      </c>
-      <c r="F32" s="74" t="s">
-        <v>288</v>
-      </c>
-      <c r="G32" s="98" t="s">
-        <v>304</v>
+        <v>281</v>
+      </c>
+      <c r="E32" s="73" t="s">
+        <v>284</v>
+      </c>
+      <c r="F32" s="73" t="s">
+        <v>283</v>
+      </c>
+      <c r="G32" s="92" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B33" s="89">
+      <c r="B33" s="84">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="C33" s="72" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D33" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E33" s="74" t="s">
-        <v>289</v>
-      </c>
-      <c r="F33" s="74" t="s">
-        <v>288</v>
-      </c>
-      <c r="G33" s="98" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B34" s="89">
+        <v>281</v>
+      </c>
+      <c r="E33" s="73" t="s">
+        <v>282</v>
+      </c>
+      <c r="F33" s="73" t="s">
+        <v>283</v>
+      </c>
+      <c r="G33" s="92" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B34" s="84">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C34" s="72" t="s">
-        <v>270</v>
-      </c>
-      <c r="D34" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E34" s="74" t="s">
-        <v>287</v>
-      </c>
-      <c r="F34" s="74" t="s">
-        <v>288</v>
-      </c>
-      <c r="G34" s="98" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B35" s="89">
+      <c r="C34" s="57" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="58">
+        <v>3</v>
+      </c>
+      <c r="E34" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="F34" s="71" t="s">
+        <v>319</v>
+      </c>
+      <c r="G34" s="85" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B35" s="84">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="C35" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="D35" s="58">
-        <v>3</v>
-      </c>
-      <c r="E35" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="F35" s="71" t="s">
-        <v>328</v>
-      </c>
-      <c r="G35" s="90" t="s">
-        <v>141</v>
+        <v>155</v>
+      </c>
+      <c r="D35" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="57" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="59" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" s="85" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B36" s="89">
+      <c r="B36" s="84">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="C36" s="57" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D36" s="55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E36" s="57" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F36" s="59" t="s">
-        <v>52</v>
-      </c>
-      <c r="G36" s="90" t="s">
-        <v>333</v>
+        <v>32</v>
+      </c>
+      <c r="G36" s="85" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B37" s="89">
+      <c r="B37" s="84">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="C37" s="57" t="s">
-        <v>172</v>
-      </c>
-      <c r="D37" s="55" t="s">
-        <v>20</v>
+        <v>106</v>
+      </c>
+      <c r="D37" s="58">
+        <v>1</v>
       </c>
       <c r="E37" s="57" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="F37" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="G37" s="90" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B38" s="89">
+        <v>64</v>
+      </c>
+      <c r="G37" s="85" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B38" s="84">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="C38" s="57" t="s">
-        <v>109</v>
+        <v>320</v>
       </c>
       <c r="D38" s="58">
         <v>1</v>
       </c>
-      <c r="E38" s="57" t="s">
-        <v>117</v>
-      </c>
-      <c r="F38" s="59" t="s">
-        <v>67</v>
-      </c>
-      <c r="G38" s="90" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B39" s="89">
+      <c r="E38" s="71" t="s">
+        <v>321</v>
+      </c>
+      <c r="F38" s="71" t="s">
+        <v>322</v>
+      </c>
+      <c r="G38" s="85" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B39" s="84">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="C39" s="57" t="s">
-        <v>329</v>
+        <v>240</v>
       </c>
       <c r="D39" s="58">
         <v>1</v>
       </c>
-      <c r="E39" s="71" t="s">
-        <v>330</v>
+      <c r="E39" s="73" t="s">
+        <v>327</v>
       </c>
       <c r="F39" s="71" t="s">
-        <v>331</v>
-      </c>
-      <c r="G39" s="90" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B40" s="89">
+        <v>225</v>
+      </c>
+      <c r="G39" s="85" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B40" s="84">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="C40" s="57" t="s">
-        <v>243</v>
+        <v>139</v>
       </c>
       <c r="D40" s="58">
-        <v>1</v>
-      </c>
-      <c r="E40" s="74" t="s">
-        <v>336</v>
+        <v>2</v>
+      </c>
+      <c r="E40" s="59" t="s">
+        <v>114</v>
       </c>
       <c r="F40" s="71" t="s">
-        <v>228</v>
-      </c>
-      <c r="G40" s="90" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B41" s="89">
+        <v>360</v>
+      </c>
+      <c r="G40" s="85" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B41" s="84">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="C41" s="57" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="D41" s="58">
-        <v>2</v>
-      </c>
-      <c r="E41" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="F41" s="71" t="s">
-        <v>370</v>
-      </c>
-      <c r="G41" s="90" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B42" s="89">
+        <v>6</v>
+      </c>
+      <c r="E41" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="F41" s="59" t="s">
+        <v>315</v>
+      </c>
+      <c r="G41" s="85" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B42" s="84">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="C42" s="57" t="s">
-        <v>122</v>
-      </c>
-      <c r="D42" s="58">
-        <v>6</v>
+        <v>181</v>
+      </c>
+      <c r="D42" s="55" t="s">
+        <v>52</v>
       </c>
       <c r="E42" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="F42" s="59" t="s">
-        <v>324</v>
-      </c>
-      <c r="G42" s="90" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B43" s="89">
+        <v>114</v>
+      </c>
+      <c r="F42" s="71" t="s">
+        <v>363</v>
+      </c>
+      <c r="G42" s="85" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B43" s="84">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="C43" s="57" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D43" s="55" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E43" s="57" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F43" s="71" t="s">
-        <v>373</v>
-      </c>
-      <c r="G43" s="90" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B44" s="89">
+        <v>328</v>
+      </c>
+      <c r="G43" s="85" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B44" s="84">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="C44" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="D44" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="57" t="s">
-        <v>117</v>
+        <v>197</v>
+      </c>
+      <c r="D44" s="58">
+        <v>1</v>
+      </c>
+      <c r="E44" s="73" t="s">
+        <v>198</v>
       </c>
       <c r="F44" s="71" t="s">
-        <v>337</v>
-      </c>
-      <c r="G44" s="90" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B45" s="89">
+        <v>212</v>
+      </c>
+      <c r="G44" s="85" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B45" s="84">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C45" s="57" t="s">
-        <v>200</v>
-      </c>
-      <c r="D45" s="58">
-        <v>1</v>
-      </c>
-      <c r="E45" s="74" t="s">
-        <v>201</v>
-      </c>
-      <c r="F45" s="71" t="s">
-        <v>215</v>
-      </c>
-      <c r="G45" s="90" t="s">
-        <v>338</v>
+        <v>167</v>
+      </c>
+      <c r="D45" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E45" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="F45" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="G45" s="85" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B46" s="89">
+      <c r="B46" s="84">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="C46" s="57" t="s">
-        <v>170</v>
-      </c>
-      <c r="D46" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="57" t="s">
-        <v>72</v>
+        <v>110</v>
+      </c>
+      <c r="D46" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="E46" s="73" t="s">
+        <v>112</v>
       </c>
       <c r="F46" s="59" t="s">
-        <v>63</v>
-      </c>
-      <c r="G46" s="90" t="s">
-        <v>73</v>
+        <v>32</v>
+      </c>
+      <c r="G46" s="85" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B47" s="89">
+      <c r="B47" s="84">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C47" s="57" t="s">
-        <v>113</v>
-      </c>
-      <c r="D47" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="E47" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="F47" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" s="90" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B48" s="89">
+      <c r="C47" s="61" t="s">
+        <v>148</v>
+      </c>
+      <c r="D47" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="61" t="s">
+        <v>32</v>
+      </c>
+      <c r="F47" s="75" t="s">
+        <v>187</v>
+      </c>
+      <c r="G47" s="86" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B48" s="84">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C48" s="61" t="s">
-        <v>151</v>
-      </c>
-      <c r="D48" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="F48" s="78" t="s">
-        <v>190</v>
-      </c>
-      <c r="G48" s="91" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B49" s="89">
+      <c r="C48" s="72" t="s">
+        <v>267</v>
+      </c>
+      <c r="D48" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="E48" s="73" t="s">
+        <v>284</v>
+      </c>
+      <c r="F48" s="73" t="s">
+        <v>261</v>
+      </c>
+      <c r="G48" s="92" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B49" s="84">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C49" s="72" t="s">
-        <v>271</v>
-      </c>
-      <c r="D49" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E49" s="74" t="s">
-        <v>289</v>
-      </c>
-      <c r="F49" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="G49" s="98" t="s">
-        <v>307</v>
+      <c r="C49" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="D49" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="57" t="s">
+        <v>69</v>
+      </c>
+      <c r="F49" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="G49" s="85" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B50" s="89">
+      <c r="B50" s="87">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C50" s="57" t="s">
-        <v>171</v>
-      </c>
-      <c r="D50" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" s="57" t="s">
-        <v>72</v>
-      </c>
-      <c r="F50" s="59" t="s">
-        <v>63</v>
-      </c>
-      <c r="G50" s="90" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B51" s="92">
-        <f t="shared" si="0"/>
+      <c r="C50" s="72" t="s">
+        <v>268</v>
+      </c>
+      <c r="D50" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="E50" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="F50" s="73" t="s">
+        <v>261</v>
+      </c>
+      <c r="G50" s="92" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B51" s="84">
+        <f t="shared" ref="B51:B81" si="1">IF(C51="","",B50+1)</f>
         <v>31</v>
       </c>
-      <c r="C51" s="72" t="s">
-        <v>272</v>
-      </c>
-      <c r="D51" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E51" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="F51" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="G51" s="98" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B52" s="89">
-        <f t="shared" ref="B52:B83" si="1">IF(C52="","",B51+1)</f>
+      <c r="C51" s="57" t="s">
+        <v>123</v>
+      </c>
+      <c r="D51" s="58">
+        <v>1</v>
+      </c>
+      <c r="E51" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="F51" s="75" t="s">
+        <v>221</v>
+      </c>
+      <c r="G51" s="85" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B52" s="84">
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="C52" s="57" t="s">
-        <v>126</v>
-      </c>
-      <c r="D52" s="58">
-        <v>1</v>
-      </c>
-      <c r="E52" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="F52" s="78" t="s">
-        <v>224</v>
-      </c>
-      <c r="G52" s="90" t="s">
-        <v>128</v>
+      <c r="C52" s="72" t="s">
+        <v>269</v>
+      </c>
+      <c r="D52" s="55" t="s">
+        <v>285</v>
+      </c>
+      <c r="E52" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="F52" s="73" t="s">
+        <v>261</v>
+      </c>
+      <c r="G52" s="92" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="53" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B53" s="89">
+      <c r="B53" s="84">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
-      <c r="C53" s="72" t="s">
-        <v>273</v>
-      </c>
-      <c r="D53" s="55" t="s">
-        <v>290</v>
-      </c>
-      <c r="E53" s="74" t="s">
+      <c r="C53" s="57" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" s="58">
+        <v>1</v>
+      </c>
+      <c r="E53" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="F53" s="71" t="s">
         <v>115</v>
       </c>
-      <c r="F53" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="G53" s="98" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B54" s="89">
+      <c r="G53" s="85" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B54" s="84">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="C54" s="57" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="D54" s="58">
         <v>1</v>
       </c>
-      <c r="E54" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="F54" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="G54" s="90" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B55" s="89">
+      <c r="E54" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="F54" s="75" t="s">
+        <v>370</v>
+      </c>
+      <c r="G54" s="85" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B55" s="84">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="C55" s="57" t="s">
-        <v>127</v>
-      </c>
-      <c r="D55" s="58">
-        <v>1</v>
-      </c>
-      <c r="E55" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="F55" s="78" t="s">
-        <v>380</v>
-      </c>
-      <c r="G55" s="90" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B56" s="89">
+      <c r="C55" s="72" t="s">
+        <v>270</v>
+      </c>
+      <c r="D55" s="55" t="s">
+        <v>285</v>
+      </c>
+      <c r="E55" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="F55" s="73" t="s">
+        <v>261</v>
+      </c>
+      <c r="G55" s="92" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B56" s="84">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="C56" s="72" t="s">
-        <v>274</v>
+      <c r="C56" s="57" t="s">
+        <v>220</v>
       </c>
       <c r="D56" s="55" t="s">
-        <v>290</v>
-      </c>
-      <c r="E56" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="F56" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="G56" s="98" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="57" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B57" s="89">
+        <v>18</v>
+      </c>
+      <c r="E56" s="59" t="s">
+        <v>112</v>
+      </c>
+      <c r="F56" s="71" t="s">
+        <v>330</v>
+      </c>
+      <c r="G56" s="86" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B57" s="84">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="C57" s="57" t="s">
-        <v>223</v>
+        <v>98</v>
       </c>
       <c r="D57" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="E57" s="59" t="s">
-        <v>115</v>
+        <v>17</v>
+      </c>
+      <c r="E57" s="57" t="s">
+        <v>112</v>
       </c>
       <c r="F57" s="71" t="s">
-        <v>339</v>
-      </c>
-      <c r="G57" s="91" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B58" s="89">
+        <v>356</v>
+      </c>
+      <c r="G57" s="85" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B58" s="84">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="C58" s="57" t="s">
+      <c r="C58" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="D58" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="F58" s="76" t="s">
+        <v>331</v>
+      </c>
+      <c r="G58" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="D58" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" s="57" t="s">
-        <v>115</v>
-      </c>
-      <c r="F58" s="71" t="s">
-        <v>366</v>
-      </c>
-      <c r="G58" s="90" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="59" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B59" s="89">
+    </row>
+    <row r="59" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B59" s="84">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="C59" s="63" t="s">
-        <v>102</v>
-      </c>
-      <c r="D59" s="64" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" s="63" t="s">
-        <v>115</v>
-      </c>
-      <c r="F59" s="79" t="s">
-        <v>340</v>
-      </c>
-      <c r="G59" s="93" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="60" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B60" s="89">
+      <c r="C59" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="D59" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="E59" s="57" t="s">
+        <v>114</v>
+      </c>
+      <c r="F59" s="71" t="s">
+        <v>221</v>
+      </c>
+      <c r="G59" s="85" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B60" s="84">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="C60" s="57" t="s">
-        <v>196</v>
-      </c>
-      <c r="D60" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="E60" s="57" t="s">
-        <v>117</v>
+        <v>170</v>
+      </c>
+      <c r="D60" s="58">
+        <v>1</v>
+      </c>
+      <c r="E60" s="59" t="s">
+        <v>114</v>
       </c>
       <c r="F60" s="71" t="s">
-        <v>224</v>
-      </c>
-      <c r="G60" s="90" t="s">
-        <v>197</v>
+        <v>115</v>
+      </c>
+      <c r="G60" s="85" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B61" s="89">
+      <c r="B61" s="84">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="C61" s="57" t="s">
-        <v>173</v>
-      </c>
-      <c r="D61" s="58">
-        <v>1</v>
-      </c>
-      <c r="E61" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="F61" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="G61" s="90" t="s">
-        <v>174</v>
+        <v>153</v>
+      </c>
+      <c r="D61" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="57" t="s">
+        <v>43</v>
+      </c>
+      <c r="F61" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="G61" s="85" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B62" s="89">
+      <c r="B62" s="84">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="C62" s="57" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D62" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" s="57" t="s">
+        <v>153</v>
+      </c>
+      <c r="F62" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="G62" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="E62" s="57" t="s">
-        <v>46</v>
-      </c>
-      <c r="F62" s="57" t="s">
-        <v>157</v>
-      </c>
-      <c r="G62" s="90" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B63" s="89">
+    </row>
+    <row r="63" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B63" s="84">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="C63" s="57" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="D63" s="55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E63" s="57" t="s">
-        <v>156</v>
-      </c>
-      <c r="F63" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="G63" s="90" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="64" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B64" s="89">
+        <v>112</v>
+      </c>
+      <c r="F63" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="G63" s="85" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B64" s="84">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="C64" s="57" t="s">
-        <v>105</v>
+        <v>213</v>
       </c>
       <c r="D64" s="55" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E64" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="F64" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="F64" s="71" t="s">
-        <v>47</v>
-      </c>
-      <c r="G64" s="90" t="s">
-        <v>107</v>
+      <c r="G64" s="85" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="65" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B65" s="89">
+      <c r="B65" s="84">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="C65" s="57" t="s">
-        <v>216</v>
-      </c>
-      <c r="D65" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E65" s="57" t="s">
-        <v>214</v>
-      </c>
-      <c r="F65" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="G65" s="90" t="s">
-        <v>217</v>
+        <v>200</v>
+      </c>
+      <c r="D65" s="58">
+        <v>1</v>
+      </c>
+      <c r="E65" s="59" t="s">
+        <v>208</v>
+      </c>
+      <c r="F65" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="G65" s="85" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B66" s="89">
+      <c r="B66" s="84">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="C66" s="57" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D66" s="58">
         <v>1</v>
       </c>
       <c r="E66" s="59" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F66" s="59" t="s">
-        <v>212</v>
-      </c>
-      <c r="G66" s="90" t="s">
-        <v>341</v>
+        <v>209</v>
+      </c>
+      <c r="G66" s="85" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B67" s="89">
+      <c r="B67" s="84">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="C67" s="57" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D67" s="58">
         <v>1</v>
       </c>
       <c r="E67" s="59" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F67" s="59" t="s">
-        <v>212</v>
-      </c>
-      <c r="G67" s="90" t="s">
-        <v>342</v>
+        <v>210</v>
+      </c>
+      <c r="G67" s="85" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B68" s="89">
+      <c r="B68" s="84">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="C68" s="57" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D68" s="58">
         <v>1</v>
       </c>
       <c r="E68" s="59" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F68" s="59" t="s">
-        <v>213</v>
-      </c>
-      <c r="G68" s="90" t="s">
-        <v>343</v>
+        <v>196</v>
+      </c>
+      <c r="G68" s="85" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B69" s="89">
+      <c r="B69" s="84">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="C69" s="57" t="s">
-        <v>206</v>
+        <v>350</v>
       </c>
       <c r="D69" s="58">
         <v>1</v>
       </c>
-      <c r="E69" s="59" t="s">
-        <v>211</v>
-      </c>
-      <c r="F69" s="59" t="s">
-        <v>199</v>
-      </c>
-      <c r="G69" s="90" t="s">
-        <v>344</v>
+      <c r="E69" s="119" t="s">
+        <v>352</v>
+      </c>
+      <c r="F69" s="119" t="s">
+        <v>355</v>
+      </c>
+      <c r="G69" s="92" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="70" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B70" s="89">
+      <c r="B70" s="84">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="C70" s="57" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="D70" s="58">
         <v>1</v>
       </c>
-      <c r="E70" s="126" t="s">
-        <v>362</v>
-      </c>
-      <c r="F70" s="126" t="s">
-        <v>365</v>
-      </c>
-      <c r="G70" s="98" t="s">
-        <v>363</v>
+      <c r="E70" s="119" t="s">
+        <v>352</v>
+      </c>
+      <c r="F70" s="119" t="s">
+        <v>355</v>
+      </c>
+      <c r="G70" s="92" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="71" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B71" s="89">
+      <c r="B71" s="84">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="C71" s="57" t="s">
-        <v>361</v>
-      </c>
-      <c r="D71" s="58">
+        <v>204</v>
+      </c>
+      <c r="D71" s="56">
         <v>1</v>
       </c>
-      <c r="E71" s="126" t="s">
-        <v>362</v>
-      </c>
-      <c r="F71" s="126" t="s">
-        <v>365</v>
-      </c>
-      <c r="G71" s="98" t="s">
-        <v>364</v>
+      <c r="E71" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="F71" s="59" t="s">
+        <v>191</v>
+      </c>
+      <c r="G71" s="85" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B72" s="89">
+      <c r="B72" s="84">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="C72" s="57" t="s">
-        <v>207</v>
-      </c>
-      <c r="D72" s="56">
-        <v>1</v>
+        <v>76</v>
+      </c>
+      <c r="D72" s="58">
+        <v>4</v>
       </c>
       <c r="E72" s="57" t="s">
-        <v>201</v>
+        <v>54</v>
       </c>
       <c r="F72" s="59" t="s">
-        <v>194</v>
-      </c>
-      <c r="G72" s="90" t="s">
-        <v>345</v>
+        <v>114</v>
+      </c>
+      <c r="G72" s="85" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B73" s="89">
+      <c r="B73" s="84">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="C73" s="57" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D73" s="58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E73" s="57" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F73" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="G73" s="90" t="s">
-        <v>91</v>
+        <v>114</v>
+      </c>
+      <c r="G73" s="85" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="74" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B74" s="89">
+      <c r="B74" s="84">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="C74" s="72" t="s">
-        <v>355</v>
-      </c>
-      <c r="D74" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E74" s="74" t="s">
-        <v>291</v>
-      </c>
-      <c r="F74" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="G74" s="98" t="s">
-        <v>311</v>
+      <c r="C74" s="57" t="s">
+        <v>77</v>
+      </c>
+      <c r="D74" s="58">
+        <v>1</v>
+      </c>
+      <c r="E74" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="F74" s="59" t="s">
+        <v>112</v>
+      </c>
+      <c r="G74" s="85" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="75" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B75" s="89">
+      <c r="B75" s="84">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="C75" s="57" t="s">
-        <v>85</v>
+        <v>340</v>
       </c>
       <c r="D75" s="58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E75" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="F75" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="G75" s="90" t="s">
-        <v>98</v>
+        <v>54</v>
+      </c>
+      <c r="F75" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="G75" s="85" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B76" s="89">
+      <c r="B76" s="84">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="C76" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="D76" s="58">
-        <v>1</v>
+        <v>161</v>
+      </c>
+      <c r="D76" s="55" t="s">
+        <v>53</v>
       </c>
       <c r="E76" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="F76" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="G76" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="F76" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="G76" s="90" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="77" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B77" s="89">
+    </row>
+    <row r="77" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B77" s="84">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="C77" s="57" t="s">
-        <v>349</v>
+        <v>117</v>
       </c>
       <c r="D77" s="58">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E77" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="F77" s="57" t="s">
-        <v>62</v>
-      </c>
-      <c r="G77" s="90" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="78" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B78" s="89">
+        <v>40</v>
+      </c>
+      <c r="F77" s="71" t="s">
+        <v>226</v>
+      </c>
+      <c r="G77" s="85" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B78" s="84">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="C78" s="57" t="s">
-        <v>164</v>
-      </c>
-      <c r="D78" s="55" t="s">
-        <v>56</v>
-      </c>
-      <c r="E78" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="F78" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="G78" s="90" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="79" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B79" s="89">
+      <c r="C78" s="61" t="s">
+        <v>150</v>
+      </c>
+      <c r="D78" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="E78" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="F78" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="G78" s="86" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B79" s="84">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
       <c r="C79" s="57" t="s">
-        <v>120</v>
-      </c>
-      <c r="D79" s="58">
-        <v>6</v>
+        <v>156</v>
+      </c>
+      <c r="D79" s="55" t="s">
+        <v>51</v>
       </c>
       <c r="E79" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="F79" s="71" t="s">
-        <v>229</v>
-      </c>
-      <c r="G79" s="90" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="80" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B80" s="89">
+        <v>40</v>
+      </c>
+      <c r="F79" s="59" t="s">
+        <v>54</v>
+      </c>
+      <c r="G79" s="85" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B80" s="84">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="C80" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="D80" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="E80" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="F80" s="78" t="s">
-        <v>41</v>
-      </c>
-      <c r="G80" s="91" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="81" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B81" s="89">
+      <c r="C80" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="D80" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="E80" s="57" t="s">
+        <v>40</v>
+      </c>
+      <c r="F80" s="59" t="s">
+        <v>59</v>
+      </c>
+      <c r="G80" s="85" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B81" s="84">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="C81" s="57" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D81" s="55" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E81" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="F81" s="59" t="s">
-        <v>57</v>
-      </c>
-      <c r="G81" s="90" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="82" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B82" s="89">
-        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="F81" s="71" t="s">
+        <v>222</v>
+      </c>
+      <c r="G81" s="85" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B82" s="84">
+        <f t="shared" ref="B82:B112" si="2">IF(C82="","",B81+1)</f>
         <v>62</v>
       </c>
       <c r="C82" s="57" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D82" s="55" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E82" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="F82" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="G82" s="90" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="83" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B83" s="89">
-        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="F82" s="71" t="s">
+        <v>339</v>
+      </c>
+      <c r="G82" s="85" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B83" s="84">
+        <f t="shared" si="2"/>
         <v>63</v>
       </c>
       <c r="C83" s="57" t="s">
         <v>160</v>
       </c>
-      <c r="D83" s="55" t="s">
-        <v>55</v>
+      <c r="D83" s="58">
+        <v>5</v>
       </c>
       <c r="E83" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="F83" s="71" t="s">
-        <v>225</v>
-      </c>
-      <c r="G83" s="90" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B84" s="89">
-        <f t="shared" ref="B84:B115" si="2">IF(C84="","",B83+1)</f>
+        <v>40</v>
+      </c>
+      <c r="F83" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="G83" s="85" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B84" s="84">
+        <f t="shared" si="2"/>
         <v>64</v>
       </c>
       <c r="C84" s="57" t="s">
-        <v>161</v>
+        <v>337</v>
       </c>
       <c r="D84" s="55" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="E84" s="57" t="s">
-        <v>43</v>
-      </c>
-      <c r="F84" s="71" t="s">
-        <v>348</v>
-      </c>
-      <c r="G84" s="90" t="s">
-        <v>178</v>
+        <v>113</v>
+      </c>
+      <c r="F84" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="G84" s="85" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="85" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B85" s="89">
+      <c r="B85" s="84">
         <f t="shared" si="2"/>
         <v>65</v>
       </c>
       <c r="C85" s="57" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="D85" s="58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E85" s="57" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F85" s="59" t="s">
-        <v>63</v>
-      </c>
-      <c r="G85" s="90" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="86" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B86" s="89">
+        <v>114</v>
+      </c>
+      <c r="G85" s="85" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B86" s="84">
         <f t="shared" si="2"/>
         <v>66</v>
       </c>
       <c r="C86" s="57" t="s">
-        <v>346</v>
-      </c>
-      <c r="D86" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86" s="57" t="s">
-        <v>116</v>
+        <v>108</v>
+      </c>
+      <c r="D86" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" s="73" t="s">
+        <v>219</v>
       </c>
       <c r="F86" s="59" t="s">
-        <v>43</v>
-      </c>
-      <c r="G86" s="90" t="s">
-        <v>347</v>
+        <v>114</v>
+      </c>
+      <c r="G86" s="85" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="87" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B87" s="89">
+      <c r="B87" s="84">
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="C87" s="57" t="s">
-        <v>219</v>
-      </c>
-      <c r="D87" s="58">
-        <v>2</v>
-      </c>
-      <c r="E87" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="F87" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="G87" s="90" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B88" s="89">
+      <c r="C87" s="72" t="s">
+        <v>271</v>
+      </c>
+      <c r="D87" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="E87" s="73" t="s">
+        <v>286</v>
+      </c>
+      <c r="F87" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="G87" s="92" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B88" s="84">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
       <c r="C88" s="57" t="s">
-        <v>111</v>
-      </c>
-      <c r="D88" s="60" t="s">
-        <v>20</v>
-      </c>
-      <c r="E88" s="74" t="s">
-        <v>222</v>
-      </c>
-      <c r="F88" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="G88" s="90" t="s">
-        <v>112</v>
+        <v>80</v>
+      </c>
+      <c r="D88" s="58">
+        <v>1</v>
+      </c>
+      <c r="E88" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="F88" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="G88" s="85" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B89" s="89">
+      <c r="B89" s="84">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="C89" s="72" t="s">
-        <v>275</v>
-      </c>
-      <c r="D89" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E89" s="74" t="s">
-        <v>291</v>
-      </c>
-      <c r="F89" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="G89" s="98" t="s">
-        <v>312</v>
+      <c r="C89" s="57" t="s">
+        <v>253</v>
+      </c>
+      <c r="D89" s="55" t="s">
+        <v>254</v>
+      </c>
+      <c r="E89" s="57" t="s">
+        <v>255</v>
+      </c>
+      <c r="F89" s="59" t="s">
+        <v>256</v>
+      </c>
+      <c r="G89" s="85" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="90" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B90" s="89">
+      <c r="B90" s="84">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="C90" s="57" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D90" s="58">
         <v>1</v>
       </c>
       <c r="E90" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="F90" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="G90" s="90" t="s">
-        <v>96</v>
+        <v>54</v>
+      </c>
+      <c r="F90" s="59" t="s">
+        <v>112</v>
+      </c>
+      <c r="G90" s="85" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B91" s="89">
+      <c r="B91" s="84">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
       <c r="C91" s="57" t="s">
-        <v>256</v>
-      </c>
-      <c r="D91" s="55" t="s">
-        <v>257</v>
+        <v>81</v>
+      </c>
+      <c r="D91" s="58">
+        <v>1</v>
       </c>
       <c r="E91" s="57" t="s">
-        <v>258</v>
-      </c>
-      <c r="F91" s="59" t="s">
-        <v>259</v>
-      </c>
-      <c r="G91" s="90" t="s">
-        <v>260</v>
+        <v>54</v>
+      </c>
+      <c r="F91" s="62" t="s">
+        <v>114</v>
+      </c>
+      <c r="G91" s="85" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="92" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B92" s="89">
+      <c r="B92" s="84">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="C92" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="D92" s="58">
-        <v>1</v>
+        <v>258</v>
+      </c>
+      <c r="D92" s="55" t="s">
+        <v>254</v>
       </c>
       <c r="E92" s="57" t="s">
-        <v>57</v>
+        <v>255</v>
       </c>
       <c r="F92" s="59" t="s">
-        <v>115</v>
-      </c>
-      <c r="G92" s="90" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B93" s="89">
+        <v>259</v>
+      </c>
+      <c r="G92" s="85" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B93" s="84">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="C93" s="57" t="s">
-        <v>84</v>
-      </c>
-      <c r="D93" s="58">
-        <v>1</v>
+        <v>218</v>
+      </c>
+      <c r="D93" s="55" t="s">
+        <v>18</v>
       </c>
       <c r="E93" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="F93" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="G93" s="90" t="s">
-        <v>97</v>
+        <v>113</v>
+      </c>
+      <c r="F93" s="71" t="s">
+        <v>248</v>
+      </c>
+      <c r="G93" s="86" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B94" s="89">
+      <c r="B94" s="84">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
       <c r="C94" s="57" t="s">
-        <v>261</v>
+        <v>84</v>
       </c>
       <c r="D94" s="55" t="s">
-        <v>257</v>
+        <v>17</v>
       </c>
       <c r="E94" s="57" t="s">
-        <v>258</v>
-      </c>
-      <c r="F94" s="59" t="s">
-        <v>262</v>
-      </c>
-      <c r="G94" s="90" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B95" s="89">
+        <v>58</v>
+      </c>
+      <c r="F94" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="G94" s="85" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B95" s="84">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="C95" s="57" t="s">
-        <v>221</v>
-      </c>
-      <c r="D95" s="55" t="s">
-        <v>20</v>
+      <c r="C95" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="D95" s="64" t="s">
+        <v>17</v>
       </c>
       <c r="E95" s="57" t="s">
-        <v>116</v>
-      </c>
-      <c r="F95" s="71" t="s">
-        <v>251</v>
-      </c>
-      <c r="G95" s="91" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B96" s="89">
+        <v>58</v>
+      </c>
+      <c r="F95" s="63" t="s">
+        <v>112</v>
+      </c>
+      <c r="G95" s="88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B96" s="84">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="C96" s="57" t="s">
-        <v>87</v>
+      <c r="C96" s="72" t="s">
+        <v>346</v>
       </c>
       <c r="D96" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E96" s="57" t="s">
-        <v>61</v>
-      </c>
-      <c r="F96" s="63" t="s">
-        <v>115</v>
-      </c>
-      <c r="G96" s="90" t="s">
-        <v>89</v>
+        <v>287</v>
+      </c>
+      <c r="E96" s="73" t="s">
+        <v>288</v>
+      </c>
+      <c r="F96" s="73" t="s">
+        <v>289</v>
+      </c>
+      <c r="G96" s="92" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="97" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B97" s="89">
+      <c r="B97" s="84">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="C97" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="D97" s="64" t="s">
-        <v>19</v>
+      <c r="C97" s="57" t="s">
+        <v>79</v>
+      </c>
+      <c r="D97" s="58">
+        <v>1</v>
       </c>
       <c r="E97" s="57" t="s">
-        <v>61</v>
-      </c>
-      <c r="F97" s="63" t="s">
-        <v>115</v>
-      </c>
-      <c r="G97" s="93" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B98" s="89">
+        <v>54</v>
+      </c>
+      <c r="F97" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="G97" s="85" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B98" s="84">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="C98" s="72" t="s">
-        <v>356</v>
-      </c>
-      <c r="D98" s="55" t="s">
-        <v>292</v>
-      </c>
-      <c r="E98" s="74" t="s">
-        <v>293</v>
-      </c>
-      <c r="F98" s="74" t="s">
-        <v>294</v>
-      </c>
-      <c r="G98" s="98" t="s">
-        <v>313</v>
+      <c r="C98" s="57" t="s">
+        <v>152</v>
+      </c>
+      <c r="D98" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="E98" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="F98" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="G98" s="85" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="99" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B99" s="89">
+      <c r="B99" s="84">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
       <c r="C99" s="57" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D99" s="58">
         <v>1</v>
       </c>
       <c r="E99" s="57" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F99" s="59" t="s">
-        <v>117</v>
-      </c>
-      <c r="G99" s="90" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B100" s="89">
+        <v>39</v>
+      </c>
+      <c r="G99" s="85" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B100" s="84">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="C100" s="57" t="s">
-        <v>155</v>
-      </c>
-      <c r="D100" s="60" t="s">
-        <v>45</v>
+        <v>105</v>
+      </c>
+      <c r="D100" s="55" t="s">
+        <v>17</v>
       </c>
       <c r="E100" s="57" t="s">
-        <v>41</v>
-      </c>
-      <c r="F100" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="G100" s="90" t="s">
-        <v>50</v>
+        <v>39</v>
+      </c>
+      <c r="F100" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="G100" s="85" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="101" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B101" s="89">
+      <c r="B101" s="84">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="C101" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="D101" s="58">
-        <v>1</v>
-      </c>
-      <c r="E101" s="57" t="s">
-        <v>57</v>
-      </c>
-      <c r="F101" s="59" t="s">
-        <v>42</v>
-      </c>
-      <c r="G101" s="90" t="s">
-        <v>100</v>
+      <c r="C101" s="61" t="s">
+        <v>73</v>
+      </c>
+      <c r="D101" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="F101" s="75" t="s">
+        <v>187</v>
+      </c>
+      <c r="G101" s="86" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B102" s="89">
+      <c r="B102" s="84">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-      <c r="C102" s="57" t="s">
-        <v>108</v>
-      </c>
-      <c r="D102" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E102" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="F102" s="71" t="s">
-        <v>115</v>
-      </c>
-      <c r="G102" s="90" t="s">
-        <v>106</v>
+      <c r="C102" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E102" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="F102" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="G102" s="89" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B103" s="89">
+      <c r="B103" s="84">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="C103" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="D103" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="E103" s="61" t="s">
-        <v>38</v>
-      </c>
-      <c r="F103" s="78" t="s">
-        <v>190</v>
-      </c>
-      <c r="G103" s="91" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="104" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B104" s="89">
+      <c r="C103" s="66" t="s">
+        <v>151</v>
+      </c>
+      <c r="D103" s="67">
+        <v>1</v>
+      </c>
+      <c r="E103" s="66" t="s">
+        <v>31</v>
+      </c>
+      <c r="F103" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="G103" s="90" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B104" s="84">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
-      <c r="C104" s="65" t="s">
-        <v>248</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E104" s="65" t="s">
-        <v>252</v>
-      </c>
-      <c r="F104" s="80" t="s">
-        <v>11</v>
-      </c>
-      <c r="G104" s="94" t="s">
-        <v>36</v>
+      <c r="C104" s="61" t="s">
+        <v>244</v>
+      </c>
+      <c r="D104" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="F104" s="75" t="s">
+        <v>250</v>
+      </c>
+      <c r="G104" s="86" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="105" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B105" s="89">
+      <c r="B105" s="84">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
-      <c r="C105" s="66" t="s">
-        <v>154</v>
-      </c>
-      <c r="D105" s="67">
-        <v>1</v>
-      </c>
-      <c r="E105" s="66" t="s">
-        <v>34</v>
-      </c>
-      <c r="F105" s="80" t="s">
-        <v>10</v>
-      </c>
-      <c r="G105" s="95" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="106" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B106" s="89">
+      <c r="C105" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="D105" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="E105" s="57" t="s">
+        <v>187</v>
+      </c>
+      <c r="F105" s="59" t="s">
+        <v>241</v>
+      </c>
+      <c r="G105" s="85" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B106" s="84">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
-      <c r="C106" s="61" t="s">
-        <v>247</v>
+      <c r="C106" s="57" t="s">
+        <v>242</v>
       </c>
       <c r="D106" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="E106" s="61" t="s">
-        <v>34</v>
-      </c>
-      <c r="F106" s="78" t="s">
-        <v>253</v>
-      </c>
-      <c r="G106" s="91" t="s">
-        <v>249</v>
+        <v>18</v>
+      </c>
+      <c r="E106" s="57" t="s">
+        <v>241</v>
+      </c>
+      <c r="F106" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="G106" s="85" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="107" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B107" s="89">
+      <c r="B107" s="84">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="C107" s="57" t="s">
-        <v>189</v>
+        <v>364</v>
       </c>
       <c r="D107" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="E107" s="57" t="s">
-        <v>190</v>
-      </c>
-      <c r="F107" s="59" t="s">
-        <v>244</v>
-      </c>
-      <c r="G107" s="90" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="108" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B108" s="89">
-        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="E107" s="119" t="s">
+        <v>355</v>
+      </c>
+      <c r="F107" s="119" t="s">
+        <v>32</v>
+      </c>
+      <c r="G107" s="92" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B108" s="84">
+        <f>IF(C108="","",B107+1)</f>
         <v>88</v>
       </c>
       <c r="C108" s="57" t="s">
-        <v>245</v>
-      </c>
-      <c r="D108" s="55" t="s">
-        <v>20</v>
+        <v>349</v>
+      </c>
+      <c r="D108" s="58">
+        <v>1</v>
       </c>
       <c r="E108" s="57" t="s">
-        <v>244</v>
-      </c>
-      <c r="F108" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="G108" s="90" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B109" s="89">
-        <f t="shared" si="2"/>
+        <v>223</v>
+      </c>
+      <c r="F108" s="71" t="s">
+        <v>247</v>
+      </c>
+      <c r="G108" s="85" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="109" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
+      <c r="B109" s="84">
+        <f>IF(C109="","",B108+1)</f>
         <v>89</v>
       </c>
-      <c r="C109" s="57" t="s">
-        <v>374</v>
-      </c>
-      <c r="D109" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E109" s="126" t="s">
-        <v>365</v>
-      </c>
-      <c r="F109" s="126" t="s">
-        <v>35</v>
-      </c>
-      <c r="G109" s="98" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="110" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B110" s="89">
+      <c r="C109" s="68" t="s">
+        <v>131</v>
+      </c>
+      <c r="D109" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E109" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="F109" s="78" t="s">
+        <v>357</v>
+      </c>
+      <c r="G109" s="91" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B110" s="84">
         <f>IF(C110="","",B109+1)</f>
         <v>90</v>
       </c>
-      <c r="C110" s="57" t="s">
-        <v>359</v>
-      </c>
-      <c r="D110" s="58">
+      <c r="C110" s="72" t="s">
+        <v>272</v>
+      </c>
+      <c r="D110" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="E110" s="73" t="s">
+        <v>261</v>
+      </c>
+      <c r="F110" s="73" t="s">
+        <v>262</v>
+      </c>
+      <c r="G110" s="92" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B111" s="84">
+        <f t="shared" si="2"/>
+        <v>91</v>
+      </c>
+      <c r="C111" s="57" t="s">
+        <v>177</v>
+      </c>
+      <c r="D111" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="E111" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="F111" s="71" t="s">
+        <v>198</v>
+      </c>
+      <c r="G111" s="85" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B112" s="84">
+        <f t="shared" si="2"/>
+        <v>92</v>
+      </c>
+      <c r="C112" s="57" t="s">
+        <v>199</v>
+      </c>
+      <c r="D112" s="58">
         <v>1</v>
       </c>
-      <c r="E110" s="57" t="s">
-        <v>226</v>
-      </c>
-      <c r="F110" s="71" t="s">
-        <v>250</v>
-      </c>
-      <c r="G110" s="90" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="111" spans="2:7" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="B111" s="89">
-        <f>IF(C111="","",B110+1)</f>
-        <v>91</v>
-      </c>
-      <c r="C111" s="68" t="s">
-        <v>134</v>
-      </c>
-      <c r="D111" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E111" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="F111" s="81" t="s">
-        <v>367</v>
-      </c>
-      <c r="G111" s="96" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="112" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B112" s="89">
-        <f>IF(C112="","",B111+1)</f>
-        <v>92</v>
-      </c>
-      <c r="C112" s="75" t="s">
-        <v>276</v>
-      </c>
-      <c r="D112" s="76" t="s">
-        <v>286</v>
-      </c>
-      <c r="E112" s="85" t="s">
-        <v>264</v>
-      </c>
-      <c r="F112" s="86" t="s">
-        <v>295</v>
-      </c>
-      <c r="G112" s="99" t="s">
-        <v>314</v>
+      <c r="E112" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="F112" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="G112" s="85" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B113" s="89">
+      <c r="B113" s="84">
         <f>IF(C113="","",B112+1)</f>
         <v>93</v>
       </c>
-      <c r="C113" s="72" t="s">
-        <v>277</v>
-      </c>
-      <c r="D113" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E113" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="F113" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="G113" s="98" t="s">
-        <v>315</v>
+      <c r="C113" s="57" t="s">
+        <v>227</v>
+      </c>
+      <c r="D113" s="58">
+        <v>2</v>
+      </c>
+      <c r="E113" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="F113" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="G113" s="85" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B114" s="89">
-        <f t="shared" si="2"/>
+      <c r="B114" s="84">
+        <f>IF(C114="","",B113+1)</f>
         <v>94</v>
       </c>
-      <c r="C114" s="57" t="s">
-        <v>180</v>
-      </c>
-      <c r="D114" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="E114" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="F114" s="71" t="s">
-        <v>201</v>
-      </c>
-      <c r="G114" s="90" t="s">
-        <v>181</v>
+      <c r="C114" s="72" t="s">
+        <v>273</v>
+      </c>
+      <c r="D114" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="E114" s="73" t="s">
+        <v>261</v>
+      </c>
+      <c r="F114" s="73" t="s">
+        <v>262</v>
+      </c>
+      <c r="G114" s="92" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B115" s="89">
-        <f t="shared" si="2"/>
+      <c r="B115" s="84">
+        <f t="shared" ref="B115:B139" si="3">IF(C115="","",B114+1)</f>
         <v>95</v>
       </c>
-      <c r="C115" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="D115" s="58">
+      <c r="C115" s="68" t="s">
+        <v>127</v>
+      </c>
+      <c r="D115" s="69">
         <v>1</v>
       </c>
-      <c r="E115" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="F115" s="71" t="s">
-        <v>194</v>
-      </c>
-      <c r="G115" s="90" t="s">
-        <v>350</v>
+      <c r="E115" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="F115" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="G115" s="91" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="116" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B116" s="89">
-        <f>IF(C116="","",B115+1)</f>
+      <c r="B116" s="84">
+        <f t="shared" si="3"/>
         <v>96</v>
       </c>
-      <c r="C116" s="57" t="s">
-        <v>230</v>
-      </c>
-      <c r="D116" s="58">
-        <v>2</v>
-      </c>
-      <c r="E116" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="F116" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="G116" s="90" t="s">
-        <v>231</v>
+      <c r="C116" s="72" t="s">
+        <v>274</v>
+      </c>
+      <c r="D116" s="55" t="s">
+        <v>285</v>
+      </c>
+      <c r="E116" s="73" t="s">
+        <v>261</v>
+      </c>
+      <c r="F116" s="73" t="s">
+        <v>262</v>
+      </c>
+      <c r="G116" s="92" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="117" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B117" s="89">
-        <f>IF(C117="","",B116+1)</f>
+      <c r="B117" s="84">
+        <f t="shared" si="3"/>
         <v>97</v>
       </c>
-      <c r="C117" s="72" t="s">
-        <v>278</v>
-      </c>
-      <c r="D117" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E117" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="F117" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="G117" s="98" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="118" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B118" s="89">
-        <f t="shared" ref="B118:B142" si="3">IF(C118="","",B117+1)</f>
+      <c r="C117" s="57" t="s">
+        <v>142</v>
+      </c>
+      <c r="D117" s="58">
+        <v>1</v>
+      </c>
+      <c r="E117" s="59" t="s">
+        <v>115</v>
+      </c>
+      <c r="F117" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="G117" s="85" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B118" s="84">
+        <f t="shared" si="3"/>
         <v>98</v>
       </c>
       <c r="C118" s="68" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D118" s="69">
         <v>1</v>
       </c>
       <c r="E118" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="F118" s="82" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="96" t="s">
-        <v>132</v>
+        <v>115</v>
+      </c>
+      <c r="F118" s="80" t="s">
+        <v>369</v>
+      </c>
+      <c r="G118" s="91" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="119" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B119" s="89">
+      <c r="B119" s="84">
         <f t="shared" si="3"/>
         <v>99</v>
       </c>
-      <c r="C119" s="72" t="s">
-        <v>279</v>
-      </c>
-      <c r="D119" s="55" t="s">
+      <c r="C119" s="74" t="s">
+        <v>275</v>
+      </c>
+      <c r="D119" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="E119" s="82" t="s">
+        <v>261</v>
+      </c>
+      <c r="F119" s="83" t="s">
         <v>290</v>
       </c>
-      <c r="E119" s="74" t="s">
-        <v>264</v>
-      </c>
-      <c r="F119" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="G119" s="98" t="s">
-        <v>317</v>
+      <c r="G119" s="93" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="120" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B120" s="89">
+      <c r="B120" s="84">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
       <c r="C120" s="57" t="s">
-        <v>145</v>
-      </c>
-      <c r="D120" s="58">
-        <v>1</v>
+        <v>233</v>
+      </c>
+      <c r="D120" s="55" t="s">
+        <v>18</v>
       </c>
       <c r="E120" s="59" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F120" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="G120" s="90" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="121" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B121" s="89">
+        <v>116</v>
+      </c>
+      <c r="G120" s="85" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B121" s="84">
         <f t="shared" si="3"/>
         <v>101</v>
       </c>
-      <c r="C121" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="D121" s="69">
-        <v>1</v>
-      </c>
-      <c r="E121" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="F121" s="83" t="s">
-        <v>379</v>
-      </c>
-      <c r="G121" s="96" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="122" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B122" s="89">
+      <c r="C121" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="D121" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E121" s="63" t="s">
+        <v>115</v>
+      </c>
+      <c r="F121" s="81" t="s">
+        <v>191</v>
+      </c>
+      <c r="G121" s="88" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B122" s="84">
         <f t="shared" si="3"/>
         <v>102</v>
       </c>
-      <c r="C122" s="77" t="s">
-        <v>280</v>
-      </c>
-      <c r="D122" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="E122" s="87" t="s">
-        <v>264</v>
-      </c>
-      <c r="F122" s="88" t="s">
-        <v>296</v>
-      </c>
-      <c r="G122" s="100" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="123" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B123" s="89">
+      <c r="C122" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="D122" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="E122" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="F122" s="71" t="s">
+        <v>361</v>
+      </c>
+      <c r="G122" s="85" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="B123" s="84">
         <f t="shared" si="3"/>
         <v>103</v>
       </c>
       <c r="C123" s="57" t="s">
-        <v>236</v>
-      </c>
-      <c r="D123" s="55" t="s">
-        <v>20</v>
+        <v>189</v>
+      </c>
+      <c r="D123" s="58">
+        <v>1</v>
       </c>
       <c r="E123" s="59" t="s">
-        <v>118</v>
-      </c>
-      <c r="F123" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="G123" s="90" t="s">
-        <v>239</v>
+        <v>115</v>
+      </c>
+      <c r="F123" s="71" t="s">
+        <v>367</v>
+      </c>
+      <c r="G123" s="85" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="124" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B124" s="89">
+      <c r="B124" s="84">
         <f t="shared" si="3"/>
         <v>104</v>
       </c>
-      <c r="C124" s="63" t="s">
-        <v>138</v>
-      </c>
-      <c r="D124" s="64" t="s">
-        <v>19</v>
-      </c>
-      <c r="E124" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="F124" s="84" t="s">
-        <v>194</v>
-      </c>
-      <c r="G124" s="93" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="125" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B125" s="89">
+      <c r="C124" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="D124" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124" s="70" t="s">
+        <v>191</v>
+      </c>
+      <c r="F124" s="79" t="s">
+        <v>16</v>
+      </c>
+      <c r="G124" s="91" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="125" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B125" s="84">
         <f t="shared" si="3"/>
         <v>105</v>
       </c>
       <c r="C125" s="57" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="D125" s="55" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="E125" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="F125" s="71" t="s">
-        <v>371</v>
-      </c>
-      <c r="G125" s="90" t="s">
-        <v>188</v>
+        <v>115</v>
+      </c>
+      <c r="F125" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="G125" s="85" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="126" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B126" s="89">
+      <c r="B126" s="84">
         <f t="shared" si="3"/>
         <v>106</v>
       </c>
       <c r="C126" s="57" t="s">
-        <v>192</v>
-      </c>
-      <c r="D126" s="58">
-        <v>1</v>
-      </c>
-      <c r="E126" s="59" t="s">
-        <v>118</v>
+        <v>146</v>
+      </c>
+      <c r="D126" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E126" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="F126" s="71" t="s">
-        <v>377</v>
-      </c>
-      <c r="G126" s="90" t="s">
-        <v>175</v>
+        <v>342</v>
+      </c>
+      <c r="G126" s="85" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="127" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B127" s="89">
+      <c r="B127" s="84">
         <f t="shared" si="3"/>
         <v>107</v>
       </c>
-      <c r="C127" s="68" t="s">
-        <v>208</v>
-      </c>
-      <c r="D127" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E127" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="F127" s="82" t="s">
-        <v>16</v>
-      </c>
-      <c r="G127" s="96" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="128" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B128" s="89">
+      <c r="C127" s="72" t="s">
+        <v>276</v>
+      </c>
+      <c r="D127" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="E127" s="73" t="s">
+        <v>262</v>
+      </c>
+      <c r="F127" s="73" t="s">
+        <v>277</v>
+      </c>
+      <c r="G127" s="92" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="128" spans="2:7" ht="33" x14ac:dyDescent="0.3">
+      <c r="B128" s="84">
         <f t="shared" si="3"/>
         <v>108</v>
       </c>
-      <c r="C128" s="57" t="s">
-        <v>210</v>
-      </c>
-      <c r="D128" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E128" s="57" t="s">
-        <v>118</v>
-      </c>
-      <c r="F128" s="57" t="s">
-        <v>194</v>
-      </c>
-      <c r="G128" s="90" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="129" spans="2:7" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="B129" s="89">
+      <c r="C128" s="72" t="s">
+        <v>277</v>
+      </c>
+      <c r="D128" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="E128" s="73" t="s">
+        <v>291</v>
+      </c>
+      <c r="F128" s="73" t="s">
+        <v>292</v>
+      </c>
+      <c r="G128" s="92" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="129" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B129" s="84">
         <f t="shared" si="3"/>
         <v>109</v>
       </c>
       <c r="C129" s="57" t="s">
-        <v>149</v>
-      </c>
-      <c r="D129" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E129" s="57" t="s">
-        <v>119</v>
-      </c>
-      <c r="F129" s="71" t="s">
-        <v>351</v>
-      </c>
-      <c r="G129" s="90" t="s">
-        <v>150</v>
+        <v>345</v>
+      </c>
+      <c r="D129" s="58">
+        <v>1</v>
+      </c>
+      <c r="E129" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="F129" s="59" t="s">
+        <v>65</v>
+      </c>
+      <c r="G129" s="85" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="130" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B130" s="89">
+      <c r="B130" s="84">
         <f t="shared" si="3"/>
         <v>110</v>
       </c>
       <c r="C130" s="72" t="s">
-        <v>281</v>
-      </c>
-      <c r="D130" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E130" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="F130" s="74" t="s">
-        <v>282</v>
-      </c>
-      <c r="G130" s="98" t="s">
-        <v>319</v>
+        <v>278</v>
+      </c>
+      <c r="D130" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="E130" s="73" t="s">
+        <v>294</v>
+      </c>
+      <c r="F130" s="73" t="s">
+        <v>295</v>
+      </c>
+      <c r="G130" s="92" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="131" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B131" s="89">
+      <c r="B131" s="84">
         <f t="shared" si="3"/>
         <v>111</v>
       </c>
-      <c r="C131" s="72" t="s">
-        <v>282</v>
-      </c>
-      <c r="D131" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E131" s="74" t="s">
-        <v>297</v>
-      </c>
-      <c r="F131" s="74" t="s">
-        <v>298</v>
-      </c>
-      <c r="G131" s="98" t="s">
-        <v>320</v>
+      <c r="C131" s="57" t="s">
+        <v>343</v>
+      </c>
+      <c r="D131" s="58">
+        <v>2</v>
+      </c>
+      <c r="E131" s="59" t="s">
+        <v>116</v>
+      </c>
+      <c r="F131" s="71" t="s">
+        <v>366</v>
+      </c>
+      <c r="G131" s="85" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="132" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B132" s="89">
+      <c r="B132" s="84">
         <f t="shared" si="3"/>
         <v>112</v>
       </c>
-      <c r="C132" s="57" t="s">
-        <v>354</v>
-      </c>
-      <c r="D132" s="58">
-        <v>1</v>
-      </c>
-      <c r="E132" s="59" t="s">
-        <v>119</v>
-      </c>
-      <c r="F132" s="59" t="s">
-        <v>68</v>
-      </c>
-      <c r="G132" s="90" t="s">
-        <v>148</v>
+      <c r="C132" s="72" t="s">
+        <v>279</v>
+      </c>
+      <c r="D132" s="58" t="s">
+        <v>281</v>
+      </c>
+      <c r="E132" s="73" t="s">
+        <v>262</v>
+      </c>
+      <c r="F132" s="73" t="s">
+        <v>294</v>
+      </c>
+      <c r="G132" s="92" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="133" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B133" s="89">
+      <c r="B133" s="84">
         <f t="shared" si="3"/>
         <v>113</v>
       </c>
       <c r="C133" s="72" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D133" s="55" t="s">
-        <v>299</v>
-      </c>
-      <c r="E133" s="74" t="s">
-        <v>300</v>
-      </c>
-      <c r="F133" s="74" t="s">
-        <v>301</v>
-      </c>
-      <c r="G133" s="98" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="134" spans="2:7" ht="33" x14ac:dyDescent="0.3">
-      <c r="B134" s="89">
+        <v>285</v>
+      </c>
+      <c r="E133" s="73" t="s">
+        <v>262</v>
+      </c>
+      <c r="F133" s="73" t="s">
+        <v>294</v>
+      </c>
+      <c r="G133" s="92" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="134" spans="2:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="B134" s="84">
         <f t="shared" si="3"/>
         <v>114</v>
       </c>
       <c r="C134" s="57" t="s">
-        <v>352</v>
-      </c>
-      <c r="D134" s="58">
-        <v>2</v>
-      </c>
-      <c r="E134" s="59" t="s">
-        <v>119</v>
+        <v>163</v>
+      </c>
+      <c r="D134" s="55" t="s">
+        <v>17</v>
+      </c>
+      <c r="E134" s="57" t="s">
+        <v>65</v>
       </c>
       <c r="F134" s="71" t="s">
-        <v>376</v>
-      </c>
-      <c r="G134" s="90" t="s">
-        <v>232</v>
+        <v>358</v>
+      </c>
+      <c r="G134" s="85" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B135" s="89">
+      <c r="B135" s="114">
         <f t="shared" si="3"/>
         <v>115</v>
       </c>
-      <c r="C135" s="72" t="s">
-        <v>284</v>
-      </c>
-      <c r="D135" s="58" t="s">
-        <v>286</v>
-      </c>
-      <c r="E135" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="F135" s="74" t="s">
-        <v>300</v>
-      </c>
-      <c r="G135" s="98" t="s">
-        <v>322</v>
+      <c r="C135" s="115" t="s">
+        <v>234</v>
+      </c>
+      <c r="D135" s="120" t="s">
+        <v>18</v>
+      </c>
+      <c r="E135" s="116" t="s">
+        <v>116</v>
+      </c>
+      <c r="F135" s="117" t="s">
+        <v>65</v>
+      </c>
+      <c r="G135" s="118" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="136" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B136" s="89">
+      <c r="B136" s="84">
         <f t="shared" si="3"/>
         <v>116</v>
       </c>
-      <c r="C136" s="72" t="s">
-        <v>285</v>
+      <c r="C136" s="57" t="s">
+        <v>230</v>
       </c>
       <c r="D136" s="55" t="s">
-        <v>290</v>
-      </c>
-      <c r="E136" s="74" t="s">
-        <v>265</v>
-      </c>
-      <c r="F136" s="74" t="s">
-        <v>300</v>
-      </c>
-      <c r="G136" s="98" t="s">
-        <v>323</v>
+        <v>52</v>
+      </c>
+      <c r="E136" s="59" t="s">
+        <v>231</v>
+      </c>
+      <c r="F136" s="71" t="s">
+        <v>58</v>
+      </c>
+      <c r="G136" s="85" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="137" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B137" s="89">
+      <c r="B137" s="84">
         <f t="shared" si="3"/>
         <v>117</v>
       </c>
       <c r="C137" s="57" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="D137" s="55" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="E137" s="57" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="F137" s="71" t="s">
-        <v>368</v>
-      </c>
-      <c r="G137" s="90" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="138" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B138" s="121">
+        <v>362</v>
+      </c>
+      <c r="G137" s="85" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B138" s="94">
         <f t="shared" si="3"/>
         <v>118</v>
       </c>
-      <c r="C138" s="122" t="s">
-        <v>237</v>
-      </c>
-      <c r="D138" s="127" t="s">
-        <v>20</v>
-      </c>
-      <c r="E138" s="123" t="s">
-        <v>119</v>
-      </c>
-      <c r="F138" s="124" t="s">
-        <v>68</v>
-      </c>
-      <c r="G138" s="125" t="s">
-        <v>240</v>
+      <c r="C138" s="109" t="s">
+        <v>344</v>
+      </c>
+      <c r="D138" s="110">
+        <v>1</v>
+      </c>
+      <c r="E138" s="111" t="s">
+        <v>116</v>
+      </c>
+      <c r="F138" s="112" t="s">
+        <v>368</v>
+      </c>
+      <c r="G138" s="113" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="139" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B139" s="89">
-        <f t="shared" si="3"/>
-        <v>119</v>
-      </c>
-      <c r="C139" s="57" t="s">
-        <v>233</v>
-      </c>
-      <c r="D139" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="E139" s="59" t="s">
-        <v>234</v>
-      </c>
-      <c r="F139" s="71" t="s">
-        <v>61</v>
-      </c>
-      <c r="G139" s="90" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="140" spans="2:7" ht="66" x14ac:dyDescent="0.3">
-      <c r="B140" s="89">
-        <f t="shared" si="3"/>
-        <v>120</v>
-      </c>
-      <c r="C140" s="57" t="s">
-        <v>182</v>
-      </c>
-      <c r="D140" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="E140" s="57" t="s">
-        <v>119</v>
-      </c>
-      <c r="F140" s="71" t="s">
-        <v>372</v>
-      </c>
-      <c r="G140" s="90" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="141" spans="2:7" ht="66.75" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B141" s="101">
-        <f t="shared" si="3"/>
-        <v>121</v>
-      </c>
-      <c r="C141" s="116" t="s">
-        <v>353</v>
-      </c>
-      <c r="D141" s="117">
-        <v>1</v>
-      </c>
-      <c r="E141" s="118" t="s">
-        <v>119</v>
-      </c>
-      <c r="F141" s="119" t="s">
-        <v>378</v>
-      </c>
-      <c r="G141" s="120" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="142" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B142" s="21" t="str">
+      <c r="B139" s="21" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="C142"/>
-      <c r="D142"/>
-      <c r="E142" s="54"/>
-      <c r="F142" s="54"/>
-      <c r="G142" s="54"/>
+      <c r="C139"/>
+      <c r="D139"/>
+      <c r="E139" s="54"/>
+      <c r="F139" s="54"/>
+      <c r="G139" s="54"/>
     </row>
   </sheetData>
-  <autoFilter ref="C20:G141" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C21:G142">
-      <sortCondition ref="C20:C141"/>
+  <autoFilter ref="C20:G138" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C21:G139">
+      <sortCondition ref="C20:C138"/>
     </sortState>
   </autoFilter>
   <mergeCells count="2">
